--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="G3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.48</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.77</v>
+        <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>2.62</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>2.42</v>
       </c>
       <c r="K5" t="n">
-        <v>630</v>
+        <v>6.2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
@@ -1864,31 +1864,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Beroe Stara Za</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H6" t="n">
         <v>2.34</v>
       </c>
-      <c r="G6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.72</v>
-      </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>2.66</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>630</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
@@ -2118,31 +2118,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Beroe Stara Za</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.52</v>
+        <v>2.34</v>
       </c>
       <c r="G7" t="n">
-        <v>1.89</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>2.66</v>
       </c>
       <c r="K7" t="n">
-        <v>640</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>1.89</v>
       </c>
       <c r="H8" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="I8" t="n">
-        <v>1.92</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>640</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,36 +2621,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Ashdod</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.22</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>2.56</v>
+        <v>1.75</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>1.89</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="G10" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="H10" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="I10" t="n">
-        <v>870</v>
+        <v>7.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2.02</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>500</v>
+        <v>660</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>FC Ashdod</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G11" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
@@ -3388,28 +3388,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>1.77</v>
       </c>
       <c r="G12" t="n">
-        <v>600</v>
+        <v>1.98</v>
       </c>
       <c r="H12" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="I12" t="n">
         <v>870</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>2.02</v>
       </c>
       <c r="K12" t="n">
         <v>500</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="G13" t="n">
         <v>600</v>
       </c>
       <c r="H13" t="n">
-        <v>2.72</v>
+        <v>1.87</v>
       </c>
       <c r="I13" t="n">
-        <v>3.15</v>
+        <v>870</v>
       </c>
       <c r="J13" t="n">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
@@ -3896,31 +3896,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.28</v>
+        <v>1.48</v>
       </c>
       <c r="G14" t="n">
-        <v>2.58</v>
+        <v>4.5</v>
       </c>
       <c r="H14" t="n">
-        <v>3.85</v>
+        <v>2.72</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>510</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,37 +4145,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2.24</v>
+        <v>3.8</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="J15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.25</v>
       </c>
-      <c r="K15" t="n">
-        <v>6.8</v>
-      </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,66 +4399,66 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.12</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
-        <v>28</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
-        <v>13.5</v>
+        <v>2.7</v>
       </c>
       <c r="K16" t="n">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>1.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4467,183 +4467,183 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="G18" t="n">
-        <v>600</v>
+        <v>1.13</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>28</v>
       </c>
       <c r="I18" t="n">
-        <v>870</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>14</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>380</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>580</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>420</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>490</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>990</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
         <v>1.01</v>
       </c>
-      <c r="K18" t="n">
-        <v>500</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
         <v>1.01</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0</v>
-      </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>870</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-16 00:33:49</t>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>
@@ -5420,28 +5420,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Confianca</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="H20" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="I20" t="n">
         <v>870</v>
       </c>
       <c r="J20" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="K20" t="n">
         <v>500</v>
@@ -5459,200 +5459,708 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-16 03:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>600</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>870</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>500</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-16 03:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Inter Limeira</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I22" t="n">
+        <v>870</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K22" t="n">
+        <v>500</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.12</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>2026-05-16 00:33:49</t>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-16 03:08:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>1.83</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
         <v>1.94</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
         <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>1.48</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8</v>
+        <v>1.71</v>
       </c>
       <c r="H5" t="n">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="I5" t="n">
-        <v>2.62</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>2.42</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>6.2</v>
+        <v>630</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
@@ -1864,31 +1864,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>Beroe Stara Za</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.48</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
-        <v>1.77</v>
+        <v>3.35</v>
       </c>
       <c r="H6" t="n">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>2.66</v>
       </c>
       <c r="K6" t="n">
-        <v>630</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
@@ -2118,31 +2118,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Beroe Stara Za</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>1.89</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>2.16</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>2.66</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>640</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1.89</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="n">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>1.92</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>640</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,36 +2621,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FC Ashdod</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1.75</v>
+        <v>2.56</v>
       </c>
       <c r="I9" t="n">
-        <v>1.89</v>
+        <v>3.75</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="G10" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="H10" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="I10" t="n">
-        <v>7.6</v>
+        <v>870</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>660</v>
+        <v>500</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="H11" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.77</v>
+        <v>3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.98</v>
+        <v>4.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="I12" t="n">
-        <v>870</v>
+        <v>2.16</v>
       </c>
       <c r="J12" t="n">
-        <v>2.02</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>5.6</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="G13" t="n">
         <v>600</v>
       </c>
       <c r="H13" t="n">
-        <v>1.87</v>
+        <v>2.72</v>
       </c>
       <c r="I13" t="n">
-        <v>870</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="K13" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
@@ -3896,31 +3896,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.48</v>
+        <v>2.26</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>2.52</v>
       </c>
       <c r="H14" t="n">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="I14" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="K14" t="n">
-        <v>510</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,66 +4399,66 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="G16" t="n">
-        <v>2.54</v>
+        <v>1.13</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>28</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7</v>
+        <v>13.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>1.62</v>
+        <v>3.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.18</v>
+        <v>1.38</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4467,183 +4467,183 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,66 +4907,66 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1.13</v>
+        <v>600</v>
       </c>
       <c r="H18" t="n">
-        <v>28</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>30</v>
+        <v>870</v>
       </c>
       <c r="J18" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="K18" t="n">
-        <v>14</v>
+        <v>500</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.55</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4975,183 +4975,183 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confianca</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>
@@ -5420,28 +5420,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Inter Limeira</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="G20" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="H20" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="I20" t="n">
         <v>870</v>
       </c>
       <c r="J20" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="K20" t="n">
         <v>500</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,515 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-16 03:08:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Real Potosi</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G21" t="n">
-        <v>600</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I21" t="n">
-        <v>870</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K21" t="n">
-        <v>500</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>2026-05-16 03:08:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Botafogo PB</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Inter Limeira</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I22" t="n">
-        <v>870</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="K22" t="n">
-        <v>500</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>2026-05-16 03:08:13</t>
+          <t>2026-05-16 05:42:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
         <v>7.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G3" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>1.48</v>
       </c>
       <c r="G5" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>870</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
         <v>630</v>
@@ -1652,7 +1652,7 @@
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="G7" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="H7" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>640</v>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
         <v>1.71</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="n">
         <v>1.76</v>
@@ -2393,7 +2393,7 @@
         <v>1.92</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
         <v>4.4</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G13" t="n">
         <v>600</v>
       </c>
       <c r="H13" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="K13" t="n">
         <v>510</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>2.26</v>
       </c>
       <c r="G14" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H14" t="n">
         <v>3.85</v>
@@ -3917,7 +3917,7 @@
         <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K14" t="n">
         <v>3.25</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G15" t="n">
         <v>3.55</v>
@@ -4174,7 +4174,7 @@
         <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -4416,13 +4416,13 @@
         <v>1.11</v>
       </c>
       <c r="G16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="H16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J16" t="n">
         <v>13.5</v>
@@ -4437,13 +4437,13 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O16" t="n">
         <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
         <v>1.38</v>
@@ -4473,7 +4473,7 @@
         <v>100</v>
       </c>
       <c r="Z16" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -4485,13 +4485,13 @@
         <v>36</v>
       </c>
       <c r="AD16" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AE16" t="n">
         <v>580</v>
       </c>
       <c r="AF16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG16" t="n">
         <v>17</v>
@@ -4500,7 +4500,7 @@
         <v>75</v>
       </c>
       <c r="AI16" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="AJ16" t="n">
         <v>7.2</v>
@@ -4527,7 +4527,7 @@
         <v>50</v>
       </c>
       <c r="AR16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS16" t="n">
         <v>22</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>870</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K18" t="n">
         <v>500</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -5181,16 +5181,16 @@
         <v>2.22</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82</v>
+        <v>3.95</v>
       </c>
       <c r="I19" t="n">
         <v>870</v>
       </c>
       <c r="J19" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="K19" t="n">
-        <v>500</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="H20" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>870</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
-        <v>1.66</v>
+        <v>2.78</v>
       </c>
       <c r="K20" t="n">
-        <v>500</v>
+        <v>5.9</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-16 05:42:39</t>
+          <t>2026-05-16 08:16:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.48</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>2.62</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>630</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
@@ -1864,31 +1864,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Beroe Stara Za</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>1.48</v>
       </c>
       <c r="G6" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>870</v>
       </c>
       <c r="J6" t="n">
-        <v>2.66</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>630</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
@@ -2118,31 +2118,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Beroe Stara Za</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="G7" t="n">
-        <v>1.98</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="I7" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="K7" t="n">
-        <v>640</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>1.65</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8</v>
+        <v>1.98</v>
       </c>
       <c r="H8" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="I8" t="n">
-        <v>1.92</v>
+        <v>12.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>640</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,36 +2621,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Ashdod</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.22</v>
+        <v>5.4</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>2.56</v>
+        <v>1.67</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>1.82</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="G10" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="H10" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="I10" t="n">
-        <v>870</v>
+        <v>7.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>500</v>
+        <v>660</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>FC Ashdod</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G11" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>1.77</v>
       </c>
       <c r="G12" t="n">
-        <v>4.7</v>
+        <v>1.98</v>
       </c>
       <c r="H12" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="I12" t="n">
-        <v>2.16</v>
+        <v>870</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>5.6</v>
+        <v>500</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>600</v>
+        <v>2.54</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="K13" t="n">
-        <v>510</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,32 +3896,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.26</v>
+        <v>3.95</v>
       </c>
       <c r="G14" t="n">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.85</v>
+        <v>1.87</v>
       </c>
       <c r="I14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
         <v>4.8</v>
       </c>
-      <c r="J14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,55 +4145,55 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="G15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K15" t="n">
+        <v>510</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3.55</v>
       </c>
-      <c r="H15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.69</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,66 +4399,66 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="G16" t="n">
-        <v>1.12</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
-        <v>30</v>
+        <v>3.85</v>
       </c>
       <c r="I16" t="n">
-        <v>32</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>13.5</v>
+        <v>2.8</v>
       </c>
       <c r="K16" t="n">
-        <v>14</v>
+        <v>3.25</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>1.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.38</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4467,183 +4467,183 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,42 +4907,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>ACS Petrolul 52</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Otelul Galati</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="G18" t="n">
-        <v>600</v>
+        <v>1.62</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
-        <v>870</v>
+        <v>7.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>500</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -4951,136 +4951,136 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BH18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>2.22</v>
+        <v>3.55</v>
       </c>
       <c r="H19" t="n">
-        <v>3.95</v>
+        <v>2.28</v>
       </c>
       <c r="I19" t="n">
-        <v>870</v>
+        <v>3.05</v>
       </c>
       <c r="J19" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,261 +5398,1277 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-16 08:16:51</t>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>29</v>
+      </c>
+      <c r="I20" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" t="n">
+        <v>14</v>
+      </c>
+      <c r="K20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>410</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>580</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>450</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>490</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>990</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>110</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-16 10:51:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-16 10:51:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>600</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>870</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K22" t="n">
+        <v>500</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-16 10:51:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Confianca</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Maranhao</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I23" t="n">
+        <v>870</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-16 10:51:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Botafogo PB</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Inter Limeira</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F24" t="n">
         <v>2.02</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G24" t="n">
         <v>2.78</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H24" t="n">
         <v>3</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I24" t="n">
         <v>4.9</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J24" t="n">
         <v>2.78</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K24" t="n">
         <v>5.9</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>1.49</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q24" t="n">
         <v>2.24</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>2026-05-16 08:16:51</t>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-16 10:51:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,16 +875,16 @@
         <v>3.15</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P2" t="n">
         <v>1.36</v>
@@ -893,194 +893,194 @@
         <v>3.15</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G3" t="n">
         <v>1.97</v>
@@ -1120,25 +1120,25 @@
         <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
         <v>1.61</v>
@@ -1147,194 +1147,194 @@
         <v>2.34</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H4" t="n">
         <v>3.05</v>
@@ -1377,218 +1377,218 @@
         <v>3.65</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
         <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
         <v>4.8</v>
@@ -1631,208 +1631,208 @@
         <v>2.62</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q5" t="n">
         <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="H6" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="I6" t="n">
         <v>870</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
         <v>630</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -2142,7 +2142,7 @@
         <v>2.66</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>1.65</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
-        <v>2.06</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>640</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G10" t="n">
         <v>1.82</v>
@@ -2901,7 +2901,7 @@
         <v>7.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
         <v>660</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
         <v>1.56</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="H11" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -3388,28 +3388,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>870</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>2.64</v>
       </c>
       <c r="K12" t="n">
         <v>500</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>2.54</v>
+        <v>1.97</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,31 +3896,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G14" t="n">
         <v>3.95</v>
       </c>
-      <c r="G14" t="n">
-        <v>4.7</v>
-      </c>
       <c r="H14" t="n">
-        <v>1.87</v>
+        <v>2.72</v>
       </c>
       <c r="I14" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>2.96</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -4150,32 +4150,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.46</v>
+        <v>2.26</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5</v>
+        <v>2.54</v>
       </c>
       <c r="H15" t="n">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="I15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.25</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="K15" t="n">
-        <v>510</v>
-      </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,31 +4404,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.28</v>
+        <v>3.95</v>
       </c>
       <c r="G16" t="n">
-        <v>2.54</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
-        <v>3.85</v>
+        <v>1.87</v>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>2.02</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>1.71</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>2.76</v>
       </c>
       <c r="G17" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H17" t="n">
         <v>2.34</v>
       </c>
       <c r="I17" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="J17" t="n">
         <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G18" t="n">
         <v>1.62</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
         <v>7.4</v>
@@ -4942,25 +4942,25 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
         <v>1.94</v>
@@ -5032,7 +5032,7 @@
         <v>3.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AR18" t="n">
         <v>4</v>
@@ -5083,75 +5083,75 @@
         <v>4.2</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="G19" t="n">
-        <v>3.55</v>
+        <v>1.29</v>
       </c>
       <c r="H19" t="n">
-        <v>2.28</v>
+        <v>13.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3.05</v>
+        <v>16.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="K19" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,66 +5415,66 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>1.12</v>
+        <v>2.32</v>
       </c>
       <c r="H20" t="n">
-        <v>29</v>
+        <v>3.45</v>
       </c>
       <c r="I20" t="n">
-        <v>30</v>
+        <v>3.85</v>
       </c>
       <c r="J20" t="n">
-        <v>14</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>14.5</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5483,183 +5483,183 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,36 +5669,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,36 +5923,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
-        <v>600</v>
+        <v>3.55</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="I22" t="n">
-        <v>870</v>
+        <v>3.05</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,66 +6177,66 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="G23" t="n">
-        <v>2.22</v>
+        <v>1.12</v>
       </c>
       <c r="H23" t="n">
-        <v>3.95</v>
+        <v>28</v>
       </c>
       <c r="I23" t="n">
-        <v>870</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>1.85</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P23" t="n">
-        <v>1.53</v>
+        <v>3.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.28</v>
+        <v>1.38</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -6245,430 +6245,1192 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-16 10:51:03</t>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-16 13:25:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Confianca</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Maranhao</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I25" t="n">
+        <v>870</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-16 13:25:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G26" t="n">
+        <v>600</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I26" t="n">
+        <v>870</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K26" t="n">
+        <v>500</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-16 13:25:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Botafogo PB</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Inter Limeira</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F27" t="n">
         <v>2.02</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G27" t="n">
         <v>2.78</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H27" t="n">
         <v>3</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I27" t="n">
         <v>4.9</v>
       </c>
-      <c r="J24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K27" t="n">
         <v>5.9</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>1.49</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB24" t="inlineStr">
-        <is>
-          <t>2026-05-16 10:51:03</t>
+      <c r="Q27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-05-16 13:25:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -899,7 +899,7 @@
         <v>6.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="U2" t="n">
         <v>1.57</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -1141,10 +1141,10 @@
         <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
@@ -1156,25 +1156,25 @@
         <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA3" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AB3" t="n">
         <v>7.2</v>
@@ -1183,10 +1183,10 @@
         <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF3" t="n">
         <v>11</v>
@@ -1198,7 +1198,7 @@
         <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
         <v>26</v>
@@ -1210,13 +1210,13 @@
         <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN3" t="n">
         <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AP3" t="n">
         <v>9</v>
@@ -1225,10 +1225,10 @@
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
         <v>5.9</v>
@@ -1240,10 +1240,10 @@
         <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
@@ -1252,25 +1252,25 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>15.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
         <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.35</v>
@@ -1285,13 +1285,13 @@
         <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="BM3" t="n">
         <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO3" t="n">
         <v>3.3</v>
@@ -1315,13 +1315,13 @@
         <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW3" t="n">
         <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BY3" t="n">
         <v>1.04</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -1407,10 +1407,10 @@
         <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="V4" t="n">
         <v>1.39</v>
@@ -1533,7 +1533,7 @@
         <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK4" t="n">
         <v>1.04</v>
@@ -1545,31 +1545,31 @@
         <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.04</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS4" t="n">
         <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW4" t="n">
         <v>1.04</v>
@@ -1581,14 +1581,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA4" t="n">
         <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>2.48</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
         <v>2.96</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,19 +2151,19 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S7" t="n">
         <v>3.55</v>
@@ -2175,52 +2175,52 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -2235,58 +2235,58 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>2.12</v>
       </c>
       <c r="AS7" t="n">
-        <v>38</v>
+        <v>2.28</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>1.96</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.8</v>
+        <v>1.88</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>2.06</v>
       </c>
       <c r="AW7" t="n">
-        <v>27</v>
+        <v>2.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>2.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>2.02</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17</v>
+        <v>2.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>40</v>
+        <v>2.28</v>
       </c>
       <c r="BB7" t="n">
-        <v>26</v>
+        <v>2.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>2.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>2.28</v>
       </c>
       <c r="BE7" t="n">
-        <v>40</v>
+        <v>2.28</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -2384,10 +2384,10 @@
         <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
         <v>7.2</v>
@@ -2396,55 +2396,55 @@
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R8" t="n">
         <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="n">
         <v>24</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB8" t="n">
         <v>11</v>
@@ -2459,16 +2459,16 @@
         <v>100</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ8" t="n">
         <v>21</v>
@@ -2477,67 +2477,67 @@
         <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN8" t="n">
         <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX8" t="n">
         <v>3.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>12.5</v>
+        <v>3.55</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2668,7 +2668,7 @@
         <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R9" t="n">
         <v>1.32</v>
@@ -2686,7 +2686,7 @@
         <v>2.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
         <v>16</v>
@@ -2755,7 +2755,7 @@
         <v>13</v>
       </c>
       <c r="AT9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AU9" t="n">
         <v>7.4</v>
@@ -2815,10 +2815,10 @@
         <v>21</v>
       </c>
       <c r="BN9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BP9" t="n">
         <v>80</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>2.22</v>
       </c>
       <c r="I10" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
@@ -2931,13 +2931,13 @@
         <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
         <v>1.35</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>990</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K11" t="n">
         <v>500</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
         <v>1.23</v>
@@ -3308,55 +3308,55 @@
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>990</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
         <v>500</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
@@ -3562,55 +3562,55 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K13" t="n">
         <v>500</v>
@@ -3675,13 +3675,13 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q13" t="n">
         <v>1.22</v>
@@ -3816,55 +3816,55 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -3908,10 +3908,10 @@
         <v>4.1</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="I14" t="n">
         <v>2.02</v>
@@ -3920,7 +3920,7 @@
         <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3935,7 +3935,7 @@
         <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
         <v>1.74</v>
@@ -3950,13 +3950,13 @@
         <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
         <v>1.98</v>
       </c>
       <c r="W14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4070,65 +4070,65 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -4159,40 +4159,40 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="G15" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="H15" t="n">
-        <v>2.26</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>990</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>660</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>2.42</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
@@ -4201,64 +4201,64 @@
         <v>2.38</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
         <v>1000</v>
@@ -4267,122 +4267,122 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>16.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AR15" t="n">
-        <v>26</v>
+        <v>2.06</v>
       </c>
       <c r="AS15" t="n">
-        <v>40</v>
+        <v>2.14</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.6</v>
+        <v>1.89</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>1.86</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>1.99</v>
       </c>
       <c r="AW15" t="n">
-        <v>34</v>
+        <v>2.08</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.87</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>1.98</v>
       </c>
       <c r="BA15" t="n">
-        <v>36</v>
+        <v>2.08</v>
       </c>
       <c r="BB15" t="n">
-        <v>15.5</v>
+        <v>2</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>1.98</v>
       </c>
       <c r="BD15" t="n">
-        <v>22</v>
+        <v>2.04</v>
       </c>
       <c r="BE15" t="n">
-        <v>40</v>
+        <v>2.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -4416,16 +4416,16 @@
         <v>2.26</v>
       </c>
       <c r="G16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
         <v>3.25</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
@@ -4443,16 +4443,16 @@
         <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
         <v>1.5</v>
@@ -4461,10 +4461,10 @@
         <v>2.46</v>
       </c>
       <c r="V16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X16" t="n">
         <v>26</v>
@@ -4482,7 +4482,7 @@
         <v>14</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>15</v>
@@ -4515,58 +4515,58 @@
         <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>15</v>
+        <v>4.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
         <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
         <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="BE16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
         <v>9.800000000000001</v>
@@ -4578,65 +4578,65 @@
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -4685,10 +4685,10 @@
         <v>4.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
         <v>3.05</v>
@@ -4703,10 +4703,10 @@
         <v>1.92</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H18" t="n">
         <v>3.2</v>
@@ -4939,7 +4939,7 @@
         <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
@@ -4948,7 +4948,7 @@
         <v>2.52</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P18" t="n">
         <v>1.62</v>
@@ -4957,7 +4957,7 @@
         <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
         <v>3.85</v>
@@ -4972,7 +4972,7 @@
         <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
         <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
         <v>1.46</v>
@@ -5217,10 +5217,10 @@
         <v>2.74</v>
       </c>
       <c r="T19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
         <v>2</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
         <v>2.34</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
         <v>1.51</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -5686,10 +5686,10 @@
         <v>2.28</v>
       </c>
       <c r="G21" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="n">
         <v>4.8</v>
@@ -5707,7 +5707,7 @@
         <v>1.13</v>
       </c>
       <c r="N21" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="O21" t="n">
         <v>1.58</v>
@@ -5725,10 +5725,10 @@
         <v>5.7</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="V21" t="n">
         <v>1.28</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G22" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J22" t="n">
         <v>3.35</v>
@@ -5967,10 +5967,10 @@
         <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R22" t="n">
         <v>1.39</v>
@@ -5985,10 +5985,10 @@
         <v>2.08</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X22" t="n">
         <v>18.5</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -6356,55 +6356,55 @@
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>990</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K24" t="n">
         <v>500</v>
@@ -6469,13 +6469,13 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="O24" t="n">
         <v>1.16</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q24" t="n">
         <v>1.16</v>
@@ -6610,55 +6610,55 @@
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
         <v>3.95</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
@@ -6750,7 +6750,7 @@
         <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X25" t="n">
         <v>13.5</v>
@@ -6861,68 +6861,68 @@
         <v>40</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -6992,13 +6992,13 @@
         <v>1.67</v>
       </c>
       <c r="S26" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
         <v>2.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V26" t="n">
         <v>1.06</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G27" t="n">
         <v>3.35</v>
       </c>
       <c r="H27" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="I27" t="n">
         <v>2.58</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7231,7 +7231,7 @@
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
         <v>1.33</v>
@@ -7249,16 +7249,16 @@
         <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="U27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V27" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W27" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X27" t="n">
         <v>15.5</v>
@@ -7300,7 +7300,7 @@
         <v>65</v>
       </c>
       <c r="AK27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL27" t="n">
         <v>60</v>
@@ -7309,7 +7309,7 @@
         <v>130</v>
       </c>
       <c r="AN27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO27" t="n">
         <v>27</v>
@@ -7318,13 +7318,13 @@
         <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR27" t="n">
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT27" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>9.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX27" t="n">
         <v>18</v>
@@ -7360,10 +7360,10 @@
         <v>4.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG27" t="n">
         <v>16</v>
@@ -7372,65 +7372,65 @@
         <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -7461,55 +7461,55 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="G28" t="n">
         <v>1.63</v>
       </c>
       <c r="H28" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="O28" t="n">
         <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="V28" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W28" t="n">
         <v>2.58</v>
@@ -7521,10 +7521,10 @@
         <v>21</v>
       </c>
       <c r="Z28" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AA28" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="AB28" t="n">
         <v>7.8</v>
@@ -7533,94 +7533,94 @@
         <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AE28" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG28" t="n">
         <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AI28" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="AJ28" t="n">
         <v>17.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AL28" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AM28" t="n">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="AN28" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AO28" t="n">
-        <v>210</v>
+        <v>410</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>15</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>6</v>
+        <v>2.86</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="AY28" t="n">
         <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BC28" t="n">
-        <v>17</v>
+        <v>3.9</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -7724,22 +7724,22 @@
         <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="O29" t="n">
         <v>1.33</v>
@@ -7751,16 +7751,16 @@
         <v>1.97</v>
       </c>
       <c r="R29" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>1.97</v>
+        <v>3.55</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U29" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V29" t="n">
         <v>1.31</v>
@@ -7769,176 +7769,176 @@
         <v>1.92</v>
       </c>
       <c r="X29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD29" t="n">
         <v>17</v>
       </c>
-      <c r="Y29" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AE29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF29" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
         <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM29" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN29" t="n">
         <v>18.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP29" t="n">
         <v>12</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.6</v>
+        <v>26</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX29" t="n">
         <v>11</v>
       </c>
       <c r="AY29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA29" t="n">
         <v>9</v>
       </c>
-      <c r="AZ29" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>5</v>
-      </c>
       <c r="BB29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC29" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH29" t="n">
         <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN29" t="n">
         <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -7978,25 +7978,25 @@
         <v>2.38</v>
       </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J30" t="n">
         <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P30" t="n">
         <v>2.06</v>
@@ -8005,194 +8005,194 @@
         <v>1.69</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
         <v>14.5</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M31" t="n">
         <v>1.02</v>
@@ -8250,31 +8250,31 @@
         <v>8.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P31" t="n">
         <v>3.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R31" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S31" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="T31" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U31" t="n">
         <v>1.57</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="X31" t="n">
         <v>44</v>
@@ -8292,7 +8292,7 @@
         <v>14</v>
       </c>
       <c r="AC31" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AD31" t="n">
         <v>130</v>
@@ -8307,7 +8307,7 @@
         <v>17.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="n">
         <v>450</v>
@@ -8376,10 +8376,10 @@
         <v>55</v>
       </c>
       <c r="BE31" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="BF31" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BG31" t="n">
         <v>140</v>
@@ -8388,65 +8388,65 @@
         <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31" t="n">
         <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN31" t="n">
         <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT31" t="n">
         <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
         <v>3.05</v>
       </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J35" t="n">
         <v>2.72</v>
@@ -9272,7 +9272,7 @@
         <v>1.49</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-16 15:59:13</t>
+          <t>2026-05-16 18:33:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB43"/>
+  <dimension ref="A1:CB47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,10 +872,10 @@
         <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -902,7 +902,7 @@
         <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
         <v>2.46</v>
@@ -1019,68 +1019,68 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2" t="n">
         <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM2" t="n">
         <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO2" t="n">
         <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS2" t="n">
         <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW2" t="n">
         <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY2" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA2" t="n">
         <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>1.51</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J3" t="n">
         <v>3.85</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -1365,94 +1365,94 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G4" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9</v>
+        <v>2.74</v>
       </c>
       <c r="T4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.98</v>
       </c>
-      <c r="U4" t="n">
-        <v>1.69</v>
-      </c>
       <c r="V4" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1470,7 +1470,7 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
         <v>1.01</v>
@@ -1527,16 +1527,16 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,50 +1545,50 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>19.5</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>24</v>
-      </c>
       <c r="CA4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="G5" t="n">
         <v>2.02</v>
@@ -1628,13 +1628,13 @@
         <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J5" t="n">
         <v>2.92</v>
       </c>
       <c r="K5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L5" t="n">
         <v>1.62</v>
@@ -1643,16 +1643,16 @@
         <v>1.16</v>
       </c>
       <c r="N5" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="O5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="P5" t="n">
         <v>1.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.13</v>
@@ -1667,34 +1667,34 @@
         <v>1.57</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
         <v>1.98</v>
       </c>
       <c r="X5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y5" t="n">
         <v>15.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AB5" t="n">
         <v>6.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
         <v>32</v>
       </c>
       <c r="AE5" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AF5" t="n">
         <v>10.5</v>
@@ -1706,7 +1706,7 @@
         <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AJ5" t="n">
         <v>32</v>
@@ -1718,25 +1718,25 @@
         <v>110</v>
       </c>
       <c r="AM5" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ5" t="n">
         <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>5</v>
@@ -1745,10 +1745,10 @@
         <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX5" t="n">
         <v>8.6</v>
@@ -1757,28 +1757,28 @@
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD5" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
         <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
         <v>1.46</v>
@@ -1906,7 +1906,7 @@
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R6" t="n">
         <v>1.22</v>
@@ -1918,37 +1918,37 @@
         <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="X6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA6" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB6" t="n">
         <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF6" t="n">
         <v>11</v>
@@ -1960,7 +1960,7 @@
         <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ6" t="n">
         <v>26</v>
@@ -1972,13 +1972,13 @@
         <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN6" t="n">
         <v>23</v>
       </c>
       <c r="AO6" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP6" t="n">
         <v>9</v>
@@ -1987,10 +1987,10 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT6" t="n">
         <v>5.9</v>
@@ -1999,10 +1999,10 @@
         <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -2014,7 +2014,7 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB6" t="n">
         <v>18.5</v>
@@ -2023,22 +2023,22 @@
         <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF6" t="n">
         <v>13.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ6" t="n">
         <v>14</v>
@@ -2053,16 +2053,16 @@
         <v>4.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
         <v>3.35</v>
       </c>
       <c r="BP6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BR6" t="n">
         <v>44</v>
@@ -2071,16 +2071,16 @@
         <v>4.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BV6" t="n">
         <v>65</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX6" t="n">
         <v>85</v>
@@ -2089,14 +2089,14 @@
         <v>4.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CA6" t="n">
         <v>4.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H7" t="n">
         <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -2145,7 +2145,7 @@
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
@@ -2160,7 +2160,7 @@
         <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.26</v>
@@ -2175,16 +2175,16 @@
         <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X7" t="n">
         <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>28</v>
@@ -2229,7 +2229,7 @@
         <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AO7" t="n">
         <v>65</v>
@@ -2241,10 +2241,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT7" t="n">
         <v>7.8</v>
@@ -2256,7 +2256,7 @@
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX7" t="n">
         <v>13</v>
@@ -2268,16 +2268,16 @@
         <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE7" t="n">
         <v>6.2</v>
@@ -2286,7 +2286,7 @@
         <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH7" t="n">
         <v>3.45</v>
@@ -2298,7 +2298,7 @@
         <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL7" t="n">
         <v>190</v>
@@ -2313,7 +2313,7 @@
         <v>4</v>
       </c>
       <c r="BP7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
         <v>1.03</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P9" t="n">
         <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>4.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I10" t="n">
         <v>2.5</v>
@@ -2919,7 +2919,7 @@
         <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
         <v>1.94</v>
@@ -2937,7 +2937,7 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W10" t="n">
         <v>1.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
         <v>1.04</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="I12" t="n">
         <v>1.67</v>
@@ -3415,7 +3415,7 @@
         <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -3439,16 +3439,16 @@
         <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="U12" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
         <v>2.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
         <v>16</v>
@@ -3466,7 +3466,7 @@
         <v>22</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
         <v>12.5</v>
@@ -3505,64 +3505,64 @@
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>11.5</v>
+        <v>3.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>12.5</v>
+        <v>3.85</v>
       </c>
       <c r="AT12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="AW12" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="AX12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC12" t="n">
         <v>4.7</v>
       </c>
-      <c r="AY12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD12" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="BH12" t="n">
         <v>4</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ12" t="n">
         <v>13.5</v>
@@ -3571,34 +3571,34 @@
         <v>3.55</v>
       </c>
       <c r="BL12" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="BM12" t="n">
         <v>4.7</v>
       </c>
       <c r="BN12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BQ12" t="n">
         <v>4.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BS12" t="n">
         <v>4.6</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BV12" t="n">
         <v>12.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H13" t="n">
         <v>2.86</v>
@@ -3663,7 +3663,7 @@
         <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>2.28</v>
       </c>
       <c r="K13" t="n">
         <v>630</v>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.36</v>
@@ -3684,7 +3684,7 @@
         <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
         <v>1.2</v>
@@ -3702,7 +3702,7 @@
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>2.42</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H14" t="n">
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -3953,7 +3953,7 @@
         <v>1.78</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
         <v>1.54</v>
@@ -4019,10 +4019,10 @@
         <v>7.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT14" t="n">
         <v>6.6</v>
@@ -4031,40 +4031,40 @@
         <v>5.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AY14" t="n">
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BD14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE14" t="n">
         <v>4.2</v>
       </c>
-      <c r="BE14" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BF14" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BH14" t="n">
         <v>3.45</v>
@@ -4082,53 +4082,53 @@
         <v>190</v>
       </c>
       <c r="BM14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BN14" t="n">
         <v>6.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP14" t="n">
         <v>26</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BR14" t="n">
         <v>48</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT14" t="n">
         <v>7.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV14" t="n">
         <v>34</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BX14" t="n">
         <v>55</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BZ14" t="n">
         <v>46</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G15" t="n">
         <v>1.77</v>
@@ -4177,13 +4177,13 @@
         <v>4.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>1.28</v>
@@ -4219,10 +4219,10 @@
         <v>24</v>
       </c>
       <c r="Z15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA15" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB15" t="n">
         <v>11</v>
@@ -4246,7 +4246,7 @@
         <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ15" t="n">
         <v>21</v>
@@ -4255,7 +4255,7 @@
         <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
         <v>140</v>
@@ -4264,52 +4264,52 @@
         <v>12</v>
       </c>
       <c r="AO15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR15" t="n">
         <v>4</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AW15" t="n">
         <v>4.1</v>
       </c>
       <c r="AX15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY15" t="n">
         <v>3.2</v>
       </c>
-      <c r="AY15" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AZ15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB15" t="n">
         <v>3.65</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.55</v>
       </c>
       <c r="BC15" t="n">
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE15" t="n">
         <v>4.2</v>
@@ -4318,10 +4318,10 @@
         <v>7.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI15" t="n">
         <v>2.88</v>
@@ -4330,16 +4330,16 @@
         <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="BL15" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="BM15" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO15" t="n">
         <v>3.35</v>
@@ -4348,41 +4348,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BR15" t="n">
         <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BT15" t="n">
         <v>11</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BV15" t="n">
         <v>60</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BX15" t="n">
         <v>65</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BZ15" t="n">
         <v>24</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -4404,31 +4404,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Djurgardens</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.36</v>
+        <v>4.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44</v>
+        <v>4.4</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,206 +4437,206 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="T16" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="U16" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="W16" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="X16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB16" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>14</v>
-      </c>
       <c r="AC16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG16" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ16" t="n">
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ16" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT16" t="n">
+      <c r="BK16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN16" t="n">
         <v>11</v>
       </c>
-      <c r="AU16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BO16" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP16" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="BQ16" t="n">
         <v>1.04</v>
       </c>
       <c r="BR16" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BS16" t="n">
         <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="BV16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
         <v>1.04</v>
       </c>
       <c r="BX16" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BY16" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
         <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -4670,22 +4670,22 @@
         <v>3.25</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H17" t="n">
         <v>2.22</v>
       </c>
       <c r="I17" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -4703,19 +4703,19 @@
         <v>1.92</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U17" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W17" t="n">
         <v>1.37</v>
@@ -4742,7 +4742,7 @@
         <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF17" t="n">
         <v>28</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,31 +5674,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IFK Goteborg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J21" t="n">
         <v>4.1</v>
       </c>
-      <c r="G21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.75</v>
-      </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5707,142 +5707,142 @@
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="V21" t="n">
-        <v>1.98</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>2.26</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV21" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AW21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB21" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BC21" t="n">
-        <v>1.99</v>
+        <v>14.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.04</v>
+        <v>6.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.04</v>
+        <v>7</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,176 +5928,176 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Djurgardens</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.7</v>
       </c>
-      <c r="G22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.18</v>
-      </c>
       <c r="X22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF22" t="n">
         <v>22</v>
       </c>
-      <c r="Z22" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AG22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY22" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF22" t="n">
+      <c r="AZ22" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH22" t="n">
+      <c r="BA22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG22" t="n">
         <v>18</v>
       </c>
-      <c r="AI22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>7</v>
-      </c>
       <c r="BH22" t="n">
         <v>1000</v>
       </c>
@@ -6105,10 +6105,10 @@
         <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6117,50 +6117,50 @@
         <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ22" t="n">
         <v>1.04</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS22" t="n">
         <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW22" t="n">
         <v>1.04</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY22" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA22" t="n">
         <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -6182,239 +6182,239 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Ashdod</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.42</v>
+        <v>1.76</v>
       </c>
       <c r="G23" t="n">
-        <v>2.74</v>
+        <v>1.97</v>
       </c>
       <c r="H23" t="n">
-        <v>2.82</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.33</v>
       </c>
-      <c r="M23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.39</v>
-      </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="X23" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AA23" t="n">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AB23" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AG23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
         <v>44</v>
       </c>
       <c r="AM23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO23" t="n">
         <v>95</v>
       </c>
-      <c r="AN23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO23" t="n">
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>160</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BR23" t="n">
         <v>32</v>
       </c>
-      <c r="AP23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>120</v>
-      </c>
-      <c r="BM23" t="n">
+      <c r="BS23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY23" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>4.8</v>
       </c>
       <c r="BZ23" t="n">
         <v>28</v>
       </c>
       <c r="CA23" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -6436,239 +6436,239 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>FC Ashdod</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.76</v>
+        <v>2.36</v>
       </c>
       <c r="G24" t="n">
-        <v>1.96</v>
+        <v>2.44</v>
       </c>
       <c r="H24" t="n">
-        <v>4.6</v>
+        <v>2.92</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.39</v>
       </c>
-      <c r="M24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S24" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="U24" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="X24" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AA24" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN24" t="n">
         <v>23</v>
       </c>
-      <c r="AE24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>15</v>
-      </c>
       <c r="AO24" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AP24" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AR24" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AS24" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
         <v>6.6</v>
       </c>
       <c r="AV24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
         <v>15</v>
       </c>
-      <c r="AW24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>10</v>
-      </c>
       <c r="BG24" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="BJ24" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BL24" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN24" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="BP24" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR24" t="n">
         <v>34</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT24" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV24" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BX24" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ24" t="n">
         <v>28</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
         <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U25" t="n">
         <v>1.84</v>
@@ -6780,7 +6780,7 @@
         <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
         <v>23</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H26" t="n">
         <v>1.87</v>
@@ -6968,31 +6968,31 @@
         <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P26" t="n">
         <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R26" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S26" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
         <v>1.57</v>
@@ -7004,22 +7004,22 @@
         <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
         <v>16</v>
       </c>
       <c r="AA26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC26" t="n">
         <v>11.5</v>
@@ -7031,7 +7031,7 @@
         <v>23</v>
       </c>
       <c r="AF26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG26" t="n">
         <v>21</v>
@@ -7043,7 +7043,7 @@
         <v>38</v>
       </c>
       <c r="AJ26" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="n">
         <v>60</v>
@@ -7073,7 +7073,7 @@
         <v>15.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU26" t="n">
         <v>6.8</v>
@@ -7112,10 +7112,10 @@
         <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI26" t="n">
         <v>3.05</v>
@@ -7133,7 +7133,7 @@
         <v>1.04</v>
       </c>
       <c r="BN26" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO26" t="n">
         <v>5.8</v>
@@ -7154,7 +7154,7 @@
         <v>5.7</v>
       </c>
       <c r="BU26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV26" t="n">
         <v>15.5</v>
@@ -7163,7 +7163,7 @@
         <v>1.04</v>
       </c>
       <c r="BX26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY26" t="n">
         <v>1.04</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
         <v>1.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="O27" t="n">
         <v>1.82</v>
@@ -7246,7 +7246,7 @@
         <v>1.12</v>
       </c>
       <c r="S27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T27" t="n">
         <v>2.34</v>
@@ -7297,7 +7297,7 @@
         <v>130</v>
       </c>
       <c r="AJ27" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="n">
         <v>80</v>
@@ -7312,10 +7312,10 @@
         <v>160</v>
       </c>
       <c r="AO27" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ27" t="n">
         <v>5.8</v>
@@ -7324,7 +7324,7 @@
         <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -7336,7 +7336,7 @@
         <v>13.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX27" t="n">
         <v>6.2</v>
@@ -7360,13 +7360,13 @@
         <v>7.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF27" t="n">
         <v>7.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G28" t="n">
         <v>2.54</v>
@@ -7470,25 +7470,25 @@
         <v>3.8</v>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>2.84</v>
       </c>
       <c r="K28" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L28" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="M28" t="n">
         <v>1.14</v>
       </c>
       <c r="N28" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O28" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P28" t="n">
         <v>1.44</v>
@@ -7503,13 +7503,13 @@
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V28" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
         <v>1.65</v>
@@ -7533,10 +7533,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF28" t="n">
         <v>15.5</v>
@@ -7545,28 +7545,28 @@
         <v>15</v>
       </c>
       <c r="AH28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI28" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ28" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK28" t="n">
         <v>44</v>
       </c>
       <c r="AL28" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN28" t="n">
         <v>50</v>
       </c>
       <c r="AO28" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP28" t="n">
         <v>6.6</v>
@@ -7578,7 +7578,7 @@
         <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT28" t="n">
         <v>5.9</v>
@@ -7587,43 +7587,43 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW28" t="n">
         <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC28" t="n">
         <v>4.7</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE28" t="n">
         <v>5.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG28" t="n">
         <v>5.1</v>
       </c>
       <c r="BH28" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI28" t="n">
         <v>2.16</v>
@@ -7632,31 +7632,31 @@
         <v>14</v>
       </c>
       <c r="BK28" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BL28" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="BM28" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BN28" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO28" t="n">
         <v>3.95</v>
       </c>
       <c r="BP28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BQ28" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BR28" t="n">
         <v>60</v>
       </c>
       <c r="BS28" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BT28" t="n">
         <v>8</v>
@@ -7665,26 +7665,26 @@
         <v>5.5</v>
       </c>
       <c r="BV28" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BW28" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BX28" t="n">
         <v>80</v>
       </c>
       <c r="BY28" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BZ28" t="n">
         <v>70</v>
       </c>
       <c r="CA28" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="G29" t="n">
         <v>2.14</v>
       </c>
       <c r="H29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I29" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,46 +7739,46 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
         <v>1.29</v>
       </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R29" t="n">
         <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U29" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="V29" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W29" t="n">
         <v>1.87</v>
       </c>
       <c r="X29" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA29" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB29" t="n">
         <v>12</v>
@@ -7787,13 +7787,13 @@
         <v>10.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
         <v>60</v>
       </c>
       <c r="AF29" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG29" t="n">
         <v>13</v>
@@ -7802,10 +7802,10 @@
         <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK29" t="n">
         <v>26</v>
@@ -7817,28 +7817,28 @@
         <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO29" t="n">
         <v>60</v>
       </c>
       <c r="AP29" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>21</v>
+        <v>3.8</v>
       </c>
       <c r="AS29" t="n">
         <v>4</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
         <v>12</v>
@@ -7847,31 +7847,31 @@
         <v>3.95</v>
       </c>
       <c r="AX29" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BA29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE29" t="n">
         <v>4</v>
       </c>
-      <c r="BB29" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG29" t="n">
         <v>3.95</v>
@@ -7895,13 +7895,13 @@
         <v>1.04</v>
       </c>
       <c r="BN29" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ29" t="n">
         <v>1.04</v>
@@ -7916,7 +7916,7 @@
         <v>10.5</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV29" t="n">
         <v>46</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,239 +7960,239 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="G30" t="n">
-        <v>990</v>
+        <v>3.35</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I30" t="n">
-        <v>990</v>
+        <v>2.54</v>
       </c>
       <c r="J30" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>500</v>
+        <v>4.2</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="P30" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>1.15</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BL30" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT30" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BX30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -8214,239 +8214,239 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Farul Constanta</t>
+          <t>ACS Petrolul 52</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Metaloglobus Bucuresti</t>
+          <t>Otelul Galati</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.23</v>
+        <v>1.59</v>
       </c>
       <c r="G31" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="H31" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="I31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X31" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>16.5</v>
       </c>
-      <c r="J31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K31" t="n">
-        <v>8</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X31" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AK31" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AM31" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AN31" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="AO31" t="n">
-        <v>330</v>
+        <v>230</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="AR31" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="AT31" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>14</v>
+        <v>5.1</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="AX31" t="n">
         <v>7.4</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="BB31" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>12</v>
+        <v>2.88</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="BH31" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL31" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN31" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BP31" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR31" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT31" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV31" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX31" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -8468,239 +8468,239 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="G32" t="n">
-        <v>2.32</v>
+        <v>1.28</v>
       </c>
       <c r="H32" t="n">
-        <v>3.45</v>
+        <v>14</v>
       </c>
       <c r="I32" t="n">
-        <v>3.9</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="M32" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="O32" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="P32" t="n">
-        <v>1.76</v>
+        <v>2.66</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="T32" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="V32" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>1.76</v>
+        <v>4.5</v>
       </c>
       <c r="X32" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG32" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y32" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH32" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AI32" t="n">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="AJ32" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="AK32" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="AL32" t="n">
         <v>44</v>
       </c>
       <c r="AM32" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>330</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>180</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV32" t="n">
         <v>140</v>
       </c>
-      <c r="AN32" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>40</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI32" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BL32" t="n">
-        <v>160</v>
-      </c>
-      <c r="BM32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BN32" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP32" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR32" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BT32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV32" t="n">
-        <v>36</v>
-      </c>
       <c r="BW32" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BX32" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="BY32" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BZ32" t="n">
-        <v>38</v>
+        <v>10.5</v>
       </c>
       <c r="CA32" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -8722,246 +8722,246 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.86</v>
+        <v>2.08</v>
       </c>
       <c r="G33" t="n">
-        <v>3.35</v>
+        <v>2.38</v>
       </c>
       <c r="H33" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J33" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K33" t="n">
         <v>4.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P33" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T33" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U33" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="V33" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="W33" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="X33" t="n">
         <v>15.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR33" t="n">
         <v>19</v>
       </c>
-      <c r="AA33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG33" t="n">
+      <c r="AS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF33" t="n">
         <v>16.5</v>
       </c>
-      <c r="AH33" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ33" t="n">
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>160</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO33" t="n">
         <v>4</v>
       </c>
-      <c r="BA33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB33" t="n">
+      <c r="BP33" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ33" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>36</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>1.72</v>
-      </c>
       <c r="BR33" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.75</v>
+        <v>5.1</v>
       </c>
       <c r="BT33" t="n">
         <v>7.6</v>
       </c>
       <c r="BU33" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV33" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="BX33" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.75</v>
+        <v>5.3</v>
       </c>
       <c r="BZ33" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,175 +8976,175 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ACS Petrolul 52</t>
+          <t>AFC Eskilstuna</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Otelul Galati</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>1.63</v>
+        <v>990</v>
       </c>
       <c r="H34" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>8.4</v>
+        <v>990</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>500</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.64</v>
+        <v>1.1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="P34" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.14</v>
+        <v>1.16</v>
       </c>
       <c r="R34" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>3.15</v>
+        <v>1.15</v>
       </c>
       <c r="T34" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
         <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="n">
         <v>1000</v>
@@ -9201,14 +9201,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -9263,22 +9263,22 @@
         <v>1.07</v>
       </c>
       <c r="N35" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>1.33</v>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R35" t="n">
         <v>1.34</v>
       </c>
       <c r="S35" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T35" t="n">
         <v>1.8</v>
@@ -9293,7 +9293,7 @@
         <v>1.92</v>
       </c>
       <c r="X35" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y35" t="n">
         <v>15.5</v>
@@ -9323,10 +9323,10 @@
         <v>10.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ35" t="n">
         <v>26</v>
@@ -9335,13 +9335,13 @@
         <v>23</v>
       </c>
       <c r="AL35" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
       </c>
       <c r="AN35" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AO35" t="n">
         <v>55</v>
@@ -9356,7 +9356,7 @@
         <v>26</v>
       </c>
       <c r="AS35" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AT35" t="n">
         <v>8.4</v>
@@ -9368,7 +9368,7 @@
         <v>14.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AX35" t="n">
         <v>11</v>
@@ -9380,7 +9380,7 @@
         <v>16.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB35" t="n">
         <v>22</v>
@@ -9392,13 +9392,13 @@
         <v>32</v>
       </c>
       <c r="BE35" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF35" t="n">
         <v>13.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -9798,7 +9798,7 @@
         <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="X37" t="n">
         <v>44</v>
@@ -9825,7 +9825,7 @@
         <v>580</v>
       </c>
       <c r="AF37" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG37" t="n">
         <v>17.5</v>
@@ -9864,16 +9864,16 @@
         <v>120</v>
       </c>
       <c r="AS37" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AT37" t="n">
         <v>13.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV37" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AW37" t="n">
         <v>140</v>
@@ -9906,7 +9906,7 @@
         <v>2.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="BH37" t="n">
         <v>7</v>
@@ -9918,13 +9918,13 @@
         <v>22</v>
       </c>
       <c r="BK37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL37" t="n">
         <v>290</v>
       </c>
       <c r="BM37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BN37" t="n">
         <v>3.8</v>
@@ -9942,35 +9942,35 @@
         <v>30</v>
       </c>
       <c r="BS37" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BT37" t="n">
         <v>36</v>
       </c>
       <c r="BU37" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV37" t="n">
         <v>330</v>
       </c>
       <c r="BW37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX37" t="n">
         <v>220</v>
       </c>
       <c r="BY37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ37" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CA37" t="n">
         <v>5</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
@@ -9992,31 +9992,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G38" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="H38" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="J38" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K38" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -10025,22 +10025,22 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="O38" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="P38" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="R38" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="S38" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -10049,10 +10049,10 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10224,14 +10224,14 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10241,78 +10241,78 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="G39" t="n">
-        <v>2.36</v>
+        <v>1.49</v>
       </c>
       <c r="H39" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="J39" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="K39" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="L39" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="M39" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.52</v>
+        <v>3.45</v>
       </c>
       <c r="O39" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="P39" t="n">
-        <v>1.62</v>
+        <v>2.72</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.28</v>
+        <v>1.42</v>
       </c>
       <c r="R39" t="n">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="S39" t="n">
-        <v>3.85</v>
+        <v>1.93</v>
       </c>
       <c r="T39" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="W39" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z39" t="n">
         <v>1000</v>
@@ -10321,49 +10321,49 @@
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.01</v>
@@ -10375,43 +10375,43 @@
         <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW39" t="n">
         <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA39" t="n">
         <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE39" t="n">
         <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG39" t="n">
         <v>1.01</v>
@@ -10420,72 +10420,72 @@
         <v>1000</v>
       </c>
       <c r="BI39" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ39" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN39" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP39" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR39" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT39" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV39" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10495,234 +10495,234 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S40" t="n">
         <v>2.22</v>
       </c>
-      <c r="G40" t="n">
+      <c r="T40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W40" t="n">
         <v>2.4</v>
       </c>
-      <c r="H40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J40" t="n">
-        <v>3</v>
-      </c>
-      <c r="K40" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.71</v>
-      </c>
       <c r="X40" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z40" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD40" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE40" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG40" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH40" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK40" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL40" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR40" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV40" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX40" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY40" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB40" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC40" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF40" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH40" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ40" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL40" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN40" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO40" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP40" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR40" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT40" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU40" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV40" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX40" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40" t="n">
         <v>0</v>
@@ -10732,14 +10732,14 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10749,132 +10749,132 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.95</v>
+        <v>4.7</v>
       </c>
       <c r="G41" t="n">
-        <v>2.22</v>
+        <v>6.4</v>
       </c>
       <c r="H41" t="n">
-        <v>4.2</v>
+        <v>1.51</v>
       </c>
       <c r="I41" t="n">
-        <v>5.5</v>
+        <v>1.63</v>
       </c>
       <c r="J41" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="K41" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="L41" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="M41" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="O41" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="P41" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.38</v>
+        <v>1.47</v>
       </c>
       <c r="R41" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="S41" t="n">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="T41" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="U41" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="V41" t="n">
-        <v>1.22</v>
+        <v>2.58</v>
       </c>
       <c r="W41" t="n">
-        <v>1.81</v>
+        <v>1.18</v>
       </c>
       <c r="X41" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="Y41" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC41" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z41" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH41" t="n">
         <v>23</v>
       </c>
-      <c r="AE41" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>27</v>
-      </c>
       <c r="AI41" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="AJ41" t="n">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="AK41" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL41" t="n">
         <v>65</v>
       </c>
       <c r="AM41" t="n">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="AN41" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AO41" t="n">
-        <v>140</v>
+        <v>6.6</v>
       </c>
       <c r="AP41" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR41" t="n">
         <v>1.01</v>
@@ -10883,100 +10883,100 @@
         <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU41" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV41" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW41" t="n">
         <v>1.01</v>
       </c>
       <c r="AX41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>95</v>
+      </c>
+      <c r="BM41" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY41" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM41" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP41" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR41" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT41" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV41" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX41" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,14 +10986,14 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11003,72 +11003,72 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G42" t="n">
-        <v>600</v>
+        <v>2.3</v>
       </c>
       <c r="H42" t="n">
-        <v>1.09</v>
+        <v>3.9</v>
       </c>
       <c r="I42" t="n">
-        <v>990</v>
+        <v>4.6</v>
       </c>
       <c r="J42" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K42" t="n">
-        <v>500</v>
+        <v>3.55</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>1.24</v>
+        <v>2.52</v>
       </c>
       <c r="O42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R42" t="n">
         <v>1.2</v>
       </c>
-      <c r="P42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S42" t="n">
-        <v>1.2</v>
+        <v>3.85</v>
       </c>
       <c r="T42" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U42" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -11185,7 +11185,7 @@
         <v>1.04</v>
       </c>
       <c r="BJ42" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK42" t="n">
         <v>1.04</v>
@@ -11197,31 +11197,31 @@
         <v>1.04</v>
       </c>
       <c r="BN42" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ42" t="n">
         <v>1.04</v>
       </c>
       <c r="BR42" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS42" t="n">
         <v>1.04</v>
       </c>
       <c r="BT42" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV42" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW42" t="n">
         <v>1.04</v>
@@ -11233,21 +11233,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ42" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA42" t="n">
         <v>1.04</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-16 23:37:16</t>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11257,244 +11257,1260 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Limeira</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>2.22</v>
       </c>
       <c r="G43" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H43" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I43" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J43" t="n">
         <v>3</v>
       </c>
       <c r="K43" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X43" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>250</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO43" t="n">
         <v>3.8</v>
       </c>
-      <c r="L43" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N43" t="n">
+      <c r="BP43" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB43" t="inlineStr">
+        <is>
+          <t>2026-05-17 02:09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G44" t="n">
+        <v>600</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I44" t="n">
+        <v>990</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>500</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB44" t="inlineStr">
+        <is>
+          <t>2026-05-17 02:09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Confianca</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Maranhao</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q45" t="n">
         <v>2.38</v>
       </c>
-      <c r="O43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P43" t="n">
+      <c r="R45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X45" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB45" t="inlineStr">
+        <is>
+          <t>2026-05-17 02:09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Inter Limeira</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P46" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q46" t="n">
         <v>2.2</v>
       </c>
-      <c r="R43" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S43" t="n">
+      <c r="R46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH46" t="n">
         <v>3.2</v>
       </c>
-      <c r="T43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W43" t="n">
+      <c r="BI46" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>200</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>48</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB46" t="inlineStr">
+        <is>
+          <t>2026-05-17 02:09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Guayaquil City</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P47" t="n">
         <v>1.61</v>
       </c>
-      <c r="X43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB43" t="inlineStr">
-        <is>
-          <t>2026-05-16 23:37:16</t>
+      <c r="Q47" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X47" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU47" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>48</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB47" t="inlineStr">
+        <is>
+          <t>2026-05-17 02:09:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -869,40 +869,40 @@
         <v>1.68</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
         <v>2.46</v>
@@ -935,7 +935,7 @@
         <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG2" t="n">
         <v>30</v>
@@ -944,22 +944,22 @@
         <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AK2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AO2" t="n">
         <v>11</v>
@@ -1019,10 +1019,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ2" t="n">
         <v>12.5</v>
@@ -1031,7 +1031,7 @@
         <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BM2" t="n">
         <v>1.04</v>
@@ -1067,20 +1067,20 @@
         <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY2" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA2" t="n">
         <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -1132,19 +1132,19 @@
         <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
         <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
         <v>1.25</v>
@@ -1165,7 +1165,7 @@
         <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
         <v>6.6</v>
@@ -1270,7 +1270,7 @@
         <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="G4" t="n">
         <v>9.199999999999999</v>
@@ -1374,13 +1374,13 @@
         <v>1.47</v>
       </c>
       <c r="I4" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.28</v>
@@ -1389,10 +1389,10 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
         <v>2.06</v>
@@ -1407,16 +1407,16 @@
         <v>2.74</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
         <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
         <v>24</v>
@@ -1428,7 +1428,7 @@
         <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AB4" t="n">
         <v>32</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -1628,10 +1628,10 @@
         <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="K5" t="n">
         <v>3.05</v>
@@ -1643,28 +1643,28 @@
         <v>1.16</v>
       </c>
       <c r="N5" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.69</v>
       </c>
       <c r="P5" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" t="n">
         <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V5" t="n">
         <v>1.17</v>
@@ -1685,7 +1685,7 @@
         <v>300</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC5" t="n">
         <v>7.4</v>
@@ -1700,7 +1700,7 @@
         <v>10.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
         <v>34</v>
@@ -1709,7 +1709,7 @@
         <v>250</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK5" t="n">
         <v>36</v>
@@ -1727,28 +1727,28 @@
         <v>430</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
         <v>5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
         <v>8.6</v>
@@ -1757,28 +1757,28 @@
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="H6" t="n">
         <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
         <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
         <v>2.34</v>
@@ -1921,10 +1921,10 @@
         <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
         <v>12</v>
@@ -2035,16 +2035,16 @@
         <v>5.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ6" t="n">
         <v>14</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BL6" t="n">
         <v>240</v>
@@ -2053,16 +2053,16 @@
         <v>4.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BR6" t="n">
         <v>44</v>
@@ -2071,16 +2071,16 @@
         <v>4.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU6" t="n">
         <v>3.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX6" t="n">
         <v>85</v>
@@ -2089,14 +2089,14 @@
         <v>4.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>2.42</v>
       </c>
       <c r="G7" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H7" t="n">
         <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -2145,7 +2145,7 @@
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
@@ -2175,10 +2175,10 @@
         <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X7" t="n">
         <v>13</v>
@@ -2292,13 +2292,13 @@
         <v>3.45</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BL7" t="n">
         <v>190</v>
@@ -2313,7 +2313,7 @@
         <v>4</v>
       </c>
       <c r="BP7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.1</v>
@@ -2322,7 +2322,7 @@
         <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT7" t="n">
         <v>7.6</v>
@@ -2343,14 +2343,14 @@
         <v>4.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA7" t="n">
         <v>4.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8" t="n">
         <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J9" t="n">
         <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.32</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="O10" t="n">
         <v>1.31</v>
@@ -2931,16 +2931,16 @@
         <v>2.96</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -3146,19 +3146,19 @@
         <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H11" t="n">
         <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J11" t="n">
         <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="I12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.39</v>
@@ -3430,25 +3430,25 @@
         <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R12" t="n">
         <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V12" t="n">
         <v>2.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>16</v>
@@ -3466,7 +3466,7 @@
         <v>22</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
         <v>12.5</v>
@@ -3505,61 +3505,61 @@
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AT12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU12" t="n">
         <v>3.45</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.55</v>
+        <v>8.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX12" t="n">
         <v>4.6</v>
       </c>
       <c r="AY12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.1</v>
       </c>
       <c r="BA12" t="n">
         <v>4.5</v>
       </c>
       <c r="BB12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC12" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC12" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI12" t="n">
         <v>2.74</v>
@@ -3577,34 +3577,34 @@
         <v>4.7</v>
       </c>
       <c r="BN12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BQ12" t="n">
         <v>4.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BS12" t="n">
         <v>4.6</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BV12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BW12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BX12" t="n">
         <v>34</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H13" t="n">
-        <v>2.86</v>
+        <v>3.65</v>
       </c>
       <c r="I13" t="n">
         <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
         <v>630</v>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O13" t="n">
         <v>1.36</v>
@@ -3684,7 +3684,7 @@
         <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R13" t="n">
         <v>1.2</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G14" t="n">
         <v>2.84</v>
@@ -3932,7 +3932,7 @@
         <v>2.92</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P14" t="n">
         <v>1.65</v>
@@ -3944,7 +3944,7 @@
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T14" t="n">
         <v>1.75</v>
@@ -3965,7 +3965,7 @@
         <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA14" t="n">
         <v>75</v>
@@ -4007,7 +4007,7 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO14" t="n">
         <v>60</v>
@@ -4019,7 +4019,7 @@
         <v>7.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AS14" t="n">
         <v>4.1</v>
@@ -4070,19 +4070,19 @@
         <v>3.45</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ14" t="n">
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="BL14" t="n">
         <v>190</v>
       </c>
       <c r="BM14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN14" t="n">
         <v>6.4</v>
@@ -4091,13 +4091,13 @@
         <v>4.1</v>
       </c>
       <c r="BP14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ14" t="n">
         <v>4.1</v>
       </c>
       <c r="BR14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS14" t="n">
         <v>4.4</v>
@@ -4112,13 +4112,13 @@
         <v>34</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX14" t="n">
         <v>55</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>46</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
         <v>1.77</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
         <v>7.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.31</v>
@@ -4201,16 +4201,16 @@
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V15" t="n">
         <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X15" t="n">
         <v>20</v>
@@ -4252,7 +4252,7 @@
         <v>21</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
         <v>42</v>
@@ -4270,10 +4270,10 @@
         <v>3.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS15" t="n">
         <v>4.3</v>
@@ -4282,13 +4282,13 @@
         <v>3.15</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX15" t="n">
         <v>3.25</v>
@@ -4309,10 +4309,10 @@
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF15" t="n">
         <v>7.4</v>
@@ -4321,7 +4321,7 @@
         <v>4.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI15" t="n">
         <v>2.88</v>
@@ -4330,16 +4330,16 @@
         <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BM15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO15" t="n">
         <v>3.35</v>
@@ -4348,41 +4348,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BR15" t="n">
         <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BT15" t="n">
         <v>11</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BV15" t="n">
         <v>60</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX15" t="n">
         <v>65</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>24</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -4422,10 +4422,10 @@
         <v>1.95</v>
       </c>
       <c r="I16" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
         <v>3.95</v>
@@ -4443,37 +4443,37 @@
         <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
         <v>1.3</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="n">
         <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA16" t="n">
         <v>24</v>
@@ -4482,7 +4482,7 @@
         <v>18.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>11</v>
@@ -4494,16 +4494,16 @@
         <v>34</v>
       </c>
       <c r="AG16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
         <v>34</v>
       </c>
       <c r="AJ16" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="n">
         <v>55</v>
@@ -4512,67 +4512,67 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
         <v>48</v>
       </c>
       <c r="AO16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AR16" t="n">
         <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.8</v>
+        <v>16.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY16" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4581,7 +4581,7 @@
         <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK16" t="n">
         <v>1.04</v>
@@ -4617,7 +4617,7 @@
         <v>3.2</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW16" t="n">
         <v>1.04</v>
@@ -4629,14 +4629,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA16" t="n">
         <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -4670,22 +4670,22 @@
         <v>3.25</v>
       </c>
       <c r="G17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H17" t="n">
         <v>2.22</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -4703,19 +4703,19 @@
         <v>1.92</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W17" t="n">
         <v>1.37</v>
@@ -4778,7 +4778,7 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17" t="n">
         <v>11.5</v>
@@ -4793,7 +4793,7 @@
         <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW17" t="n">
         <v>19</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
         <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -5453,13 +5453,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="O20" t="n">
         <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q20" t="n">
         <v>1.22</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G21" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K21" t="n">
         <v>4.7</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.8</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5713,28 +5713,28 @@
         <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
         <v>1.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U21" t="n">
         <v>2.24</v>
       </c>
       <c r="V21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W21" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="X21" t="n">
         <v>25</v>
@@ -5767,7 +5767,7 @@
         <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI21" t="n">
         <v>60</v>
@@ -5797,10 +5797,10 @@
         <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT21" t="n">
         <v>9</v>
@@ -5812,7 +5812,7 @@
         <v>15.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -5824,7 +5824,7 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB21" t="n">
         <v>15.5</v>
@@ -5833,7 +5833,7 @@
         <v>14.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE21" t="n">
         <v>6.2</v>
@@ -5842,7 +5842,7 @@
         <v>7</v>
       </c>
       <c r="BG21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G22" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -5952,7 +5952,7 @@
         <v>3.9</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5961,34 +5961,34 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
         <v>1.23</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="T22" t="n">
         <v>1.61</v>
       </c>
       <c r="U22" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V22" t="n">
         <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X22" t="n">
         <v>22</v>
@@ -5997,7 +5997,7 @@
         <v>16.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA22" t="n">
         <v>60</v>
@@ -6006,13 +6006,13 @@
         <v>14</v>
       </c>
       <c r="AC22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF22" t="n">
         <v>22</v>
@@ -6030,7 +6030,7 @@
         <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
         <v>50</v>
@@ -6042,28 +6042,28 @@
         <v>16</v>
       </c>
       <c r="AO22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP22" t="n">
         <v>18</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR22" t="n">
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
         <v>19</v>
@@ -6087,10 +6087,10 @@
         <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF22" t="n">
         <v>12.5</v>
@@ -6102,7 +6102,7 @@
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BJ22" t="n">
         <v>12.5</v>
@@ -6114,7 +6114,7 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BN22" t="n">
         <v>7.8</v>
@@ -6126,13 +6126,13 @@
         <v>23</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="BR22" t="n">
         <v>36</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="BT22" t="n">
         <v>9.199999999999999</v>
@@ -6144,23 +6144,23 @@
         <v>30</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BX22" t="n">
         <v>44</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="BZ22" t="n">
         <v>28</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -6191,25 +6191,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G23" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H23" t="n">
         <v>4.6</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="n">
         <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -6218,31 +6218,31 @@
         <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P23" t="n">
         <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R23" t="n">
         <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
         <v>1.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X23" t="n">
         <v>16.5</v>
@@ -6284,7 +6284,7 @@
         <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
         <v>44</v>
@@ -6368,7 +6368,7 @@
         <v>160</v>
       </c>
       <c r="BM23" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN23" t="n">
         <v>5</v>
@@ -6380,10 +6380,10 @@
         <v>15</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BR23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS23" t="n">
         <v>4.9</v>
@@ -6392,19 +6392,19 @@
         <v>9.4</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV23" t="n">
         <v>50</v>
       </c>
       <c r="BW23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BX23" t="n">
         <v>60</v>
       </c>
       <c r="BY23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BZ23" t="n">
         <v>28</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
         <v>2.44</v>
       </c>
       <c r="H24" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="I24" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J24" t="n">
         <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
         <v>1.33</v>
@@ -6472,7 +6472,7 @@
         <v>3.95</v>
       </c>
       <c r="O24" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P24" t="n">
         <v>2.02</v>
@@ -6484,7 +6484,7 @@
         <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
         <v>1.68</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV24" t="n">
         <v>26</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G25" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I25" t="n">
         <v>3.95</v>
@@ -6732,7 +6732,7 @@
         <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
@@ -6741,10 +6741,10 @@
         <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U25" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="V25" t="n">
         <v>1.34</v>
@@ -6756,7 +6756,7 @@
         <v>13</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z25" t="n">
         <v>28</v>
@@ -6813,7 +6813,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS25" t="n">
         <v>1.01</v>
@@ -6837,7 +6837,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
         <v>1.01</v>
@@ -6855,7 +6855,7 @@
         <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G26" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H26" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="I26" t="n">
         <v>2</v>
@@ -6968,43 +6968,43 @@
         <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
         <v>1.71</v>
       </c>
       <c r="R26" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T26" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="V26" t="n">
         <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="n">
         <v>23</v>
@@ -7040,25 +7040,25 @@
         <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ26" t="n">
         <v>100</v>
       </c>
       <c r="AK26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL26" t="n">
         <v>60</v>
       </c>
-      <c r="AL26" t="n">
-        <v>65</v>
-      </c>
       <c r="AM26" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP26" t="n">
         <v>14</v>
@@ -7067,7 +7067,7 @@
         <v>8</v>
       </c>
       <c r="AR26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS26" t="n">
         <v>15.5</v>
@@ -7076,7 +7076,7 @@
         <v>13</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
         <v>7.8</v>
@@ -7115,22 +7115,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ26" t="n">
         <v>11</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL26" t="n">
         <v>120</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN26" t="n">
         <v>9.199999999999999</v>
@@ -7139,19 +7139,19 @@
         <v>5.8</v>
       </c>
       <c r="BP26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR26" t="n">
         <v>46</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT26" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU26" t="n">
         <v>3.75</v>
@@ -7160,23 +7160,23 @@
         <v>15.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BX26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BZ26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -7207,37 +7207,37 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="H27" t="n">
         <v>2.72</v>
       </c>
       <c r="I27" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="J27" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
         <v>1.66</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
-        <v>1.82</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Q27" t="n">
         <v>3.55</v>
@@ -7246,127 +7246,127 @@
         <v>1.12</v>
       </c>
       <c r="S27" t="n">
-        <v>7.8</v>
+        <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="V27" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W27" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G28" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="H28" t="n">
         <v>3.8</v>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
         <v>2.84</v>
       </c>
       <c r="K28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L28" t="n">
         <v>1.61</v>
@@ -7485,13 +7485,13 @@
         <v>1.14</v>
       </c>
       <c r="N28" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
         <v>1.6</v>
       </c>
       <c r="P28" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q28" t="n">
         <v>2.88</v>
@@ -7512,7 +7512,7 @@
         <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X28" t="n">
         <v>8.6</v>
@@ -7542,7 +7542,7 @@
         <v>15.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH28" t="n">
         <v>30</v>
@@ -7551,7 +7551,7 @@
         <v>120</v>
       </c>
       <c r="AJ28" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK28" t="n">
         <v>44</v>
@@ -7563,13 +7563,13 @@
         <v>270</v>
       </c>
       <c r="AN28" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO28" t="n">
         <v>140</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>8.4</v>
@@ -7578,7 +7578,7 @@
         <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT28" t="n">
         <v>5.9</v>
@@ -7590,7 +7590,7 @@
         <v>13.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX28" t="n">
         <v>10.5</v>
@@ -7602,25 +7602,25 @@
         <v>19.5</v>
       </c>
       <c r="BA28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD28" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5</v>
-      </c>
       <c r="BE28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG28" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>5.1</v>
       </c>
       <c r="BH28" t="n">
         <v>2.8</v>
@@ -7638,10 +7638,10 @@
         <v>290</v>
       </c>
       <c r="BM28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BN28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO28" t="n">
         <v>3.95</v>
@@ -7650,13 +7650,13 @@
         <v>25</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR28" t="n">
         <v>60</v>
       </c>
       <c r="BS28" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BT28" t="n">
         <v>8</v>
@@ -7668,23 +7668,23 @@
         <v>50</v>
       </c>
       <c r="BW28" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX28" t="n">
         <v>80</v>
       </c>
       <c r="BY28" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BZ28" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="CA28" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,40 +7739,40 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
         <v>1.29</v>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R29" t="n">
         <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T29" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="U29" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="V29" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W29" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X29" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y29" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z29" t="n">
         <v>38</v>
@@ -7793,7 +7793,7 @@
         <v>60</v>
       </c>
       <c r="AF29" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG29" t="n">
         <v>13</v>
@@ -7802,22 +7802,22 @@
         <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK29" t="n">
         <v>26</v>
       </c>
       <c r="AL29" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM29" t="n">
         <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO29" t="n">
         <v>60</v>
@@ -7826,43 +7826,43 @@
         <v>11.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.8</v>
+        <v>21</v>
       </c>
       <c r="AS29" t="n">
         <v>4</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV29" t="n">
         <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ29" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD29" t="n">
         <v>3.8</v>
@@ -7871,10 +7871,10 @@
         <v>4</v>
       </c>
       <c r="BF29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BH29" t="n">
         <v>1000</v>
@@ -7898,7 +7898,7 @@
         <v>6.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP29" t="n">
         <v>20</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -7969,61 +7969,61 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G30" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="I30" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K30" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O30" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P30" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R30" t="n">
         <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T30" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U30" t="n">
         <v>2.06</v>
       </c>
       <c r="V30" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W30" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X30" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="n">
         <v>12</v>
@@ -8089,7 +8089,7 @@
         <v>4.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU30" t="n">
         <v>7</v>
@@ -8104,10 +8104,10 @@
         <v>17.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA30" t="n">
         <v>4.5</v>
@@ -8125,46 +8125,46 @@
         <v>4.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG30" t="n">
         <v>14.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BJ30" t="n">
         <v>11.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BL30" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BM30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BN30" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT30" t="n">
         <v>6.4</v>
@@ -8173,26 +8173,26 @@
         <v>4.1</v>
       </c>
       <c r="BV30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW30" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BX30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BZ30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA30" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G31" t="n">
         <v>1.63</v>
@@ -8235,7 +8235,7 @@
         <v>8.4</v>
       </c>
       <c r="J31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
         <v>4.2</v>
@@ -8247,22 +8247,22 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P31" t="n">
         <v>1.73</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S31" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
         <v>2</v>
@@ -8271,7 +8271,7 @@
         <v>1.62</v>
       </c>
       <c r="V31" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W31" t="n">
         <v>2.58</v>
@@ -8286,103 +8286,103 @@
         <v>60</v>
       </c>
       <c r="AA31" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
         <v>970</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE31" t="n">
         <v>140</v>
       </c>
       <c r="AF31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG31" t="n">
         <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
         <v>20</v>
       </c>
       <c r="AL31" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN31" t="n">
         <v>13</v>
       </c>
       <c r="AO31" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.6</v>
+        <v>2.56</v>
       </c>
       <c r="AQ31" t="n">
         <v>16</v>
       </c>
       <c r="AR31" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AT31" t="n">
         <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AV31" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW31" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AY31" t="n">
         <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="BA31" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BB31" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BG31" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G32" t="n">
         <v>1.28</v>
       </c>
       <c r="H32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="J32" t="n">
         <v>6.4</v>
       </c>
       <c r="K32" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L32" t="n">
         <v>1.22</v>
@@ -8501,28 +8501,28 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
         <v>1.16</v>
       </c>
       <c r="P32" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q32" t="n">
         <v>1.48</v>
       </c>
       <c r="R32" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S32" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T32" t="n">
         <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V32" t="n">
         <v>1.06</v>
@@ -8570,7 +8570,7 @@
         <v>11</v>
       </c>
       <c r="AK32" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL32" t="n">
         <v>44</v>
@@ -8582,19 +8582,19 @@
         <v>4.3</v>
       </c>
       <c r="AO32" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT32" t="n">
         <v>9.199999999999999</v>
@@ -8603,10 +8603,10 @@
         <v>14</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX32" t="n">
         <v>7.4</v>
@@ -8615,92 +8615,92 @@
         <v>10</v>
       </c>
       <c r="AZ32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB32" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC32" t="n">
         <v>12</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF32" t="n">
         <v>3.2</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI32" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK32" t="n">
         <v>4.1</v>
       </c>
       <c r="BL32" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BM32" t="n">
         <v>5.5</v>
       </c>
       <c r="BN32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP32" t="n">
         <v>7.6</v>
       </c>
       <c r="BQ32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR32" t="n">
         <v>25</v>
       </c>
       <c r="BS32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT32" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BU32" t="n">
         <v>4.4</v>
       </c>
       <c r="BV32" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BW32" t="n">
         <v>5.5</v>
       </c>
       <c r="BX32" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BY32" t="n">
         <v>5.4</v>
       </c>
       <c r="BZ32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA32" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -8731,61 +8731,61 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G33" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H33" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K33" t="n">
         <v>3.9</v>
       </c>
-      <c r="J33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L33" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
         <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P33" t="n">
         <v>1.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="R33" t="n">
         <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T33" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="U33" t="n">
         <v>1.96</v>
       </c>
       <c r="V33" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="X33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y33" t="n">
         <v>13</v>
@@ -8893,10 +8893,10 @@
         <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BJ33" t="n">
         <v>11.5</v>
@@ -8923,7 +8923,7 @@
         <v>4.6</v>
       </c>
       <c r="BR33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS33" t="n">
         <v>5.1</v>
@@ -8932,7 +8932,7 @@
         <v>7.6</v>
       </c>
       <c r="BU33" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV33" t="n">
         <v>36</v>
@@ -8941,20 +8941,20 @@
         <v>5</v>
       </c>
       <c r="BX33" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY33" t="n">
         <v>5.3</v>
       </c>
       <c r="BZ33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
         <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -9263,28 +9263,28 @@
         <v>1.07</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="O35" t="n">
         <v>1.33</v>
       </c>
       <c r="P35" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R35" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S35" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T35" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U35" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V35" t="n">
         <v>1.31</v>
@@ -9308,16 +9308,16 @@
         <v>9.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD35" t="n">
         <v>17</v>
       </c>
       <c r="AE35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF35" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG35" t="n">
         <v>10.5</v>
@@ -9338,7 +9338,7 @@
         <v>38</v>
       </c>
       <c r="AM35" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN35" t="n">
         <v>16</v>
@@ -9347,7 +9347,7 @@
         <v>55</v>
       </c>
       <c r="AP35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ35" t="n">
         <v>13</v>
@@ -9356,10 +9356,10 @@
         <v>26</v>
       </c>
       <c r="AS35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT35" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU35" t="n">
         <v>7.4</v>
@@ -9368,7 +9368,7 @@
         <v>14.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX35" t="n">
         <v>11</v>
@@ -9380,7 +9380,7 @@
         <v>16.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB35" t="n">
         <v>22</v>
@@ -9392,13 +9392,13 @@
         <v>32</v>
       </c>
       <c r="BE35" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF35" t="n">
         <v>13.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>3.3</v>
       </c>
       <c r="H36" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I36" t="n">
         <v>3.05</v>
@@ -9508,7 +9508,7 @@
         <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9529,16 +9529,16 @@
         <v>1.58</v>
       </c>
       <c r="R36" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S36" t="n">
         <v>2.5</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V36" t="n">
         <v>1.49</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -9753,10 +9753,10 @@
         <v>1.12</v>
       </c>
       <c r="H37" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J37" t="n">
         <v>14</v>
@@ -9789,7 +9789,7 @@
         <v>1.93</v>
       </c>
       <c r="T37" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="U37" t="n">
         <v>1.56</v>
@@ -9798,7 +9798,7 @@
         <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="X37" t="n">
         <v>44</v>
@@ -9837,7 +9837,7 @@
         <v>470</v>
       </c>
       <c r="AJ37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AK37" t="n">
         <v>15</v>
@@ -9858,13 +9858,13 @@
         <v>40</v>
       </c>
       <c r="AQ37" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AR37" t="n">
         <v>120</v>
       </c>
       <c r="AS37" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AT37" t="n">
         <v>13.5</v>
@@ -9873,10 +9873,10 @@
         <v>30</v>
       </c>
       <c r="AV37" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AW37" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AX37" t="n">
         <v>7.6</v>
@@ -9894,10 +9894,10 @@
         <v>6.6</v>
       </c>
       <c r="BC37" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE37" t="n">
         <v>100</v>
@@ -9906,7 +9906,7 @@
         <v>2.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="BH37" t="n">
         <v>7</v>
@@ -9954,13 +9954,13 @@
         <v>330</v>
       </c>
       <c r="BW37" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BX37" t="n">
         <v>220</v>
       </c>
       <c r="BY37" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BZ37" t="n">
         <v>6.6</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -10001,46 +10001,46 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="G38" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I38" t="n">
         <v>2.94</v>
       </c>
-      <c r="H38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2.84</v>
-      </c>
       <c r="J38" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K38" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N38" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="O38" t="n">
         <v>1.15</v>
       </c>
       <c r="P38" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R38" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S38" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -10049,10 +10049,10 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W38" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -10255,67 +10255,67 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G39" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="I39" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="J39" t="n">
         <v>4.4</v>
       </c>
       <c r="K39" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="L39" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N39" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="O39" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P39" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="R39" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="S39" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V39" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="X39" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y39" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
@@ -10324,31 +10324,31 @@
         <v>16</v>
       </c>
       <c r="AC39" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF39" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH39" t="n">
         <v>24</v>
       </c>
       <c r="AI39" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL39" t="n">
         <v>30</v>
@@ -10357,13 +10357,13 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP39" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.01</v>
@@ -10375,43 +10375,43 @@
         <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
         <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
         <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
         <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BG39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -10512,16 +10512,16 @@
         <v>1.04</v>
       </c>
       <c r="G40" t="n">
-        <v>1.71</v>
+        <v>180</v>
       </c>
       <c r="H40" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="J40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K40" t="n">
         <v>1000</v>
@@ -10530,25 +10530,25 @@
         <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N40" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="O40" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P40" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.14</v>
+        <v>1.46</v>
       </c>
       <c r="R40" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S40" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -10557,10 +10557,10 @@
         <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G41" t="n">
         <v>6.4</v>
@@ -10784,22 +10784,22 @@
         <v>1.23</v>
       </c>
       <c r="M41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N41" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="O41" t="n">
         <v>1.16</v>
       </c>
       <c r="P41" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="Q41" t="n">
         <v>1.47</v>
       </c>
       <c r="R41" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S41" t="n">
         <v>2.08</v>
@@ -10808,7 +10808,7 @@
         <v>1.63</v>
       </c>
       <c r="U41" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V41" t="n">
         <v>2.58</v>
@@ -10868,7 +10868,7 @@
         <v>60</v>
       </c>
       <c r="AO41" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP41" t="n">
         <v>1.01</v>
@@ -10940,7 +10940,7 @@
         <v>95</v>
       </c>
       <c r="BM41" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN41" t="n">
         <v>11.5</v>
@@ -10973,7 +10973,7 @@
         <v>1.01</v>
       </c>
       <c r="BX41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -11026,221 +11026,221 @@
         <v>3.9</v>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J42" t="n">
         <v>3.1</v>
       </c>
       <c r="K42" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L42" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M42" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="O42" t="n">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="P42" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q42" t="n">
         <v>2.28</v>
       </c>
       <c r="R42" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S42" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="U42" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="V42" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W42" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BH42" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BJ42" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BK42" t="n">
         <v>1.04</v>
       </c>
       <c r="BL42" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM42" t="n">
         <v>1.04</v>
       </c>
       <c r="BN42" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BP42" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BQ42" t="n">
         <v>1.04</v>
       </c>
       <c r="BR42" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BS42" t="n">
         <v>1.04</v>
       </c>
       <c r="BT42" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU42" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV42" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BW42" t="n">
         <v>1.04</v>
       </c>
       <c r="BX42" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY42" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ42" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="CA42" t="n">
         <v>1.04</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
         <v>2.22</v>
       </c>
       <c r="G43" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H43" t="n">
         <v>3.75</v>
@@ -11289,19 +11289,19 @@
         <v>3.35</v>
       </c>
       <c r="L43" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M43" t="n">
         <v>1.12</v>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="O43" t="n">
         <v>1.51</v>
       </c>
       <c r="P43" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q43" t="n">
         <v>2.52</v>
@@ -11316,13 +11316,13 @@
         <v>2.08</v>
       </c>
       <c r="U43" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="V43" t="n">
         <v>1.31</v>
       </c>
       <c r="W43" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="X43" t="n">
         <v>9.199999999999999</v>
@@ -11358,7 +11358,7 @@
         <v>28</v>
       </c>
       <c r="AI43" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ43" t="n">
         <v>40</v>
@@ -11424,7 +11424,7 @@
         <v>5.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF43" t="n">
         <v>5.3</v>
@@ -11433,10 +11433,10 @@
         <v>5.8</v>
       </c>
       <c r="BH43" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ43" t="n">
         <v>13.5</v>
@@ -11445,31 +11445,31 @@
         <v>3.65</v>
       </c>
       <c r="BL43" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="BM43" t="n">
         <v>4.9</v>
       </c>
       <c r="BN43" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO43" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP43" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ43" t="n">
         <v>4.1</v>
       </c>
       <c r="BR43" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS43" t="n">
         <v>4.6</v>
       </c>
       <c r="BT43" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU43" t="n">
         <v>5.2</v>
@@ -11481,7 +11481,7 @@
         <v>4.5</v>
       </c>
       <c r="BX43" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY43" t="n">
         <v>4.7</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -11525,13 +11525,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="G44" t="n">
         <v>600</v>
       </c>
       <c r="H44" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="I44" t="n">
         <v>990</v>
@@ -11549,7 +11549,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O44" t="n">
         <v>1.2</v>
@@ -11564,7 +11564,7 @@
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="T44" t="n">
         <v>1.11</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -11785,10 +11785,10 @@
         <v>2.22</v>
       </c>
       <c r="H45" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I45" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J45" t="n">
         <v>3.05</v>
@@ -11806,7 +11806,7 @@
         <v>2.68</v>
       </c>
       <c r="O45" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P45" t="n">
         <v>1.57</v>
@@ -11830,7 +11830,7 @@
         <v>1.23</v>
       </c>
       <c r="W45" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X45" t="n">
         <v>11</v>
@@ -11887,10 +11887,10 @@
         <v>140</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR45" t="n">
         <v>1.01</v>
@@ -11899,34 +11899,34 @@
         <v>1.01</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW45" t="n">
         <v>1.01</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA45" t="n">
         <v>1.01</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD45" t="n">
         <v>1.01</v>
@@ -11935,7 +11935,7 @@
         <v>1.01</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -12033,25 +12033,25 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G46" t="n">
         <v>2.56</v>
       </c>
       <c r="H46" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J46" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L46" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="M46" t="n">
         <v>1.1</v>
@@ -12066,7 +12066,7 @@
         <v>1.6</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="R46" t="n">
         <v>1.22</v>
@@ -12081,7 +12081,7 @@
         <v>1.84</v>
       </c>
       <c r="V46" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W46" t="n">
         <v>1.65</v>
@@ -12204,34 +12204,34 @@
         <v>12.5</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL46" t="n">
         <v>200</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BN46" t="n">
         <v>5.6</v>
       </c>
       <c r="BO46" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR46" t="n">
         <v>46</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT46" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU46" t="n">
         <v>5.3</v>
@@ -12240,23 +12240,23 @@
         <v>40</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BX46" t="n">
         <v>60</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ46" t="n">
         <v>48</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>
@@ -12287,10 +12287,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G47" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H47" t="n">
         <v>2.56</v>
@@ -12311,10 +12311,10 @@
         <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O47" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P47" t="n">
         <v>1.61</v>
@@ -12323,19 +12323,19 @@
         <v>2.32</v>
       </c>
       <c r="R47" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S47" t="n">
         <v>4.1</v>
       </c>
       <c r="T47" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U47" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V47" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
         <v>1.4</v>
@@ -12350,7 +12350,7 @@
         <v>970</v>
       </c>
       <c r="AA47" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB47" t="n">
         <v>970</v>
@@ -12362,7 +12362,7 @@
         <v>970</v>
       </c>
       <c r="AE47" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF47" t="n">
         <v>24</v>
@@ -12404,7 +12404,7 @@
         <v>3.95</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT47" t="n">
         <v>8</v>
@@ -12413,40 +12413,40 @@
         <v>5.7</v>
       </c>
       <c r="AV47" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY47" t="n">
         <v>3.8</v>
       </c>
-      <c r="AW47" t="n">
+      <c r="AZ47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC47" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB47" t="n">
+      <c r="BD47" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE47" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC47" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BF47" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG47" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH47" t="n">
         <v>3.25</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-17 02:09:00</t>
+          <t>2026-05-17 04:40:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -857,31 +857,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="I2" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.31</v>
@@ -890,25 +890,25 @@
         <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
         <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
         <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
@@ -923,7 +923,7 @@
         <v>17.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
@@ -941,13 +941,13 @@
         <v>950</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
         <v>38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AK2" t="n">
         <v>120</v>
@@ -980,46 +980,46 @@
         <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AW2" t="n">
         <v>14.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.1</v>
+        <v>19</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC2" t="n">
         <v>6</v>
       </c>
-      <c r="BC2" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BI2" t="n">
         <v>2.94</v>
@@ -1055,10 +1055,10 @@
         <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BV2" t="n">
         <v>11.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -1126,10 +1126,10 @@
         <v>3.85</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1273,68 +1273,68 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK3" t="n">
         <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM3" t="n">
         <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BO3" t="n">
         <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BQ3" t="n">
         <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BS3" t="n">
         <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
         <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA3" t="n">
         <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>3.05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="M5" t="n">
         <v>1.16</v>
@@ -1646,7 +1646,7 @@
         <v>2.28</v>
       </c>
       <c r="O5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P5" t="n">
         <v>1.4</v>
@@ -1781,68 +1781,68 @@
         <v>7.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK5" t="n">
         <v>1.04</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="BM5" t="n">
         <v>1.04</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.04</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS5" t="n">
         <v>1.04</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU5" t="n">
         <v>1.04</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW5" t="n">
         <v>1.04</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BY5" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA5" t="n">
         <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -2145,10 +2145,10 @@
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
         <v>3.1</v>
@@ -2157,7 +2157,7 @@
         <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
         <v>2.16</v>
@@ -2166,13 +2166,13 @@
         <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="V7" t="n">
         <v>1.72</v>
@@ -2181,91 +2181,91 @@
         <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
         <v>1.01</v>
@@ -2286,71 +2286,71 @@
         <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
         <v>3.55</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
@@ -2414,7 +2414,7 @@
         <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
         <v>1.27</v>
@@ -2423,16 +2423,16 @@
         <v>4.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U8" t="n">
         <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2450,7 +2450,7 @@
         <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
         <v>18.5</v>
@@ -2474,7 +2474,7 @@
         <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
@@ -2489,7 +2489,7 @@
         <v>65</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>9.800000000000001</v>
@@ -2507,7 +2507,7 @@
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW8" t="n">
         <v>25</v>
@@ -2528,16 +2528,16 @@
         <v>21</v>
       </c>
       <c r="BC8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD8" t="n">
         <v>28</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
         <v>28</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -2889,118 +2889,118 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.59</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>5.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="S10" t="n">
-        <v>1.13</v>
+        <v>2.16</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR10" t="n">
         <v>1.01</v>
@@ -3009,110 +3009,110 @@
         <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
         <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE10" t="n">
         <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -3143,145 +3143,145 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I11" t="n">
         <v>2.3</v>
       </c>
       <c r="J11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.35</v>
       </c>
-      <c r="K11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.82</v>
-      </c>
       <c r="O11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.31</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>3.55</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W11" t="n">
         <v>1.31</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA11" t="n">
         <v>1.01</v>
@@ -3302,58 +3302,58 @@
         <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
         <v>1.04</v>
       </c>
       <c r="BL11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM11" t="n">
         <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ11" t="n">
         <v>1.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS11" t="n">
         <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW11" t="n">
         <v>1.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY11" t="n">
         <v>1.04</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v>1.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -3654,10 +3654,10 @@
         <v>1.45</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.09</v>
+        <v>2.96</v>
       </c>
       <c r="I13" t="n">
         <v>10.5</v>
@@ -3666,7 +3666,7 @@
         <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>630</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3678,7 +3678,7 @@
         <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P13" t="n">
         <v>1.64</v>
@@ -3702,7 +3702,7 @@
         <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -3953,7 +3953,7 @@
         <v>1.78</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
         <v>1.54</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -4159,230 +4159,230 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="G15" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -4413,40 +4413,40 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="I16" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P16" t="n">
         <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
         <v>1.33</v>
@@ -4455,188 +4455,188 @@
         <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
         <v>15.5</v>
       </c>
       <c r="Y16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z16" t="n">
         <v>8</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AA16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AE16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF16" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AG16" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AH16" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI16" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ16" t="n">
+        <v>420</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN16" t="n">
         <v>260</v>
       </c>
-      <c r="AK16" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>170</v>
-      </c>
       <c r="AO16" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ16" t="n">
         <v>6.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AS16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BA16" t="n">
         <v>32</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BL16" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="BM16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BN16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BO16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>95</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BW16" t="n">
         <v>3.5</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>80</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>85</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>3.55</v>
       </c>
       <c r="BX16" t="n">
         <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CA16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -4924,22 +4924,22 @@
         <v>4.1</v>
       </c>
       <c r="G18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K18" t="n">
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -4969,10 +4969,10 @@
         <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X18" t="n">
         <v>23</v>
@@ -4987,7 +4987,7 @@
         <v>24</v>
       </c>
       <c r="AB18" t="n">
-        <v>18.5</v>
+        <v>950</v>
       </c>
       <c r="AC18" t="n">
         <v>9.199999999999999</v>
@@ -5002,10 +5002,10 @@
         <v>34</v>
       </c>
       <c r="AG18" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI18" t="n">
         <v>34</v>
@@ -5038,7 +5038,7 @@
         <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
         <v>15</v>
@@ -5053,28 +5053,28 @@
         <v>16.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY18" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
         <v>8.199999999999999</v>
@@ -5083,68 +5083,68 @@
         <v>9.6</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.66</v>
+        <v>3.35</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.91</v>
+        <v>4.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BR18" t="n">
         <v>48</v>
       </c>
-      <c r="BQ18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>55</v>
-      </c>
       <c r="BS18" t="n">
-        <v>1.84</v>
+        <v>4.3</v>
       </c>
       <c r="BT18" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.73</v>
+        <v>3.65</v>
       </c>
       <c r="BX18" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.81</v>
+        <v>4.1</v>
       </c>
       <c r="BZ18" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.78</v>
+        <v>3.95</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -5178,31 +5178,31 @@
         <v>3.25</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H19" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="I19" t="n">
         <v>2.48</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P19" t="n">
         <v>1.9</v>
@@ -5211,34 +5211,34 @@
         <v>1.92</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
         <v>1.36</v>
       </c>
       <c r="X19" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y19" t="n">
         <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB19" t="n">
         <v>15.5</v>
@@ -5256,10 +5256,10 @@
         <v>28</v>
       </c>
       <c r="AG19" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AI19" t="n">
         <v>44</v>
@@ -5277,61 +5277,61 @@
         <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO19" t="n">
         <v>22</v>
       </c>
       <c r="AP19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT19" t="n">
         <v>11</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>10</v>
       </c>
       <c r="AU19" t="n">
         <v>6.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG19" t="n">
         <v>14.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -5456,19 +5456,19 @@
         <v>1.32</v>
       </c>
       <c r="O20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
         <v>1.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
         <v>990</v>
       </c>
       <c r="J21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K21" t="n">
         <v>500</v>
@@ -5707,13 +5707,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="O21" t="n">
         <v>1.23</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q21" t="n">
         <v>1.23</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
         <v>3.95</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
@@ -6015,7 +6015,7 @@
         <v>50</v>
       </c>
       <c r="AF22" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG22" t="n">
         <v>12</v>
@@ -6033,19 +6033,19 @@
         <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
         <v>70</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>23</v>
       </c>
       <c r="AP22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>14</v>
@@ -6084,7 +6084,7 @@
         <v>21</v>
       </c>
       <c r="BC22" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD22" t="n">
         <v>19.5</v>
@@ -6099,68 +6099,68 @@
         <v>18</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.92</v>
+        <v>3.15</v>
       </c>
       <c r="BJ22" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="BL22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.92</v>
+        <v>4.4</v>
       </c>
       <c r="BN22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT22" t="n">
         <v>7.8</v>
       </c>
-      <c r="BO22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP22" t="n">
+      <c r="BU22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BZ22" t="n">
         <v>23</v>
       </c>
-      <c r="BQ22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>44</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>28</v>
-      </c>
       <c r="CA22" t="n">
-        <v>1.8</v>
+        <v>3.85</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -6191,58 +6191,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G23" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
         <v>4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W23" t="n">
         <v>2.28</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.3</v>
       </c>
       <c r="X23" t="n">
         <v>25</v>
@@ -6353,68 +6353,68 @@
         <v>6.2</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK23" t="n">
         <v>1.04</v>
       </c>
       <c r="BL23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM23" t="n">
         <v>1.04</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ23" t="n">
         <v>1.04</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS23" t="n">
         <v>1.04</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU23" t="n">
         <v>1.04</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW23" t="n">
         <v>1.04</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY23" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA23" t="n">
         <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G25" t="n">
         <v>1.96</v>
@@ -6708,7 +6708,7 @@
         <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>3.65</v>
@@ -6717,16 +6717,16 @@
         <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P25" t="n">
         <v>1.86</v>
@@ -6738,16 +6738,16 @@
         <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="U25" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W25" t="n">
         <v>2.04</v>
@@ -6807,7 +6807,7 @@
         <v>95</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.05</v>
+        <v>11</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.05</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>2.24</v>
       </c>
       <c r="G26" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H26" t="n">
         <v>3.4</v>
@@ -6965,25 +6965,25 @@
         <v>3.95</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="K26" t="n">
         <v>3.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O26" t="n">
         <v>1.39</v>
       </c>
       <c r="P26" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q26" t="n">
         <v>2.18</v>
@@ -6995,16 +6995,16 @@
         <v>4.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U26" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V26" t="n">
         <v>1.34</v>
       </c>
       <c r="W26" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X26" t="n">
         <v>13</v>
@@ -7019,19 +7019,19 @@
         <v>85</v>
       </c>
       <c r="AB26" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC26" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE26" t="n">
         <v>60</v>
       </c>
       <c r="AF26" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG26" t="n">
         <v>13</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G27" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H27" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="I27" t="n">
         <v>3.25</v>
@@ -7222,7 +7222,7 @@
         <v>3.45</v>
       </c>
       <c r="K27" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L27" t="n">
         <v>1.33</v>
@@ -7234,82 +7234,82 @@
         <v>3.95</v>
       </c>
       <c r="O27" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P27" t="n">
         <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R27" t="n">
         <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U27" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X27" t="n">
         <v>19</v>
       </c>
       <c r="Y27" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="Z27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA27" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB27" t="n">
         <v>13.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD27" t="n">
         <v>15.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH27" t="n">
         <v>19</v>
       </c>
       <c r="AI27" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AJ27" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK27" t="n">
         <v>30</v>
       </c>
       <c r="AL27" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AM27" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>32</v>
@@ -7318,25 +7318,25 @@
         <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT27" t="n">
         <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.05</v>
+        <v>25</v>
       </c>
       <c r="AX27" t="n">
         <v>13</v>
@@ -7348,22 +7348,22 @@
         <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.05</v>
+        <v>26</v>
       </c>
       <c r="BC27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
         <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG27" t="n">
         <v>20</v>
@@ -7372,19 +7372,19 @@
         <v>4.1</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BJ27" t="n">
         <v>10.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BL27" t="n">
         <v>120</v>
       </c>
       <c r="BM27" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BN27" t="n">
         <v>6.4</v>
@@ -7393,22 +7393,22 @@
         <v>4.4</v>
       </c>
       <c r="BP27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR27" t="n">
         <v>34</v>
       </c>
       <c r="BS27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BT27" t="n">
         <v>7</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV27" t="n">
         <v>26</v>
@@ -7420,17 +7420,17 @@
         <v>38</v>
       </c>
       <c r="BY27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="G28" t="n">
         <v>4.3</v>
@@ -7470,13 +7470,13 @@
         <v>1.89</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.27</v>
@@ -7485,31 +7485,31 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P28" t="n">
         <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="R28" t="n">
         <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T28" t="n">
         <v>1.64</v>
       </c>
       <c r="U28" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="W28" t="n">
         <v>1.3</v>
@@ -7539,10 +7539,10 @@
         <v>23</v>
       </c>
       <c r="AF28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH28" t="n">
         <v>21</v>
@@ -7551,7 +7551,7 @@
         <v>32</v>
       </c>
       <c r="AJ28" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK28" t="n">
         <v>55</v>
@@ -7563,7 +7563,7 @@
         <v>80</v>
       </c>
       <c r="AN28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO28" t="n">
         <v>12.5</v>
@@ -7572,7 +7572,7 @@
         <v>14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR28" t="n">
         <v>10</v>
@@ -7584,10 +7584,10 @@
         <v>13</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW28" t="n">
         <v>13.5</v>
@@ -7623,10 +7623,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ28" t="n">
         <v>11</v>
@@ -7641,7 +7641,7 @@
         <v>4.5</v>
       </c>
       <c r="BN28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BO28" t="n">
         <v>5.8</v>
@@ -7659,19 +7659,19 @@
         <v>4.3</v>
       </c>
       <c r="BT28" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU28" t="n">
         <v>3.75</v>
       </c>
       <c r="BV28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW28" t="n">
         <v>3.6</v>
       </c>
       <c r="BX28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY28" t="n">
         <v>4</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
         <v>1.78</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -7981,13 +7981,13 @@
         <v>4.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K30" t="n">
         <v>3.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="M30" t="n">
         <v>1.14</v>
@@ -7999,28 +7999,28 @@
         <v>1.6</v>
       </c>
       <c r="P30" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q30" t="n">
         <v>2.94</v>
       </c>
       <c r="R30" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U30" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X30" t="n">
         <v>8.6</v>
@@ -8092,7 +8092,7 @@
         <v>5.9</v>
       </c>
       <c r="AU30" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
         <v>13.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
         <v>3.8</v>
       </c>
       <c r="I31" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
         <v>3.55</v>
@@ -8256,22 +8256,22 @@
         <v>1.98</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="R31" t="n">
         <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="T31" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="U31" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="V31" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
         <v>1.86</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -8477,37 +8477,37 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H32" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="I32" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J32" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K32" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P32" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q32" t="n">
         <v>1.93</v>
@@ -8519,16 +8519,16 @@
         <v>3.45</v>
       </c>
       <c r="T32" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U32" t="n">
         <v>2.06</v>
       </c>
       <c r="V32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W32" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X32" t="n">
         <v>18</v>
@@ -8588,7 +8588,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR32" t="n">
         <v>13</v>
@@ -8606,10 +8606,10 @@
         <v>9.4</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.3</v>
+        <v>19.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY32" t="n">
         <v>9.800000000000001</v>
@@ -8642,13 +8642,13 @@
         <v>3.85</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ32" t="n">
         <v>11.5</v>
       </c>
       <c r="BK32" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BL32" t="n">
         <v>150</v>
@@ -8663,7 +8663,7 @@
         <v>4.7</v>
       </c>
       <c r="BP32" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ32" t="n">
         <v>4.2</v>
@@ -8672,7 +8672,7 @@
         <v>46</v>
       </c>
       <c r="BS32" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT32" t="n">
         <v>6.4</v>
@@ -8693,14 +8693,14 @@
         <v>4.3</v>
       </c>
       <c r="BZ32" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -8731,166 +8731,166 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="G33" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="H33" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="I33" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J33" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K33" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R33" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
         <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="U33" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V33" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W33" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="X33" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y33" t="n">
         <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA33" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="AB33" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD33" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG33" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ33" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN33" t="n">
         <v>970</v>
       </c>
       <c r="AO33" t="n">
-        <v>390</v>
+        <v>180</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.66</v>
+        <v>4.9</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.14</v>
+        <v>6.8</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.66</v>
+        <v>7.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="AX33" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY33" t="n">
         <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2.22</v>
+        <v>8.4</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.18</v>
+        <v>7.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="BC33" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.18</v>
+        <v>7.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O34" t="n">
         <v>1.15</v>
@@ -9021,10 +9021,10 @@
         <v>1.44</v>
       </c>
       <c r="R34" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S34" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="T34" t="n">
         <v>1.98</v>
@@ -9048,7 +9048,7 @@
         <v>160</v>
       </c>
       <c r="AA34" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="AB34" t="n">
         <v>12.5</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>2.2</v>
       </c>
       <c r="G35" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H35" t="n">
         <v>3.4</v>
@@ -9251,28 +9251,28 @@
         <v>3.85</v>
       </c>
       <c r="J35" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L35" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M35" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N35" t="n">
         <v>3.15</v>
       </c>
       <c r="O35" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P35" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R35" t="n">
         <v>1.28</v>
@@ -9281,7 +9281,7 @@
         <v>3.75</v>
       </c>
       <c r="T35" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U35" t="n">
         <v>1.97</v>
@@ -9290,13 +9290,13 @@
         <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X35" t="n">
         <v>15</v>
       </c>
       <c r="Y35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z35" t="n">
         <v>27</v>
@@ -9305,7 +9305,7 @@
         <v>75</v>
       </c>
       <c r="AB35" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
         <v>8.6</v>
@@ -9317,19 +9317,19 @@
         <v>50</v>
       </c>
       <c r="AF35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG35" t="n">
         <v>11.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI35" t="n">
         <v>60</v>
       </c>
       <c r="AJ35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK35" t="n">
         <v>27</v>
@@ -9341,7 +9341,7 @@
         <v>140</v>
       </c>
       <c r="AN35" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO35" t="n">
         <v>55</v>
@@ -9359,43 +9359,43 @@
         <v>1.05</v>
       </c>
       <c r="AT35" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU35" t="n">
         <v>7</v>
       </c>
       <c r="AV35" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW35" t="n">
         <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ35" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA35" t="n">
         <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>22</v>
+        <v>1.05</v>
       </c>
       <c r="BC35" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD35" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
         <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG35" t="n">
         <v>1.01</v>
@@ -9440,7 +9440,7 @@
         <v>7.6</v>
       </c>
       <c r="BU35" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV35" t="n">
         <v>36</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -9520,19 +9520,19 @@
         <v>1.1</v>
       </c>
       <c r="O36" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P36" t="n">
         <v>1.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="R36" t="n">
         <v>1.24</v>
       </c>
       <c r="S36" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T36" t="n">
         <v>1.11</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -9747,40 +9747,40 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G37" t="n">
-        <v>140</v>
+        <v>990</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="I37" t="n">
-        <v>140</v>
+        <v>990</v>
       </c>
       <c r="J37" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K37" t="n">
         <v>6.8</v>
       </c>
       <c r="L37" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O37" t="n">
         <v>1.24</v>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
@@ -9789,10 +9789,10 @@
         <v>1.24</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
@@ -9855,52 +9855,52 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
         <v>1.01</v>
@@ -9912,65 +9912,65 @@
         <v>1000</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ37" t="n">
         <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN37" t="n">
         <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT37" t="n">
         <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G38" t="n">
         <v>2.04</v>
@@ -10019,7 +10019,7 @@
         <v>3.8</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
@@ -10043,7 +10043,7 @@
         <v>3.45</v>
       </c>
       <c r="T38" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U38" t="n">
         <v>2.14</v>
@@ -10103,7 +10103,7 @@
         <v>100</v>
       </c>
       <c r="AN38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO38" t="n">
         <v>55</v>
@@ -10118,7 +10118,7 @@
         <v>26</v>
       </c>
       <c r="AS38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT38" t="n">
         <v>8.4</v>
@@ -10130,7 +10130,7 @@
         <v>14.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX38" t="n">
         <v>11</v>
@@ -10142,7 +10142,7 @@
         <v>16.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB38" t="n">
         <v>22</v>
@@ -10154,77 +10154,77 @@
         <v>32</v>
       </c>
       <c r="BE38" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF38" t="n">
         <v>13.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH38" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BJ38" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK38" t="n">
         <v>1.04</v>
       </c>
       <c r="BL38" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM38" t="n">
         <v>1.04</v>
       </c>
       <c r="BN38" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP38" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ38" t="n">
         <v>1.04</v>
       </c>
       <c r="BR38" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS38" t="n">
         <v>1.04</v>
       </c>
       <c r="BT38" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV38" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW38" t="n">
         <v>1.04</v>
       </c>
       <c r="BX38" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY38" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA38" t="n">
         <v>1.04</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -10255,166 +10255,166 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G39" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H39" t="n">
         <v>2.44</v>
       </c>
       <c r="I39" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="J39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X39" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX39" t="n">
         <v>3.65</v>
       </c>
-      <c r="K39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
         <v>34</v>
       </c>
       <c r="J40" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="K40" t="n">
         <v>14.5</v>
@@ -10548,7 +10548,7 @@
         <v>2.04</v>
       </c>
       <c r="S40" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="T40" t="n">
         <v>2.68</v>
@@ -10560,7 +10560,7 @@
         <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="X40" t="n">
         <v>44</v>
@@ -10578,7 +10578,7 @@
         <v>14</v>
       </c>
       <c r="AC40" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AD40" t="n">
         <v>130</v>
@@ -10620,13 +10620,13 @@
         <v>40</v>
       </c>
       <c r="AQ40" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AR40" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AS40" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AT40" t="n">
         <v>13</v>
@@ -10638,7 +10638,7 @@
         <v>46</v>
       </c>
       <c r="AW40" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX40" t="n">
         <v>7.6</v>
@@ -10647,19 +10647,19 @@
         <v>16</v>
       </c>
       <c r="AZ40" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BA40" t="n">
         <v>130</v>
       </c>
       <c r="BB40" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC40" t="n">
         <v>13.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE40" t="n">
         <v>100</v>
@@ -10668,7 +10668,7 @@
         <v>2.4</v>
       </c>
       <c r="BG40" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="BH40" t="n">
         <v>7</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
         <v>2.36</v>
       </c>
       <c r="G41" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H41" t="n">
         <v>2.66</v>
@@ -10781,199 +10781,199 @@
         <v>4.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M41" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N41" t="n">
-        <v>2.52</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P41" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="S41" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="T41" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="U41" t="n">
-        <v>1.11</v>
+        <v>2.74</v>
       </c>
       <c r="V41" t="n">
         <v>1.51</v>
       </c>
       <c r="W41" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS41" t="n">
         <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA41" t="n">
         <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE41" t="n">
         <v>1.01</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH41" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI41" t="n">
         <v>1.04</v>
       </c>
       <c r="BJ41" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK41" t="n">
         <v>1.04</v>
       </c>
       <c r="BL41" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM41" t="n">
         <v>1.04</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO41" t="n">
         <v>1.04</v>
       </c>
       <c r="BP41" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ41" t="n">
         <v>1.04</v>
       </c>
       <c r="BR41" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS41" t="n">
         <v>1.04</v>
       </c>
       <c r="BT41" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU41" t="n">
         <v>1.04</v>
       </c>
       <c r="BV41" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW41" t="n">
         <v>1.04</v>
       </c>
       <c r="BX41" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY41" t="n">
         <v>1.04</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -11017,22 +11017,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G42" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="H42" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L42" t="n">
         <v>1.22</v>
@@ -11041,34 +11041,34 @@
         <v>1.02</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O42" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P42" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R42" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S42" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="T42" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U42" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="V42" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W42" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="X42" t="n">
         <v>950</v>
@@ -11077,7 +11077,7 @@
         <v>950</v>
       </c>
       <c r="Z42" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA42" t="n">
         <v>1000</v>
@@ -11092,7 +11092,7 @@
         <v>950</v>
       </c>
       <c r="AE42" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
         <v>970</v>
@@ -11104,7 +11104,7 @@
         <v>950</v>
       </c>
       <c r="AI42" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ42" t="n">
         <v>970</v>
@@ -11116,7 +11116,7 @@
         <v>29</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN42" t="n">
         <v>970</v>
@@ -11125,58 +11125,58 @@
         <v>55</v>
       </c>
       <c r="AP42" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.78</v>
+        <v>4.6</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.78</v>
+        <v>4.8</v>
       </c>
       <c r="AT42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV42" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AW42" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="AX42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ42" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY42" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ42" t="n">
+      <c r="BA42" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA42" t="n">
-        <v>2.78</v>
-      </c>
       <c r="BB42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF42" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC42" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BG42" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH42" t="n">
         <v>5.6</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -11271,19 +11271,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="G43" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="H43" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I43" t="n">
-        <v>990</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="K43" t="n">
         <v>500</v>
@@ -11295,88 +11295,88 @@
         <v>1.02</v>
       </c>
       <c r="N43" t="n">
-        <v>2.52</v>
+        <v>5.3</v>
       </c>
       <c r="O43" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P43" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="R43" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="S43" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T43" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U43" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="W43" t="n">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA43" t="n">
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF43" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG43" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH43" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -11525,19 +11525,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="G44" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H44" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I44" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="J44" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K44" t="n">
         <v>5.8</v>
@@ -11549,22 +11549,22 @@
         <v>1.02</v>
       </c>
       <c r="N44" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O44" t="n">
         <v>1.15</v>
       </c>
       <c r="P44" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R44" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="S44" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T44" t="n">
         <v>1.6</v>
@@ -11573,19 +11573,19 @@
         <v>2.36</v>
       </c>
       <c r="V44" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="W44" t="n">
         <v>1.19</v>
       </c>
       <c r="X44" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Y44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z44" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA44" t="n">
         <v>18.5</v>
@@ -11594,10 +11594,10 @@
         <v>34</v>
       </c>
       <c r="AC44" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE44" t="n">
         <v>17</v>
@@ -11630,61 +11630,61 @@
         <v>55</v>
       </c>
       <c r="AO44" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX44" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT44" t="n">
+      <c r="AY44" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD44" t="n">
         <v>4.7</v>
       </c>
-      <c r="AU44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>5</v>
-      </c>
       <c r="BE44" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF44" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BG44" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="BH44" t="n">
         <v>5.6</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -11782,19 +11782,19 @@
         <v>1.04</v>
       </c>
       <c r="G45" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H45" t="n">
         <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J45" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K45" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
@@ -11803,7 +11803,7 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O45" t="n">
         <v>1.01</v>
@@ -11821,10 +11821,10 @@
         <v>1.43</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V45" t="n">
         <v>1.01</v>
@@ -11944,55 +11944,55 @@
         <v>1000</v>
       </c>
       <c r="BI45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ45" t="n">
         <v>1000</v>
       </c>
       <c r="BK45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN45" t="n">
         <v>1000</v>
       </c>
       <c r="BO45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP45" t="n">
         <v>1000</v>
       </c>
       <c r="BQ45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR45" t="n">
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT45" t="n">
         <v>1000</v>
       </c>
       <c r="BU45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ45" t="n">
         <v>0</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -12036,13 +12036,13 @@
         <v>2.06</v>
       </c>
       <c r="G46" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H46" t="n">
         <v>3.9</v>
       </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J46" t="n">
         <v>3.1</v>
@@ -12072,7 +12072,7 @@
         <v>1.24</v>
       </c>
       <c r="S46" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T46" t="n">
         <v>1.96</v>
@@ -12081,10 +12081,10 @@
         <v>1.86</v>
       </c>
       <c r="V46" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W46" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X46" t="n">
         <v>12</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -12290,19 +12290,19 @@
         <v>2.4</v>
       </c>
       <c r="G47" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H47" t="n">
         <v>3.65</v>
       </c>
       <c r="I47" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J47" t="n">
         <v>2.98</v>
       </c>
       <c r="K47" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L47" t="n">
         <v>1.46</v>
@@ -12320,7 +12320,7 @@
         <v>1.56</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R47" t="n">
         <v>1.2</v>
@@ -12338,7 +12338,7 @@
         <v>1.34</v>
       </c>
       <c r="W47" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X47" t="n">
         <v>9.199999999999999</v>
@@ -12359,7 +12359,7 @@
         <v>7.2</v>
       </c>
       <c r="AD47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE47" t="n">
         <v>80</v>
@@ -12401,7 +12401,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR47" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS47" t="n">
         <v>6</v>
@@ -12413,10 +12413,10 @@
         <v>6.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>15</v>
+        <v>4.9</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX47" t="n">
         <v>11.5</v>
@@ -12434,16 +12434,16 @@
         <v>5.5</v>
       </c>
       <c r="BC47" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE47" t="n">
         <v>6.2</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG47" t="n">
         <v>6</v>
@@ -12458,7 +12458,7 @@
         <v>13.5</v>
       </c>
       <c r="BK47" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BL47" t="n">
         <v>240</v>
@@ -12473,10 +12473,10 @@
         <v>3.75</v>
       </c>
       <c r="BP47" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ47" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR47" t="n">
         <v>50</v>
@@ -12485,7 +12485,7 @@
         <v>4.6</v>
       </c>
       <c r="BT47" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU47" t="n">
         <v>5.2</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12547,7 @@
         <v>110</v>
       </c>
       <c r="H48" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I48" t="n">
         <v>990</v>
@@ -12565,13 +12565,13 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O48" t="n">
         <v>1.2</v>
       </c>
       <c r="P48" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -12804,16 +12804,16 @@
         <v>4.2</v>
       </c>
       <c r="I49" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K49" t="n">
         <v>3.85</v>
       </c>
       <c r="L49" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M49" t="n">
         <v>1.11</v>
@@ -12846,7 +12846,7 @@
         <v>1.22</v>
       </c>
       <c r="W49" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X49" t="n">
         <v>11</v>
@@ -12957,55 +12957,55 @@
         <v>5</v>
       </c>
       <c r="BH49" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI49" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ49" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK49" t="n">
         <v>1.04</v>
       </c>
       <c r="BL49" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM49" t="n">
         <v>1.04</v>
       </c>
       <c r="BN49" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO49" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP49" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ49" t="n">
         <v>1.04</v>
       </c>
       <c r="BR49" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS49" t="n">
         <v>1.04</v>
       </c>
       <c r="BT49" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU49" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV49" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW49" t="n">
         <v>1.04</v>
       </c>
       <c r="BX49" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY49" t="n">
         <v>1.04</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
         <v>3.8</v>
       </c>
       <c r="L50" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="M50" t="n">
         <v>1.1</v>
@@ -13082,13 +13082,13 @@
         <v>1.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="R50" t="n">
         <v>1.22</v>
       </c>
       <c r="S50" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T50" t="n">
         <v>1.96</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -13303,118 +13303,118 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G51" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="H51" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J51" t="n">
         <v>3.2</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>4.3</v>
       </c>
-      <c r="J51" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K51" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L51" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M51" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N51" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
       <c r="O51" t="n">
         <v>1.33</v>
       </c>
       <c r="P51" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q51" t="n">
         <v>1.98</v>
       </c>
       <c r="R51" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S51" t="n">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="T51" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U51" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V51" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W51" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z51" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA51" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI51" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL51" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM51" t="n">
         <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO51" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR51" t="n">
         <v>1.01</v>
@@ -13423,10 +13423,10 @@
         <v>1.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV51" t="n">
         <v>1.01</v>
@@ -13435,10 +13435,10 @@
         <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ51" t="n">
         <v>1.01</v>
@@ -13465,68 +13465,68 @@
         <v>1.01</v>
       </c>
       <c r="BH51" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN51" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO51" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP51" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR51" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BU51" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV51" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX51" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ51" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -13557,112 +13557,112 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="G52" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H52" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I52" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J52" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="K52" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M52" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N52" t="n">
-        <v>1.24</v>
+        <v>3.35</v>
       </c>
       <c r="O52" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P52" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="R52" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S52" t="n">
-        <v>1.27</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U52" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W52" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X52" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA52" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB52" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC52" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF52" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG52" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH52" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK52" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM52" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP52" t="n">
         <v>1.01</v>
@@ -13719,58 +13719,58 @@
         <v>1.01</v>
       </c>
       <c r="BH52" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI52" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ52" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL52" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN52" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP52" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR52" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT52" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV52" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX52" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ52" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
         <v>2.56</v>
       </c>
       <c r="I53" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="J53" t="n">
         <v>2.78</v>
@@ -13838,7 +13838,7 @@
         <v>2.82</v>
       </c>
       <c r="O53" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P53" t="n">
         <v>1.61</v>
@@ -13874,7 +13874,7 @@
         <v>970</v>
       </c>
       <c r="AA53" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB53" t="n">
         <v>970</v>
@@ -13919,13 +13919,13 @@
         <v>42</v>
       </c>
       <c r="AP53" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ53" t="n">
         <v>6.8</v>
       </c>
       <c r="AR53" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AS53" t="n">
         <v>4.5</v>
@@ -13937,7 +13937,7 @@
         <v>5.7</v>
       </c>
       <c r="AV53" t="n">
-        <v>3.7</v>
+        <v>9.6</v>
       </c>
       <c r="AW53" t="n">
         <v>4.4</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-17 07:11:33</t>
+          <t>2026-05-17 09:42:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -875,13 +875,13 @@
         <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
         <v>1.31</v>
@@ -899,10 +899,10 @@
         <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
         <v>2.48</v>
@@ -920,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AB2" t="n">
         <v>24</v>
@@ -1019,7 +1019,7 @@
         <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BI2" t="n">
         <v>2.94</v>
@@ -1028,31 +1028,31 @@
         <v>12.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL2" t="n">
         <v>170</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN2" t="n">
         <v>12</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP2" t="n">
         <v>75</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR2" t="n">
         <v>75</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT2" t="n">
         <v>4.6</v>
@@ -1064,23 +1064,23 @@
         <v>11.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BX2" t="n">
         <v>30</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>22</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1273,40 +1273,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3" t="n">
         <v>15.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL3" t="n">
         <v>280</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN3" t="n">
         <v>14</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP3" t="n">
         <v>120</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR3" t="n">
         <v>120</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT3" t="n">
         <v>4.4</v>
@@ -1318,23 +1318,23 @@
         <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BX3" t="n">
         <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>30</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
         <v>4.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ4" t="n">
         <v>950</v>
@@ -1548,7 +1548,7 @@
         <v>950</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP4" t="n">
         <v>70</v>
@@ -1557,7 +1557,7 @@
         <v>4.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BS4" t="n">
         <v>4.5</v>
@@ -1584,11 +1584,11 @@
         <v>19.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>1.96</v>
       </c>
       <c r="G5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K5" t="n">
         <v>3.05</v>
@@ -1643,7 +1643,7 @@
         <v>1.16</v>
       </c>
       <c r="N5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.68</v>
@@ -1661,16 +1661,16 @@
         <v>7.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
         <v>6.6</v>
@@ -1790,13 +1790,13 @@
         <v>17</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL5" t="n">
         <v>420</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN5" t="n">
         <v>4.9</v>
@@ -1808,41 +1808,41 @@
         <v>19.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR5" t="n">
         <v>60</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT5" t="n">
         <v>11.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV5" t="n">
         <v>95</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX5" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ5" t="n">
         <v>65</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="G6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>1.46</v>
@@ -1906,7 +1906,7 @@
         <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R6" t="n">
         <v>1.23</v>
@@ -1969,7 +1969,7 @@
         <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>210</v>
@@ -1990,7 +1990,7 @@
         <v>5.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT6" t="n">
         <v>5.9</v>
@@ -2014,7 +2014,7 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB6" t="n">
         <v>18.5</v>
@@ -2026,7 +2026,7 @@
         <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF6" t="n">
         <v>13.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -2127,64 +2127,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
         <v>1.82</v>
       </c>
       <c r="V7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
         <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z7" t="n">
         <v>15.5</v>
@@ -2217,7 +2217,7 @@
         <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
         <v>65</v>
@@ -2229,16 +2229,16 @@
         <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR7" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
         <v>12.5</v>
@@ -2298,13 +2298,13 @@
         <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL7" t="n">
         <v>180</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN7" t="n">
         <v>8</v>
@@ -2316,13 +2316,13 @@
         <v>40</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR7" t="n">
         <v>60</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT7" t="n">
         <v>5.5</v>
@@ -2331,26 +2331,26 @@
         <v>3.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX7" t="n">
         <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>40</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H8" t="n">
         <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
         <v>1.46</v>
@@ -2432,13 +2432,13 @@
         <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
         <v>28</v>
@@ -2519,7 +2519,7 @@
         <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
         <v>32</v>
@@ -2534,7 +2534,7 @@
         <v>28</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="BF8" t="n">
         <v>18</v>
@@ -2552,13 +2552,13 @@
         <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BL8" t="n">
         <v>190</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN8" t="n">
         <v>6</v>
@@ -2570,41 +2570,41 @@
         <v>23</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR8" t="n">
         <v>44</v>
       </c>
       <c r="BS8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU8" t="n">
         <v>5</v>
       </c>
       <c r="BV8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX8" t="n">
         <v>60</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>44</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -2913,31 +2913,31 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="U10" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
         <v>1.01</v>
@@ -3060,13 +3060,13 @@
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL10" t="n">
         <v>110</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN10" t="n">
         <v>5.3</v>
@@ -3078,31 +3078,31 @@
         <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BR10" t="n">
         <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BT10" t="n">
         <v>12.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV10" t="n">
         <v>55</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>3.6</v>
       </c>
       <c r="G11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="H11" t="n">
         <v>2.06</v>
@@ -3161,7 +3161,7 @@
         <v>3.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
@@ -3173,7 +3173,7 @@
         <v>1.34</v>
       </c>
       <c r="P11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
         <v>2</v>
@@ -3182,16 +3182,16 @@
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W11" t="n">
         <v>1.31</v>
@@ -3290,7 +3290,7 @@
         <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD11" t="n">
         <v>1.01</v>
@@ -3314,13 +3314,13 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL11" t="n">
         <v>150</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BN11" t="n">
         <v>8</v>
@@ -3332,13 +3332,13 @@
         <v>38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
         <v>50</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BT11" t="n">
         <v>5.6</v>
@@ -3350,13 +3350,13 @@
         <v>18.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX11" t="n">
         <v>36</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="H13" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
         <v>8.199999999999999</v>
@@ -3672,19 +3672,19 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
         <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
         <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.41</v>
@@ -3953,7 +3953,7 @@
         <v>1.78</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
         <v>1.54</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -4165,46 +4165,46 @@
         <v>1.74</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
         <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.32</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="V15" t="n">
         <v>1.2</v>
@@ -4213,176 +4213,176 @@
         <v>2.34</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -4413,115 +4413,115 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y16" t="n">
         <v>8</v>
       </c>
-      <c r="G16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>7.2</v>
-      </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AB16" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AF16" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AG16" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AH16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="AK16" t="n">
+        <v>210</v>
+      </c>
+      <c r="AL16" t="n">
         <v>180</v>
       </c>
-      <c r="AL16" t="n">
-        <v>160</v>
-      </c>
       <c r="AM16" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN16" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AO16" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>6.8</v>
@@ -4530,37 +4530,37 @@
         <v>7</v>
       </c>
       <c r="AS16" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>23</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AV16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="AZ16" t="n">
-        <v>25</v>
+        <v>8.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
         <v>11</v>
       </c>
       <c r="BC16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD16" t="n">
         <v>10.5</v>
@@ -4572,71 +4572,71 @@
         <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH16" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="BJ16" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="BL16" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="BM16" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="BP16" t="n">
+        <v>110</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR16" t="n">
         <v>95</v>
       </c>
-      <c r="BQ16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>100</v>
-      </c>
       <c r="BS16" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BU16" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BX16" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BY16" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BZ16" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>4.1</v>
       </c>
       <c r="G18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H18" t="n">
         <v>1.96</v>
@@ -4987,7 +4987,7 @@
         <v>24</v>
       </c>
       <c r="AB18" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
         <v>9.199999999999999</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -5178,19 +5178,19 @@
         <v>3.25</v>
       </c>
       <c r="G19" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I19" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J19" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
         <v>1.35</v>
@@ -5199,10 +5199,10 @@
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P19" t="n">
         <v>1.9</v>
@@ -5211,10 +5211,10 @@
         <v>1.92</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
         <v>1.72</v>
@@ -5223,22 +5223,22 @@
         <v>2.12</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W19" t="n">
         <v>1.36</v>
       </c>
       <c r="X19" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y19" t="n">
         <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB19" t="n">
         <v>15.5</v>
@@ -5256,10 +5256,10 @@
         <v>28</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
         <v>44</v>
@@ -5277,7 +5277,7 @@
         <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AO19" t="n">
         <v>22</v>
@@ -5289,49 +5289,49 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
         <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AX19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE19" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF19" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BG19" t="n">
         <v>14.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -5429,112 +5429,112 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G20" t="n">
-        <v>990</v>
+        <v>2.92</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="I20" t="n">
-        <v>990</v>
+        <v>3.75</v>
       </c>
       <c r="J20" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="K20" t="n">
-        <v>500</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>1.32</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>1.32</v>
+        <v>1.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>2.74</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP20" t="n">
         <v>1.01</v>
@@ -5591,58 +5591,58 @@
         <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL20" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -5683,112 +5683,112 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="G21" t="n">
-        <v>990</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="I21" t="n">
-        <v>990</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>500</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.29</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>1.28</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>1.23</v>
+        <v>2.56</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP21" t="n">
         <v>1.01</v>
@@ -5845,58 +5845,58 @@
         <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
         <v>3.95</v>
       </c>
       <c r="L22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
@@ -6015,10 +6015,10 @@
         <v>50</v>
       </c>
       <c r="AF22" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
         <v>16</v>
@@ -6039,7 +6039,7 @@
         <v>70</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO22" t="n">
         <v>23</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v>4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
@@ -6362,13 +6362,13 @@
         <v>11</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BL23" t="n">
         <v>110</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN23" t="n">
         <v>5.3</v>
@@ -6380,41 +6380,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR23" t="n">
         <v>27</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT23" t="n">
         <v>9.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV23" t="n">
         <v>42</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX23" t="n">
         <v>48</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ23" t="n">
         <v>19.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -6445,112 +6445,112 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="G24" t="n">
-        <v>990</v>
+        <v>1.98</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>500</v>
+        <v>4.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>1.34</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>1.23</v>
       </c>
       <c r="P24" t="n">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>1.23</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP24" t="n">
         <v>1.01</v>
@@ -6607,58 +6607,58 @@
         <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
         <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
         <v>3.65</v>
@@ -6729,7 +6729,7 @@
         <v>1.31</v>
       </c>
       <c r="P25" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
         <v>1.93</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -7207,109 +7207,109 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="H27" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="I27" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="J27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M27" t="n">
         <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.27</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="X27" t="n">
         <v>19</v>
       </c>
       <c r="Y27" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC27" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AD27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>40</v>
       </c>
       <c r="AF27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG27" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI27" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ27" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK27" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL27" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AM27" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AO27" t="n">
         <v>32</v>
@@ -7318,49 +7318,49 @@
         <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS27" t="n">
         <v>36</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>25</v>
+        <v>1.05</v>
       </c>
       <c r="AX27" t="n">
         <v>13</v>
       </c>
       <c r="AY27" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
         <v>12.5</v>
       </c>
       <c r="BA27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.05</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>26</v>
       </c>
       <c r="BC27" t="n">
         <v>19.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF27" t="n">
         <v>14.5</v>
@@ -7369,49 +7369,49 @@
         <v>20</v>
       </c>
       <c r="BH27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ27" t="n">
         <v>10.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BL27" t="n">
         <v>120</v>
       </c>
       <c r="BM27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BN27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BR27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS27" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BT27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW27" t="n">
         <v>4.6</v>
@@ -7420,17 +7420,17 @@
         <v>38</v>
       </c>
       <c r="BY27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BZ27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -7464,19 +7464,19 @@
         <v>3.75</v>
       </c>
       <c r="G28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H28" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="I28" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J28" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L28" t="n">
         <v>1.27</v>
@@ -7485,7 +7485,7 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
         <v>1.23</v>
@@ -7494,25 +7494,25 @@
         <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R28" t="n">
         <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T28" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V28" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
         <v>23</v>
@@ -7530,7 +7530,7 @@
         <v>22</v>
       </c>
       <c r="AC28" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD28" t="n">
         <v>13</v>
@@ -7620,13 +7620,13 @@
         <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ28" t="n">
         <v>11</v>
@@ -7638,7 +7638,7 @@
         <v>120</v>
       </c>
       <c r="BM28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BN28" t="n">
         <v>9.4</v>
@@ -7665,16 +7665,16 @@
         <v>3.75</v>
       </c>
       <c r="BV28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW28" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BX28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ28" t="n">
         <v>22</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -7739,10 +7739,10 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O29" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="P29" t="n">
         <v>1.25</v>
@@ -7760,7 +7760,7 @@
         <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.51</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
         <v>1.44</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G30" t="n">
         <v>2.46</v>
@@ -7984,7 +7984,7 @@
         <v>2.88</v>
       </c>
       <c r="K30" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L30" t="n">
         <v>1.61</v>
@@ -8035,7 +8035,7 @@
         <v>120</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC30" t="n">
         <v>8.199999999999999</v>
@@ -8086,7 +8086,7 @@
         <v>20</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT30" t="n">
         <v>5.9</v>
@@ -8098,7 +8098,7 @@
         <v>13.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX30" t="n">
         <v>10.5</v>
@@ -8110,25 +8110,25 @@
         <v>19.5</v>
       </c>
       <c r="BA30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB30" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB30" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BC30" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH30" t="n">
         <v>2.8</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
         <v>1.98</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R31" t="n">
         <v>1.38</v>
@@ -8331,7 +8331,7 @@
         <v>60</v>
       </c>
       <c r="AP31" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>11</v>
@@ -8343,10 +8343,10 @@
         <v>4</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
@@ -8358,10 +8358,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA31" t="n">
         <v>3.9</v>
@@ -8370,7 +8370,7 @@
         <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD31" t="n">
         <v>3.8</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -8477,28 +8477,28 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="G32" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H32" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I32" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L32" t="n">
         <v>1.35</v>
       </c>
       <c r="M32" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N32" t="n">
         <v>3.4</v>
@@ -8507,10 +8507,10 @@
         <v>1.33</v>
       </c>
       <c r="P32" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R32" t="n">
         <v>1.33</v>
@@ -8525,10 +8525,10 @@
         <v>2.06</v>
       </c>
       <c r="V32" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W32" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X32" t="n">
         <v>18</v>
@@ -8558,7 +8558,7 @@
         <v>26</v>
       </c>
       <c r="AG32" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH32" t="n">
         <v>22</v>
@@ -8588,7 +8588,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR32" t="n">
         <v>13</v>
@@ -8621,13 +8621,13 @@
         <v>4.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC32" t="n">
         <v>4.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE32" t="n">
         <v>4.8</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -8731,55 +8731,55 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G33" t="n">
         <v>1.77</v>
       </c>
       <c r="H33" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="I33" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J33" t="n">
         <v>3.7</v>
       </c>
       <c r="K33" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="O33" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P33" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Q33" t="n">
         <v>2.16</v>
       </c>
       <c r="R33" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="T33" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W33" t="n">
         <v>2.28</v>
@@ -8791,10 +8791,10 @@
         <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA33" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="AB33" t="n">
         <v>9</v>
@@ -8803,19 +8803,19 @@
         <v>9</v>
       </c>
       <c r="AD33" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AE33" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AF33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AG33" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AH33" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AI33" t="n">
         <v>210</v>
@@ -8824,73 +8824,73 @@
         <v>17.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AL33" t="n">
         <v>75</v>
       </c>
       <c r="AM33" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="AN33" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AO33" t="n">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ33" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AR33" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT33" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.8</v>
+        <v>3.1</v>
       </c>
       <c r="AV33" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AW33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX33" t="n">
         <v>7</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>5.2</v>
       </c>
       <c r="AY33" t="n">
         <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB33" t="n">
         <v>15</v>
       </c>
       <c r="BC33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BD33" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
         <v>1.21</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
         <v>6.2</v>
@@ -9186,16 +9186,16 @@
         <v>18</v>
       </c>
       <c r="BU34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV34" t="n">
         <v>120</v>
       </c>
       <c r="BW34" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX34" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BY34" t="n">
         <v>5.3</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -9239,154 +9239,154 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="G35" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H35" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I35" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K35" t="n">
         <v>3.85</v>
       </c>
       <c r="L35" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N35" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="O35" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="P35" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.04</v>
+        <v>1.06</v>
       </c>
       <c r="R35" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="S35" t="n">
-        <v>3.75</v>
+        <v>1.44</v>
       </c>
       <c r="T35" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="U35" t="n">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W35" t="n">
         <v>1.76</v>
       </c>
       <c r="X35" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
         <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
         <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
         <v>1.01</v>
@@ -9395,74 +9395,74 @@
         <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
         <v>1.01</v>
       </c>
       <c r="BH35" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BJ35" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL35" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN35" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP35" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR35" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BT35" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV35" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BX35" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ35" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -9493,175 +9493,175 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G36" t="n">
-        <v>990</v>
+        <v>2.88</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="I36" t="n">
-        <v>990</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="K36" t="n">
-        <v>500</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N36" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="O36" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P36" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.17</v>
+        <v>1.51</v>
       </c>
       <c r="R36" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>1.17</v>
+        <v>2.28</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH36" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI36" t="n">
         <v>1.04</v>
       </c>
       <c r="BJ36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BK36" t="n">
         <v>1.04</v>
@@ -9673,37 +9673,37 @@
         <v>1.04</v>
       </c>
       <c r="BN36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BO36" t="n">
         <v>1.04</v>
       </c>
       <c r="BP36" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ36" t="n">
         <v>1.04</v>
       </c>
       <c r="BR36" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS36" t="n">
         <v>1.04</v>
       </c>
       <c r="BT36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BU36" t="n">
         <v>1.04</v>
       </c>
       <c r="BV36" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW36" t="n">
         <v>1.04</v>
       </c>
       <c r="BX36" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY36" t="n">
         <v>1.04</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -9747,230 +9747,230 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.09</v>
+        <v>2.24</v>
       </c>
       <c r="G37" t="n">
-        <v>990</v>
+        <v>2.58</v>
       </c>
       <c r="H37" t="n">
-        <v>1.18</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>990</v>
+        <v>3.75</v>
       </c>
       <c r="J37" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="K37" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>1.26</v>
+        <v>3.85</v>
       </c>
       <c r="O37" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P37" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>1.24</v>
+        <v>2.64</v>
       </c>
       <c r="T37" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="U37" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK37" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH37" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ37" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL37" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN37" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BP37" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR37" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT37" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BV37" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BX37" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ37" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
         <v>2.04</v>
@@ -10025,10 +10025,10 @@
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O38" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P38" t="n">
         <v>1.97</v>
@@ -10172,13 +10172,13 @@
         <v>11</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BL38" t="n">
         <v>140</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN38" t="n">
         <v>5.5</v>
@@ -10190,13 +10190,13 @@
         <v>17</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR38" t="n">
         <v>34</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT38" t="n">
         <v>8.199999999999999</v>
@@ -10208,23 +10208,23 @@
         <v>38</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX38" t="n">
         <v>48</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ38" t="n">
         <v>29</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G39" t="n">
         <v>3.1</v>
@@ -10264,13 +10264,13 @@
         <v>2.44</v>
       </c>
       <c r="I39" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K39" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10279,7 +10279,7 @@
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.3</v>
+        <v>2.24</v>
       </c>
       <c r="O39" t="n">
         <v>1.26</v>
@@ -10291,79 +10291,79 @@
         <v>1.76</v>
       </c>
       <c r="R39" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S39" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="T39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V39" t="n">
         <v>1.64</v>
       </c>
-      <c r="U39" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.67</v>
-      </c>
       <c r="W39" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X39" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF39" t="n">
         <v>22</v>
       </c>
-      <c r="Y39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>26</v>
-      </c>
       <c r="AG39" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI39" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ39" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK39" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL39" t="n">
         <v>38</v>
       </c>
-      <c r="AL39" t="n">
-        <v>46</v>
-      </c>
       <c r="AM39" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN39" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AO39" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AP39" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="AQ39" t="n">
         <v>11</v>
@@ -10372,7 +10372,7 @@
         <v>15.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT39" t="n">
         <v>12</v>
@@ -10384,37 +10384,37 @@
         <v>10.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="AX39" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AY39" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ39" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="BB39" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="BC39" t="n">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF39" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BG39" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -10521,10 +10521,10 @@
         <v>34</v>
       </c>
       <c r="J40" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="K40" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="L40" t="n">
         <v>1.21</v>
@@ -10533,13 +10533,13 @@
         <v>1.02</v>
       </c>
       <c r="N40" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O40" t="n">
         <v>1.11</v>
       </c>
       <c r="P40" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q40" t="n">
         <v>1.36</v>
@@ -10548,10 +10548,10 @@
         <v>2.04</v>
       </c>
       <c r="S40" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T40" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="U40" t="n">
         <v>1.56</v>
@@ -10560,10 +10560,10 @@
         <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="X40" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Y40" t="n">
         <v>100</v>
@@ -10572,7 +10572,7 @@
         <v>440</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AB40" t="n">
         <v>14</v>
@@ -10611,22 +10611,22 @@
         <v>490</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AO40" t="n">
         <v>990</v>
       </c>
       <c r="AP40" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AQ40" t="n">
         <v>65</v>
       </c>
       <c r="AR40" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AS40" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AT40" t="n">
         <v>13</v>
@@ -10644,7 +10644,7 @@
         <v>7.6</v>
       </c>
       <c r="AY40" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ40" t="n">
         <v>60</v>
@@ -10665,7 +10665,7 @@
         <v>100</v>
       </c>
       <c r="BF40" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BG40" t="n">
         <v>110</v>
@@ -10677,16 +10677,16 @@
         <v>4.5</v>
       </c>
       <c r="BJ40" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BK40" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BL40" t="n">
         <v>290</v>
       </c>
       <c r="BM40" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BN40" t="n">
         <v>3.8</v>
@@ -10701,16 +10701,16 @@
         <v>4.6</v>
       </c>
       <c r="BR40" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BS40" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BT40" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BU40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BV40" t="n">
         <v>330</v>
@@ -10725,14 +10725,14 @@
         <v>32</v>
       </c>
       <c r="BZ40" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="CA40" t="n">
         <v>5</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
         <v>2.36</v>
       </c>
       <c r="G41" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H41" t="n">
         <v>2.66</v>
@@ -10778,7 +10778,7 @@
         <v>3.95</v>
       </c>
       <c r="K41" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L41" t="n">
         <v>1.23</v>
@@ -10811,10 +10811,10 @@
         <v>2.74</v>
       </c>
       <c r="V41" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W41" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X41" t="n">
         <v>34</v>
@@ -10880,7 +10880,7 @@
         <v>20</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT41" t="n">
         <v>13</v>
@@ -10892,7 +10892,7 @@
         <v>10</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="AX41" t="n">
         <v>18</v>
@@ -10904,10 +10904,10 @@
         <v>11</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="BC41" t="n">
         <v>19.5</v>
@@ -10916,7 +10916,7 @@
         <v>20</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF41" t="n">
         <v>9.199999999999999</v>
@@ -10928,55 +10928,55 @@
         <v>5.3</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ41" t="n">
         <v>9.6</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BL41" t="n">
         <v>75</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BN41" t="n">
         <v>7</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP41" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR41" t="n">
         <v>26</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT41" t="n">
         <v>7.4</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BV41" t="n">
         <v>21</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX41" t="n">
         <v>28</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -11017,58 +11017,58 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="G42" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H42" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="J42" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="K42" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M42" t="n">
         <v>1.02</v>
       </c>
       <c r="N42" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O42" t="n">
         <v>1.15</v>
       </c>
       <c r="P42" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="Q42" t="n">
         <v>1.45</v>
       </c>
       <c r="R42" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S42" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U42" t="n">
         <v>2.44</v>
       </c>
       <c r="V42" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W42" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X42" t="n">
         <v>950</v>
@@ -11077,7 +11077,7 @@
         <v>950</v>
       </c>
       <c r="Z42" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AA42" t="n">
         <v>1000</v>
@@ -11092,7 +11092,7 @@
         <v>950</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF42" t="n">
         <v>970</v>
@@ -11101,7 +11101,7 @@
         <v>970</v>
       </c>
       <c r="AH42" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI42" t="n">
         <v>65</v>
@@ -11113,76 +11113,76 @@
         <v>970</v>
       </c>
       <c r="AL42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM42" t="n">
         <v>75</v>
       </c>
       <c r="AN42" t="n">
-        <v>970</v>
+        <v>5.8</v>
       </c>
       <c r="AO42" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP42" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX42" t="n">
         <v>4</v>
       </c>
-      <c r="AU42" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV42" t="n">
+      <c r="AY42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB42" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>3.95</v>
       </c>
       <c r="BC42" t="n">
         <v>4.1</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF42" t="n">
         <v>4.3</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH42" t="n">
         <v>5.6</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ42" t="n">
         <v>970</v>
@@ -11194,13 +11194,13 @@
         <v>90</v>
       </c>
       <c r="BM42" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BN42" t="n">
         <v>5.3</v>
       </c>
       <c r="BO42" t="n">
-        <v>2.72</v>
+        <v>3.75</v>
       </c>
       <c r="BP42" t="n">
         <v>970</v>
@@ -11212,25 +11212,25 @@
         <v>22</v>
       </c>
       <c r="BS42" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT42" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="BU42" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV42" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW42" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BX42" t="n">
         <v>44</v>
       </c>
       <c r="BY42" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ42" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -11271,19 +11271,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="G43" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H43" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>9.199999999999999</v>
+        <v>990</v>
       </c>
       <c r="J43" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="K43" t="n">
         <v>500</v>
@@ -11295,88 +11295,88 @@
         <v>1.02</v>
       </c>
       <c r="N43" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W43" t="n">
         <v>2.66</v>
       </c>
-      <c r="Q43" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W43" t="n">
-        <v>2.68</v>
-      </c>
       <c r="X43" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -11555,13 +11555,13 @@
         <v>1.15</v>
       </c>
       <c r="P44" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R44" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S44" t="n">
         <v>2.1</v>
@@ -11576,7 +11576,7 @@
         <v>2.74</v>
       </c>
       <c r="W44" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X44" t="n">
         <v>40</v>
@@ -11585,13 +11585,13 @@
         <v>16</v>
       </c>
       <c r="Z44" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA44" t="n">
         <v>18.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC44" t="n">
         <v>15.5</v>
@@ -11603,10 +11603,10 @@
         <v>17</v>
       </c>
       <c r="AF44" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AG44" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH44" t="n">
         <v>23</v>
@@ -11630,7 +11630,7 @@
         <v>55</v>
       </c>
       <c r="AO44" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP44" t="n">
         <v>4.5</v>
@@ -11645,7 +11645,7 @@
         <v>12</v>
       </c>
       <c r="AT44" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU44" t="n">
         <v>10</v>
@@ -11669,10 +11669,10 @@
         <v>18.5</v>
       </c>
       <c r="BB44" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC44" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BD44" t="n">
         <v>4.7</v>
@@ -11684,7 +11684,7 @@
         <v>4.7</v>
       </c>
       <c r="BG44" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH44" t="n">
         <v>5.6</v>
@@ -11696,19 +11696,19 @@
         <v>11</v>
       </c>
       <c r="BK44" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL44" t="n">
         <v>90</v>
       </c>
       <c r="BM44" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BN44" t="n">
         <v>11.5</v>
       </c>
       <c r="BO44" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP44" t="n">
         <v>46</v>
@@ -11720,7 +11720,7 @@
         <v>44</v>
       </c>
       <c r="BS44" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BT44" t="n">
         <v>5.3</v>
@@ -11732,7 +11732,7 @@
         <v>11</v>
       </c>
       <c r="BW44" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BX44" t="n">
         <v>22</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -11785,13 +11785,13 @@
         <v>990</v>
       </c>
       <c r="H45" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I45" t="n">
         <v>990</v>
       </c>
       <c r="J45" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K45" t="n">
         <v>500</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
         <v>3.9</v>
       </c>
       <c r="I46" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J46" t="n">
         <v>3.1</v>
@@ -12072,10 +12072,10 @@
         <v>1.24</v>
       </c>
       <c r="S46" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T46" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U46" t="n">
         <v>1.86</v>
@@ -12147,10 +12147,10 @@
         <v>9.6</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT46" t="n">
         <v>6</v>
@@ -12162,7 +12162,7 @@
         <v>13</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX46" t="n">
         <v>9.6</v>
@@ -12174,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB46" t="n">
         <v>21</v>
@@ -12183,16 +12183,16 @@
         <v>20</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF46" t="n">
         <v>18</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH46" t="n">
         <v>3.3</v>
@@ -12204,13 +12204,13 @@
         <v>12.5</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL46" t="n">
         <v>200</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BN46" t="n">
         <v>5.3</v>
@@ -12222,13 +12222,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR46" t="n">
         <v>42</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT46" t="n">
         <v>8.199999999999999</v>
@@ -12240,23 +12240,23 @@
         <v>44</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX46" t="n">
         <v>65</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ46" t="n">
         <v>42</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>2.4</v>
       </c>
       <c r="G47" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H47" t="n">
         <v>3.65</v>
@@ -12302,7 +12302,7 @@
         <v>2.98</v>
       </c>
       <c r="K47" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L47" t="n">
         <v>1.46</v>
@@ -12338,7 +12338,7 @@
         <v>1.34</v>
       </c>
       <c r="W47" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X47" t="n">
         <v>9.199999999999999</v>
@@ -12413,7 +12413,7 @@
         <v>6.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AW47" t="n">
         <v>5.9</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
         <v>5.6</v>
       </c>
       <c r="J49" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
         <v>3.85</v>
@@ -12843,10 +12843,10 @@
         <v>1.76</v>
       </c>
       <c r="V49" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W49" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X49" t="n">
         <v>11</v>
@@ -12966,13 +12966,13 @@
         <v>13</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL49" t="n">
         <v>230</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BN49" t="n">
         <v>5.1</v>
@@ -12984,13 +12984,13 @@
         <v>19</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR49" t="n">
         <v>44</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT49" t="n">
         <v>8.800000000000001</v>
@@ -13002,13 +13002,13 @@
         <v>55</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX49" t="n">
         <v>75</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BZ49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>2.22</v>
       </c>
       <c r="G50" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H50" t="n">
         <v>3.5</v>
@@ -13082,7 +13082,7 @@
         <v>1.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R50" t="n">
         <v>1.22</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
         <v>3.45</v>
       </c>
       <c r="I51" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J51" t="n">
         <v>3.2</v>
@@ -13345,13 +13345,13 @@
         <v>3.2</v>
       </c>
       <c r="T51" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="U51" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="V51" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W51" t="n">
         <v>1.73</v>
@@ -13411,13 +13411,13 @@
         <v>65</v>
       </c>
       <c r="AP51" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR51" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.01</v>
       </c>
       <c r="AS51" t="n">
         <v>1.01</v>
@@ -13429,28 +13429,28 @@
         <v>6</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW51" t="n">
         <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.05</v>
+        <v>10</v>
       </c>
       <c r="AY51" t="n">
         <v>8</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA51" t="n">
         <v>1.01</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD51" t="n">
         <v>1.01</v>
@@ -13459,7 +13459,7 @@
         <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG51" t="n">
         <v>1.01</v>
@@ -13474,13 +13474,13 @@
         <v>950</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN51" t="n">
         <v>5.8</v>
@@ -13492,13 +13492,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ51" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BR51" t="n">
         <v>38</v>
       </c>
       <c r="BS51" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT51" t="n">
         <v>950</v>
@@ -13510,23 +13510,23 @@
         <v>38</v>
       </c>
       <c r="BW51" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX51" t="n">
         <v>55</v>
       </c>
       <c r="BY51" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BZ51" t="n">
         <v>34</v>
       </c>
       <c r="CA51" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -13569,13 +13569,13 @@
         <v>4.9</v>
       </c>
       <c r="J52" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K52" t="n">
         <v>4.4</v>
       </c>
       <c r="L52" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M52" t="n">
         <v>1.06</v>
@@ -13599,13 +13599,13 @@
         <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="U52" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="V52" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W52" t="n">
         <v>1.84</v>
@@ -13665,58 +13665,58 @@
         <v>70</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH52" t="n">
         <v>3.85</v>
@@ -13728,49 +13728,49 @@
         <v>11.5</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BL52" t="n">
         <v>140</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN52" t="n">
         <v>5.3</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BP52" t="n">
         <v>16</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR52" t="n">
         <v>32</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT52" t="n">
         <v>8.6</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV52" t="n">
         <v>40</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX52" t="n">
         <v>55</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ52" t="n">
         <v>0</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
         <v>2.56</v>
       </c>
       <c r="I53" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="J53" t="n">
         <v>2.78</v>
@@ -13853,13 +13853,13 @@
         <v>4.1</v>
       </c>
       <c r="T53" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U53" t="n">
         <v>1.88</v>
       </c>
       <c r="V53" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W53" t="n">
         <v>1.4</v>
@@ -13880,7 +13880,7 @@
         <v>970</v>
       </c>
       <c r="AC53" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD53" t="n">
         <v>970</v>
@@ -13895,7 +13895,7 @@
         <v>970</v>
       </c>
       <c r="AH53" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI53" t="n">
         <v>65</v>
@@ -13925,10 +13925,10 @@
         <v>6.8</v>
       </c>
       <c r="AR53" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT53" t="n">
         <v>8</v>
@@ -13937,40 +13937,40 @@
         <v>5.7</v>
       </c>
       <c r="AV53" t="n">
-        <v>9.6</v>
+        <v>3.85</v>
       </c>
       <c r="AW53" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX53" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AY53" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AZ53" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA53" t="n">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="BB53" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="BC53" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="BE53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BF53" t="n">
         <v>4.8</v>
       </c>
-      <c r="BF53" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG53" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH53" t="n">
         <v>3.25</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-17 09:42:53</t>
+          <t>2026-05-17 12:08:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -863,28 +863,28 @@
         <v>7.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="I2" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
         <v>2.06</v>
@@ -893,7 +893,7 @@
         <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
@@ -902,22 +902,22 @@
         <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="W2" t="n">
         <v>1.16</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" t="n">
         <v>180</v>
@@ -929,13 +929,13 @@
         <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
         <v>950</v>
@@ -944,40 +944,40 @@
         <v>42</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AK2" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AL2" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN2" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AO2" t="n">
         <v>10.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
         <v>6.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS2" t="n">
         <v>12.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
@@ -989,31 +989,31 @@
         <v>14.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG2" t="n">
         <v>7.8</v>
@@ -1022,65 +1022,65 @@
         <v>3.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>11</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>4.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BV2" t="n">
         <v>10.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="CA2" t="n">
         <v>6.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -1111,55 +1111,55 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="G3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="I3" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T3" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V3" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="W3" t="n">
         <v>1.11</v>
@@ -1171,28 +1171,28 @@
         <v>6.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB3" t="n">
         <v>24</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
         <v>170</v>
       </c>
       <c r="AG3" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
         <v>950</v>
@@ -1201,7 +1201,7 @@
         <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="AK3" t="n">
         <v>210</v>
@@ -1213,7 +1213,7 @@
         <v>300</v>
       </c>
       <c r="AN3" t="n">
-        <v>380</v>
+        <v>460</v>
       </c>
       <c r="AO3" t="n">
         <v>14</v>
@@ -1243,98 +1243,98 @@
         <v>14</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BU3" t="n">
         <v>3.2</v>
       </c>
-      <c r="BI3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
+      <c r="BV3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="CA3" t="n">
         <v>7.8</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>30</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
         <v>2.74</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
@@ -1452,7 +1452,7 @@
         <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
         <v>1000</v>
@@ -1473,7 +1473,7 @@
         <v>29</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.85</v>
@@ -1482,7 +1482,7 @@
         <v>3.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AT4" t="n">
         <v>4.2</v>
@@ -1494,19 +1494,19 @@
         <v>3.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX4" t="n">
         <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="BB4" t="n">
         <v>4.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
@@ -1631,7 +1631,7 @@
         <v>6.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
         <v>3.15</v>
@@ -1673,7 +1673,7 @@
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Y5" t="n">
         <v>16.5</v>
@@ -1682,19 +1682,19 @@
         <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AB5" t="n">
         <v>5.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AE5" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
         <v>10.5</v>
@@ -1703,10 +1703,10 @@
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI5" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AJ5" t="n">
         <v>29</v>
@@ -1715,16 +1715,16 @@
         <v>80</v>
       </c>
       <c r="AL5" t="n">
-        <v>240</v>
+        <v>460</v>
       </c>
       <c r="AM5" t="n">
-        <v>410</v>
+        <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>430</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
         <v>5.8</v>
@@ -1733,52 +1733,52 @@
         <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AU5" t="n">
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
         <v>8.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF5" t="n">
         <v>7</v>
       </c>
-      <c r="BD5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="n">
         <v>2.54</v>
@@ -1802,13 +1802,13 @@
         <v>4.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BP5" t="n">
         <v>17</v>
       </c>
       <c r="BQ5" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR5" t="n">
         <v>55</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
@@ -1987,7 +1987,7 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
         <v>6.8</v>
@@ -2023,7 +2023,7 @@
         <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
         <v>6.8</v>
@@ -2038,7 +2038,7 @@
         <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="BJ6" t="n">
         <v>12</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -2136,16 +2136,16 @@
         <v>2.06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J7" t="n">
         <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
@@ -2169,10 +2169,10 @@
         <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
         <v>1.8</v>
@@ -2184,16 +2184,16 @@
         <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
         <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
@@ -2202,40 +2202,40 @@
         <v>10.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AH7" t="n">
         <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="AL7" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>7.4</v>
@@ -2244,13 +2244,13 @@
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AT7" t="n">
         <v>11.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
         <v>8.4</v>
@@ -2259,40 +2259,40 @@
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY7" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC7" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC7" t="n">
-        <v>7</v>
-      </c>
       <c r="BD7" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="n">
         <v>3.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="I8" t="n">
         <v>1.39</v>
       </c>
       <c r="J8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K8" t="n">
         <v>6.4</v>
@@ -2423,16 +2423,16 @@
         <v>2.68</v>
       </c>
       <c r="T8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V8" t="n">
         <v>3.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
         <v>21</v>
@@ -2462,10 +2462,10 @@
         <v>140</v>
       </c>
       <c r="AG8" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AH8" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AI8" t="n">
         <v>55</v>
@@ -2489,28 +2489,28 @@
         <v>6.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR8" t="n">
         <v>3.95</v>
       </c>
-      <c r="AR8" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
         <v>6.6</v>
@@ -2519,28 +2519,28 @@
         <v>6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC8" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC8" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H9" t="n">
         <v>3.35</v>
@@ -2650,10 +2650,10 @@
         <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2665,7 +2665,7 @@
         <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
         <v>2.3</v>
@@ -2680,25 +2680,25 @@
         <v>1.97</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
         <v>8.6</v>
@@ -2707,49 +2707,49 @@
         <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK9" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
@@ -2767,22 +2767,22 @@
         <v>25</v>
       </c>
       <c r="AX9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
         <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
         <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="BD9" t="n">
         <v>28</v>
@@ -2791,7 +2791,7 @@
         <v>42</v>
       </c>
       <c r="BF9" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BG9" t="n">
         <v>27</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.13</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
         <v>1.07</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q10" t="n">
         <v>1.23</v>
@@ -2934,13 +2934,13 @@
         <v>1.28</v>
       </c>
       <c r="U10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
@@ -2949,7 +2949,7 @@
         <v>950</v>
       </c>
       <c r="Z10" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2964,145 +2964,145 @@
         <v>32</v>
       </c>
       <c r="AE10" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
         <v>32</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
         <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
         <v>7.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AP10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA10" t="n">
         <v>5.1</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="BB10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>3.85</v>
       </c>
       <c r="BT10" t="n">
         <v>9</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -3152,10 +3152,10 @@
         <v>6.2</v>
       </c>
       <c r="I11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
         <v>6</v>
@@ -3218,7 +3218,7 @@
         <v>26</v>
       </c>
       <c r="AE11" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="AF11" t="n">
         <v>12.5</v>
@@ -3236,19 +3236,19 @@
         <v>15.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL11" t="n">
         <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="AN11" t="n">
         <v>5.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="AP11" t="n">
         <v>21</v>
@@ -3257,7 +3257,7 @@
         <v>15.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS11" t="n">
         <v>8.6</v>
@@ -3284,7 +3284,7 @@
         <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB11" t="n">
         <v>10.5</v>
@@ -3302,7 +3302,7 @@
         <v>4.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="n">
         <v>5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -3412,10 +3412,10 @@
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -3424,22 +3424,22 @@
         <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P12" t="n">
         <v>1.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R12" t="n">
         <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U12" t="n">
         <v>2.16</v>
@@ -3451,7 +3451,7 @@
         <v>1.31</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y12" t="n">
         <v>11</v>
@@ -3460,10 +3460,10 @@
         <v>14</v>
       </c>
       <c r="AA12" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
         <v>9.199999999999999</v>
@@ -3472,19 +3472,19 @@
         <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
         <v>32</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
         <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AJ12" t="n">
         <v>900</v>
@@ -3499,7 +3499,7 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
@@ -3520,7 +3520,7 @@
         <v>10.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
         <v>8.6</v>
@@ -3538,19 +3538,19 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC12" t="n">
         <v>40</v>
       </c>
       <c r="BD12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE12" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.5</v>
       </c>
       <c r="BF12" t="n">
         <v>38</v>
@@ -3559,7 +3559,7 @@
         <v>13.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI12" t="n">
         <v>2.8</v>
@@ -3568,13 +3568,13 @@
         <v>11.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
         <v>7.2</v>
@@ -3586,13 +3586,13 @@
         <v>38</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT12" t="n">
         <v>5</v>
@@ -3604,13 +3604,13 @@
         <v>18</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G13" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
         <v>6.8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.19</v>
@@ -3675,19 +3675,19 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S13" t="n">
         <v>1.96</v>
@@ -3702,7 +3702,7 @@
         <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3714,10 +3714,10 @@
         <v>160</v>
       </c>
       <c r="AA13" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB13" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
         <v>42</v>
@@ -3732,7 +3732,7 @@
         <v>40</v>
       </c>
       <c r="AG13" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AH13" t="n">
         <v>34</v>
@@ -3741,130 +3741,130 @@
         <v>150</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="AK13" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>70</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AS13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="BN13" t="n">
         <v>5.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.26</v>
+        <v>6.4</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -3935,22 +3935,22 @@
         <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
         <v>2.08</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G15" t="n">
         <v>1.76</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
         <v>6.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.37</v>
@@ -4183,7 +4183,7 @@
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>1.37</v>
@@ -4201,22 +4201,22 @@
         <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
         <v>1.68</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z15" t="n">
         <v>500</v>
@@ -4237,10 +4237,10 @@
         <v>700</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AH15" t="n">
         <v>950</v>
@@ -4249,7 +4249,7 @@
         <v>700</v>
       </c>
       <c r="AJ15" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
         <v>500</v>
@@ -4267,28 +4267,28 @@
         <v>700</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.76</v>
+        <v>7.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="AX15" t="n">
         <v>4.5</v>
@@ -4297,28 +4297,28 @@
         <v>4.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.78</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="BB15" t="n">
         <v>7.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="BE15" t="n">
         <v>14.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="BH15" t="n">
         <v>3.75</v>
@@ -4342,7 +4342,7 @@
         <v>4.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G16" t="n">
         <v>2.88</v>
@@ -4443,28 +4443,28 @@
         <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
         <v>3.65</v>
       </c>
       <c r="T16" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X16" t="n">
         <v>24</v>
@@ -4479,7 +4479,7 @@
         <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
         <v>14</v>
@@ -4512,7 +4512,7 @@
         <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>500</v>
@@ -4521,58 +4521,58 @@
         <v>500</v>
       </c>
       <c r="AP16" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AT16" t="n">
         <v>4.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AW16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY16" t="n">
         <v>5.2</v>
       </c>
-      <c r="AX16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
         <v>21</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="n">
         <v>3.4</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -4682,37 +4682,37 @@
         <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
         <v>1.2</v>
@@ -4727,10 +4727,10 @@
         <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB17" t="n">
         <v>970</v>
@@ -4742,28 +4742,28 @@
         <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AF17" t="n">
         <v>12.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AI17" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ17" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
         <v>970</v>
       </c>
       <c r="AL17" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
@@ -4772,61 +4772,61 @@
         <v>29</v>
       </c>
       <c r="AO17" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT17" t="n">
         <v>9</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AW17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY17" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>5.2</v>
       </c>
       <c r="AZ17" t="n">
         <v>15.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC17" t="n">
         <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH17" t="n">
         <v>4.2</v>
@@ -4838,13 +4838,13 @@
         <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN17" t="n">
         <v>5</v>
@@ -4886,11 +4886,11 @@
         <v>24</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -4921,58 +4921,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
         <v>1.35</v>
       </c>
       <c r="I18" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="J18" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="V18" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>21</v>
@@ -4984,10 +4984,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AB18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AC18" t="n">
         <v>13.5</v>
@@ -4996,7 +4996,7 @@
         <v>10</v>
       </c>
       <c r="AE18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF18" t="n">
         <v>120</v>
@@ -5011,25 +5011,25 @@
         <v>42</v>
       </c>
       <c r="AJ18" t="n">
-        <v>570</v>
+        <v>510</v>
       </c>
       <c r="AK18" t="n">
+        <v>210</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM18" t="n">
         <v>200</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>190</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>220</v>
       </c>
       <c r="AN18" t="n">
         <v>270</v>
       </c>
       <c r="AO18" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.6</v>
@@ -5038,61 +5038,61 @@
         <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
         <v>10.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW18" t="n">
         <v>13</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BE18" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BF18" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BH18" t="n">
         <v>4.8</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BJ18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5101,10 +5101,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
@@ -5116,35 +5116,35 @@
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BW18" t="n">
         <v>4.2</v>
       </c>
       <c r="BX18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CA18" t="n">
         <v>5.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -5181,13 +5181,13 @@
         <v>1.21</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="I19" t="n">
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K19" t="n">
         <v>11</v>
@@ -5199,43 +5199,43 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P19" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="Q19" t="n">
         <v>1.26</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="S19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="U19" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="V19" t="n">
         <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="Y19" t="n">
         <v>950</v>
       </c>
       <c r="Z19" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
@@ -5250,7 +5250,7 @@
         <v>950</v>
       </c>
       <c r="AE19" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AF19" t="n">
         <v>14.5</v>
@@ -5259,76 +5259,76 @@
         <v>17.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AI19" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ19" t="n">
         <v>13</v>
       </c>
       <c r="AK19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AO19" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.2</v>
+        <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF19" t="n">
         <v>2.1</v>
@@ -5340,55 +5340,55 @@
         <v>6.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BJ19" t="n">
         <v>13</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>3.05</v>
+        <v>10</v>
       </c>
       <c r="BN19" t="n">
         <v>4.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BP19" t="n">
         <v>6.4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BR19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS19" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>3.05</v>
+        <v>10</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H20" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="I20" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>3.85</v>
@@ -5453,37 +5453,37 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
         <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U20" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
         <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>90</v>
+        <v>18.5</v>
       </c>
       <c r="Y20" t="n">
         <v>11</v>
@@ -5492,10 +5492,10 @@
         <v>13</v>
       </c>
       <c r="AA20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC20" t="n">
         <v>9</v>
@@ -5522,25 +5522,25 @@
         <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AL20" t="n">
         <v>120</v>
       </c>
       <c r="AM20" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN20" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AO20" t="n">
         <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR20" t="n">
         <v>11</v>
@@ -5555,13 +5555,13 @@
         <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW20" t="n">
         <v>16.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY20" t="n">
         <v>14.5</v>
@@ -5570,19 +5570,19 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD20" t="n">
         <v>42</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
         <v>32</v>
@@ -5600,31 +5600,31 @@
         <v>9.6</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN20" t="n">
         <v>8</v>
       </c>
       <c r="BO20" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
         <v>4.9</v>
@@ -5633,7 +5633,7 @@
         <v>4.1</v>
       </c>
       <c r="BV20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BW20" t="n">
         <v>9.4</v>
@@ -5642,17 +5642,17 @@
         <v>29</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ20" t="n">
         <v>24</v>
       </c>
       <c r="CA20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.39</v>
@@ -5746,7 +5746,7 @@
         <v>16.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AB21" t="n">
         <v>14</v>
@@ -5755,16 +5755,16 @@
         <v>8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF21" t="n">
         <v>65</v>
       </c>
-      <c r="AF21" t="n">
-        <v>28</v>
-      </c>
       <c r="AG21" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
         <v>18</v>
@@ -5773,22 +5773,22 @@
         <v>100</v>
       </c>
       <c r="AJ21" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK21" t="n">
         <v>100</v>
       </c>
       <c r="AL21" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AM21" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AO21" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AP21" t="n">
         <v>12.5</v>
@@ -5800,7 +5800,7 @@
         <v>11.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -5824,22 +5824,22 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG21" t="n">
         <v>14.5</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G22" t="n">
         <v>2.1</v>
@@ -5946,13 +5946,13 @@
         <v>3.85</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
         <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.29</v>
@@ -5964,7 +5964,7 @@
         <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
         <v>2.14</v>
@@ -5979,13 +5979,13 @@
         <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U22" t="n">
         <v>2.24</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
         <v>1.9</v>
@@ -5997,7 +5997,7 @@
         <v>22</v>
       </c>
       <c r="Z22" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -6009,7 +6009,7 @@
         <v>11</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
         <v>55</v>
@@ -6030,13 +6030,13 @@
         <v>28</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="n">
         <v>80</v>
       </c>
       <c r="AM22" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
         <v>14.5</v>
@@ -6048,13 +6048,13 @@
         <v>12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
         <v>9.199999999999999</v>
@@ -6066,7 +6066,7 @@
         <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX22" t="n">
         <v>10</v>
@@ -6078,7 +6078,7 @@
         <v>12.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
         <v>17.5</v>
@@ -6087,16 +6087,16 @@
         <v>15</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF22" t="n">
         <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH22" t="n">
         <v>3.9</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
         <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
         <v>1.67</v>
@@ -6314,7 +6314,7 @@
         <v>3.9</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AV23" t="n">
         <v>4.6</v>
@@ -6347,7 +6347,7 @@
         <v>5.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG23" t="n">
         <v>5.4</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G24" t="n">
         <v>2.36</v>
@@ -6466,13 +6466,13 @@
         <v>1.27</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
         <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P24" t="n">
         <v>2.36</v>
@@ -6484,16 +6484,16 @@
         <v>1.54</v>
       </c>
       <c r="S24" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T24" t="n">
         <v>1.6</v>
       </c>
       <c r="U24" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
         <v>1.73</v>
@@ -6514,7 +6514,7 @@
         <v>14</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
         <v>13.5</v>
@@ -6553,13 +6553,13 @@
         <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AQ24" t="n">
         <v>14.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
         <v>27</v>
@@ -6577,7 +6577,7 @@
         <v>27</v>
       </c>
       <c r="AX24" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
@@ -6586,13 +6586,13 @@
         <v>14</v>
       </c>
       <c r="BA24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB24" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BC24" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD24" t="n">
         <v>26</v>
@@ -6601,7 +6601,7 @@
         <v>30</v>
       </c>
       <c r="BF24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG24" t="n">
         <v>19</v>
@@ -6622,10 +6622,10 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO24" t="n">
         <v>4.3</v>
@@ -6634,13 +6634,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR24" t="n">
         <v>32</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT24" t="n">
         <v>6.8</v>
@@ -6658,7 +6658,7 @@
         <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ24" t="n">
         <v>19</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H25" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.28</v>
@@ -6738,16 +6738,16 @@
         <v>1.52</v>
       </c>
       <c r="S25" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U25" t="n">
         <v>2.28</v>
       </c>
       <c r="V25" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W25" t="n">
         <v>2.28</v>
@@ -6828,7 +6828,7 @@
         <v>17</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -6840,7 +6840,7 @@
         <v>16</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BB25" t="n">
         <v>16</v>
@@ -6852,13 +6852,13 @@
         <v>25</v>
       </c>
       <c r="BE25" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BF25" t="n">
         <v>7.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BH25" t="n">
         <v>4.2</v>
@@ -6888,7 +6888,7 @@
         <v>12</v>
       </c>
       <c r="BQ25" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BR25" t="n">
         <v>24</v>
@@ -6918,11 +6918,11 @@
         <v>17</v>
       </c>
       <c r="CA25" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G26" t="n">
         <v>5.6</v>
@@ -6962,13 +6962,13 @@
         <v>1.73</v>
       </c>
       <c r="I26" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J26" t="n">
         <v>3.8</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.29</v>
@@ -6986,7 +6986,7 @@
         <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R26" t="n">
         <v>1.43</v>
@@ -6995,37 +6995,37 @@
         <v>2.86</v>
       </c>
       <c r="T26" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U26" t="n">
         <v>2.1</v>
       </c>
       <c r="V26" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W26" t="n">
         <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Y26" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Z26" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AA26" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB26" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
       </c>
       <c r="AD26" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>970</v>
@@ -7037,7 +7037,7 @@
         <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AI26" t="n">
         <v>500</v>
@@ -7061,10 +7061,10 @@
         <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR26" t="n">
         <v>8</v>
@@ -7073,43 +7073,43 @@
         <v>12.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="AU26" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA26" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>7</v>
-      </c>
       <c r="BB26" t="n">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BD26" t="n">
         <v>7</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BG26" t="n">
         <v>6.6</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G27" t="n">
         <v>1.91</v>
@@ -7225,7 +7225,7 @@
         <v>4.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -7261,7 +7261,7 @@
         <v>2.08</v>
       </c>
       <c r="X27" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y27" t="n">
         <v>970</v>
@@ -7270,13 +7270,13 @@
         <v>500</v>
       </c>
       <c r="AA27" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD27" t="n">
         <v>950</v>
@@ -7288,10 +7288,10 @@
         <v>20</v>
       </c>
       <c r="AG27" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="AH27" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI27" t="n">
         <v>700</v>
@@ -7315,58 +7315,58 @@
         <v>700</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AQ27" t="n">
         <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU27" t="n">
         <v>7.2</v>
       </c>
       <c r="AV27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX27" t="n">
         <v>5.8</v>
       </c>
-      <c r="AW27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AY27" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF27" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH27" t="n">
         <v>3.5</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
         <v>1.66</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
@@ -7515,10 +7515,10 @@
         <v>1.67</v>
       </c>
       <c r="X28" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y28" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z28" t="n">
         <v>500</v>
@@ -7527,25 +7527,25 @@
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AG28" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AH28" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI28" t="n">
         <v>500</v>
@@ -7578,7 +7578,7 @@
         <v>18.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT28" t="n">
         <v>6.8</v>
@@ -7590,7 +7590,7 @@
         <v>11.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX28" t="n">
         <v>10.5</v>
@@ -7602,25 +7602,25 @@
         <v>15</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BB28" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF28" t="n">
         <v>20</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH28" t="n">
         <v>3.1</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
         <v>1.96</v>
       </c>
       <c r="W29" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X29" t="n">
         <v>38</v>
@@ -7778,7 +7778,7 @@
         <v>16</v>
       </c>
       <c r="AA29" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
         <v>22</v>
@@ -7811,7 +7811,7 @@
         <v>120</v>
       </c>
       <c r="AL29" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AM29" t="n">
         <v>580</v>
@@ -7847,7 +7847,7 @@
         <v>13.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY29" t="n">
         <v>12.5</v>
@@ -7856,7 +7856,7 @@
         <v>12.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB29" t="n">
         <v>6.6</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>2.36</v>
       </c>
       <c r="G30" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H30" t="n">
         <v>3.2</v>
@@ -8017,10 +8017,10 @@
         <v>2.26</v>
       </c>
       <c r="V30" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W30" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X30" t="n">
         <v>18</v>
@@ -8068,13 +8068,13 @@
         <v>36</v>
       </c>
       <c r="AM30" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN30" t="n">
         <v>19.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AP30" t="n">
         <v>12.5</v>
@@ -8098,7 +8098,7 @@
         <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -8113,16 +8113,16 @@
         <v>30</v>
       </c>
       <c r="BB30" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC30" t="n">
         <v>19.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF30" t="n">
         <v>14.5</v>
@@ -8134,7 +8134,7 @@
         <v>3.85</v>
       </c>
       <c r="BI30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ30" t="n">
         <v>9.4</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -8229,16 +8229,16 @@
         <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I31" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>2.48</v>
       </c>
       <c r="K31" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.74</v>
@@ -8247,13 +8247,13 @@
         <v>1.18</v>
       </c>
       <c r="N31" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O31" t="n">
         <v>1.84</v>
       </c>
       <c r="P31" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Q31" t="n">
         <v>3.6</v>
@@ -8268,16 +8268,16 @@
         <v>2.16</v>
       </c>
       <c r="U31" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="V31" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.33</v>
       </c>
       <c r="X31" t="n">
-        <v>970</v>
+        <v>6</v>
       </c>
       <c r="Y31" t="n">
         <v>970</v>
@@ -8286,103 +8286,103 @@
         <v>970</v>
       </c>
       <c r="AA31" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AB31" t="n">
         <v>970</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD31" t="n">
         <v>970</v>
       </c>
       <c r="AE31" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AF31" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AG31" t="n">
         <v>950</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI31" t="n">
-        <v>260</v>
+        <v>540</v>
       </c>
       <c r="AJ31" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AK31" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AL31" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.12</v>
+        <v>3.15</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.11</v>
+        <v>3.85</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.12</v>
+        <v>7</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -8483,13 +8483,13 @@
         <v>2.46</v>
       </c>
       <c r="H32" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I32" t="n">
         <v>4.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K32" t="n">
         <v>3.05</v>
@@ -8504,7 +8504,7 @@
         <v>2.38</v>
       </c>
       <c r="O32" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P32" t="n">
         <v>1.46</v>
@@ -8525,10 +8525,10 @@
         <v>1.7</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X32" t="n">
         <v>7.8</v>
@@ -8549,7 +8549,7 @@
         <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE32" t="n">
         <v>190</v>
@@ -8561,10 +8561,10 @@
         <v>13.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI32" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ32" t="n">
         <v>85</v>
@@ -8573,19 +8573,19 @@
         <v>40</v>
       </c>
       <c r="AL32" t="n">
-        <v>190</v>
+        <v>460</v>
       </c>
       <c r="AM32" t="n">
         <v>500</v>
       </c>
       <c r="AN32" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AO32" t="n">
         <v>500</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ32" t="n">
         <v>8.4</v>
@@ -8594,19 +8594,19 @@
         <v>20</v>
       </c>
       <c r="AS32" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT32" t="n">
         <v>5.9</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV32" t="n">
         <v>13.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
@@ -8618,25 +8618,25 @@
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB32" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BD32" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF32" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH32" t="n">
         <v>2.62</v>
@@ -8660,7 +8660,7 @@
         <v>5.1</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BP32" t="n">
         <v>23</v>
@@ -8678,7 +8678,7 @@
         <v>7.4</v>
       </c>
       <c r="BU32" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BV32" t="n">
         <v>50</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -8731,19 +8731,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="G33" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="H33" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="I33" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K33" t="n">
         <v>3.95</v>
@@ -8755,196 +8755,196 @@
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O33" t="n">
         <v>1.29</v>
       </c>
       <c r="P33" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S33" t="n">
         <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U33" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V33" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W33" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="X33" t="n">
         <v>17.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AA33" t="n">
         <v>100</v>
       </c>
       <c r="AB33" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD33" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE33" t="n">
         <v>60</v>
       </c>
       <c r="AF33" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AG33" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI33" t="n">
         <v>65</v>
       </c>
       <c r="AJ33" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AL33" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
       </c>
       <c r="AN33" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO33" t="n">
         <v>60</v>
       </c>
       <c r="AP33" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF33" t="n">
         <v>11</v>
       </c>
-      <c r="AR33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG33" t="n">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="BH33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ33" t="n">
         <v>9.6</v>
       </c>
       <c r="BK33" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN33" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BP33" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ33" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR33" t="n">
         <v>34</v>
       </c>
       <c r="BS33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT33" t="n">
         <v>7.8</v>
       </c>
-      <c r="BT33" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BU33" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV33" t="n">
         <v>38</v>
       </c>
       <c r="BW33" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX33" t="n">
         <v>50</v>
       </c>
       <c r="BY33" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -8985,52 +8985,52 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G34" t="n">
         <v>3.1</v>
       </c>
       <c r="H34" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I34" t="n">
         <v>2.58</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K34" t="n">
         <v>3.85</v>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M34" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O34" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P34" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="R34" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="U34" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V34" t="n">
         <v>1.63</v>
@@ -9045,7 +9045,7 @@
         <v>12</v>
       </c>
       <c r="Z34" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA34" t="n">
         <v>46</v>
@@ -9063,34 +9063,34 @@
         <v>32</v>
       </c>
       <c r="AF34" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG34" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI34" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AJ34" t="n">
         <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AL34" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AM34" t="n">
         <v>580</v>
       </c>
       <c r="AN34" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AO34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP34" t="n">
         <v>12.5</v>
@@ -9102,13 +9102,13 @@
         <v>13</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="AT34" t="n">
         <v>10</v>
       </c>
       <c r="AU34" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV34" t="n">
         <v>9.4</v>
@@ -9126,43 +9126,43 @@
         <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG34" t="n">
         <v>14.5</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="BJ34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM34" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM34" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BN34" t="n">
         <v>6.4</v>
@@ -9171,16 +9171,16 @@
         <v>4.6</v>
       </c>
       <c r="BP34" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BQ34" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT34" t="n">
         <v>5.8</v>
@@ -9189,26 +9189,26 @@
         <v>4.2</v>
       </c>
       <c r="BV34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW34" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BZ34" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="CA34" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
         <v>1.67</v>
       </c>
       <c r="H35" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I35" t="n">
         <v>7.6</v>
@@ -9263,10 +9263,10 @@
         <v>1.08</v>
       </c>
       <c r="N35" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O35" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P35" t="n">
         <v>1.72</v>
@@ -9275,10 +9275,10 @@
         <v>2.16</v>
       </c>
       <c r="R35" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T35" t="n">
         <v>2.18</v>
@@ -9290,13 +9290,13 @@
         <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X35" t="n">
         <v>19</v>
       </c>
       <c r="Y35" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z35" t="n">
         <v>130</v>
@@ -9308,10 +9308,10 @@
         <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AD35" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AE35" t="n">
         <v>700</v>
@@ -9332,7 +9332,7 @@
         <v>16.5</v>
       </c>
       <c r="AK35" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL35" t="n">
         <v>75</v>
@@ -9341,64 +9341,64 @@
         <v>220</v>
       </c>
       <c r="AN35" t="n">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="AO35" t="n">
         <v>700</v>
       </c>
       <c r="AP35" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT35" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AU35" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV35" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX35" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY35" t="n">
         <v>9</v>
       </c>
       <c r="AZ35" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF35" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH35" t="n">
         <v>3.15</v>
@@ -9410,7 +9410,7 @@
         <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
@@ -9428,13 +9428,13 @@
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>7.8</v>
+        <v>1.92</v>
       </c>
       <c r="BT35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -9520,22 +9520,22 @@
         <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P36" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R36" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S36" t="n">
         <v>2.12</v>
       </c>
       <c r="T36" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U36" t="n">
         <v>1.83</v>
@@ -9562,7 +9562,7 @@
         <v>12</v>
       </c>
       <c r="AC36" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AD36" t="n">
         <v>55</v>
@@ -9580,7 +9580,7 @@
         <v>34</v>
       </c>
       <c r="AI36" t="n">
-        <v>170</v>
+        <v>470</v>
       </c>
       <c r="AJ36" t="n">
         <v>11</v>
@@ -9601,16 +9601,16 @@
         <v>270</v>
       </c>
       <c r="AP36" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AQ36" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AR36" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT36" t="n">
         <v>9.199999999999999</v>
@@ -9619,10 +9619,10 @@
         <v>14</v>
       </c>
       <c r="AV36" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AW36" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX36" t="n">
         <v>7.8</v>
@@ -9631,10 +9631,10 @@
         <v>10</v>
       </c>
       <c r="AZ36" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BA36" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB36" t="n">
         <v>8.4</v>
@@ -9643,16 +9643,16 @@
         <v>12</v>
       </c>
       <c r="BD36" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BE36" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF36" t="n">
         <v>3.35</v>
       </c>
       <c r="BG36" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BH36" t="n">
         <v>5.1</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G37" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H37" t="n">
         <v>3.6</v>
@@ -9783,7 +9783,7 @@
         <v>2.02</v>
       </c>
       <c r="R37" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
         <v>3.75</v>
@@ -9792,16 +9792,16 @@
         <v>1.85</v>
       </c>
       <c r="U37" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V37" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W37" t="n">
         <v>1.81</v>
       </c>
       <c r="X37" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y37" t="n">
         <v>13</v>
@@ -9810,7 +9810,7 @@
         <v>27</v>
       </c>
       <c r="AA37" t="n">
-        <v>900</v>
+        <v>440</v>
       </c>
       <c r="AB37" t="n">
         <v>8.800000000000001</v>
@@ -9819,7 +9819,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD37" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE37" t="n">
         <v>120</v>
@@ -9846,7 +9846,7 @@
         <v>42</v>
       </c>
       <c r="AM37" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN37" t="n">
         <v>21</v>
@@ -9864,7 +9864,7 @@
         <v>21</v>
       </c>
       <c r="AS37" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT37" t="n">
         <v>7.2</v>
@@ -9876,7 +9876,7 @@
         <v>12</v>
       </c>
       <c r="AW37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX37" t="n">
         <v>9.800000000000001</v>
@@ -9888,7 +9888,7 @@
         <v>15.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BB37" t="n">
         <v>22</v>
@@ -9900,13 +9900,13 @@
         <v>30</v>
       </c>
       <c r="BE37" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF37" t="n">
         <v>14.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH37" t="n">
         <v>3.25</v>
@@ -9930,13 +9930,13 @@
         <v>5.1</v>
       </c>
       <c r="BO37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP37" t="n">
         <v>18</v>
       </c>
       <c r="BQ37" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BR37" t="n">
         <v>38</v>
@@ -9948,7 +9948,7 @@
         <v>7</v>
       </c>
       <c r="BU37" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV37" t="n">
         <v>34</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -10004,16 +10004,16 @@
         <v>2.5</v>
       </c>
       <c r="G38" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H38" t="n">
         <v>2.52</v>
       </c>
       <c r="I38" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K38" t="n">
         <v>4.5</v>
@@ -10034,7 +10034,7 @@
         <v>2.26</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R38" t="n">
         <v>1.54</v>
@@ -10049,13 +10049,13 @@
         <v>2.48</v>
       </c>
       <c r="V38" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W38" t="n">
         <v>1.54</v>
       </c>
       <c r="X38" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y38" t="n">
         <v>970</v>
@@ -10082,10 +10082,10 @@
         <v>500</v>
       </c>
       <c r="AG38" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AH38" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI38" t="n">
         <v>500</v>
@@ -10103,67 +10103,67 @@
         <v>580</v>
       </c>
       <c r="AN38" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO38" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AQ38" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.66</v>
+        <v>4.7</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU38" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AW38" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AX38" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="AY38" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AZ38" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="BA38" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB38" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="BC38" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BG38" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BH38" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BI38" t="n">
         <v>3.4</v>
@@ -10172,7 +10172,7 @@
         <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.45</v>
+        <v>6.6</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -10282,16 +10282,16 @@
         <v>1.1</v>
       </c>
       <c r="O39" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P39" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q39" t="n">
         <v>1.56</v>
       </c>
       <c r="R39" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S39" t="n">
         <v>2.42</v>
@@ -10300,7 +10300,7 @@
         <v>1.68</v>
       </c>
       <c r="U39" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V39" t="n">
         <v>1.15</v>
@@ -10309,7 +10309,7 @@
         <v>2.58</v>
       </c>
       <c r="X39" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="Y39" t="n">
         <v>75</v>
@@ -10333,10 +10333,10 @@
         <v>700</v>
       </c>
       <c r="AF39" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="AG39" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AH39" t="n">
         <v>38</v>
@@ -10363,58 +10363,58 @@
         <v>700</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>5</v>
       </c>
-      <c r="AS39" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BA39" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF39" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH39" t="n">
         <v>4.5</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -10518,10 +10518,10 @@
         <v>3.1</v>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="J40" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K40" t="n">
         <v>4</v>
@@ -10578,7 +10578,7 @@
         <v>13</v>
       </c>
       <c r="AC40" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD40" t="n">
         <v>14.5</v>
@@ -10599,10 +10599,10 @@
         <v>42</v>
       </c>
       <c r="AJ40" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK40" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL40" t="n">
         <v>34</v>
@@ -10617,58 +10617,58 @@
         <v>27</v>
       </c>
       <c r="AP40" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ40" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AR40" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT40" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="AV40" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW40" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX40" t="n">
         <v>12.5</v>
       </c>
       <c r="AY40" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AZ40" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="BA40" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB40" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BC40" t="n">
-        <v>17.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD40" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE40" t="n">
         <v>17.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BG40" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="BH40" t="n">
         <v>4</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -10763,16 +10763,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G41" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="H41" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I41" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>3.7</v>
@@ -10787,37 +10787,37 @@
         <v>1.07</v>
       </c>
       <c r="N41" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O41" t="n">
         <v>1.33</v>
       </c>
       <c r="P41" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q41" t="n">
         <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
         <v>3.55</v>
       </c>
       <c r="T41" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U41" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V41" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W41" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X41" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y41" t="n">
         <v>16</v>
@@ -10835,7 +10835,7 @@
         <v>8.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE41" t="n">
         <v>60</v>
@@ -10847,7 +10847,7 @@
         <v>10.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI41" t="n">
         <v>70</v>
@@ -10889,13 +10889,13 @@
         <v>7.8</v>
       </c>
       <c r="AV41" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW41" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="AX41" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY41" t="n">
         <v>9.4</v>
@@ -10907,13 +10907,13 @@
         <v>13</v>
       </c>
       <c r="BB41" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC41" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="BE41" t="n">
         <v>14</v>
@@ -10928,7 +10928,7 @@
         <v>3.55</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ41" t="n">
         <v>10.5</v>
@@ -10937,7 +10937,7 @@
         <v>5.1</v>
       </c>
       <c r="BL41" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM41" t="n">
         <v>9.4</v>
@@ -10952,10 +10952,10 @@
         <v>14.5</v>
       </c>
       <c r="BQ41" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR41" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS41" t="n">
         <v>7.4</v>
@@ -10964,19 +10964,19 @@
         <v>8</v>
       </c>
       <c r="BU41" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BV41" t="n">
         <v>38</v>
       </c>
       <c r="BW41" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX41" t="n">
         <v>48</v>
       </c>
       <c r="BY41" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ41" t="n">
         <v>26</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -11017,13 +11017,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G42" t="n">
         <v>2.12</v>
       </c>
       <c r="H42" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I42" t="n">
         <v>6.8</v>
@@ -11035,7 +11035,7 @@
         <v>3.55</v>
       </c>
       <c r="L42" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M42" t="n">
         <v>1.15</v>
@@ -11047,7 +11047,7 @@
         <v>1.65</v>
       </c>
       <c r="P42" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q42" t="n">
         <v>2.7</v>
@@ -11056,13 +11056,13 @@
         <v>1.13</v>
       </c>
       <c r="S42" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T42" t="n">
         <v>2.42</v>
       </c>
       <c r="U42" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V42" t="n">
         <v>1.17</v>
@@ -11074,16 +11074,16 @@
         <v>13.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z42" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA42" t="n">
         <v>900</v>
       </c>
       <c r="AB42" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AC42" t="n">
         <v>14</v>
@@ -11092,97 +11092,97 @@
         <v>950</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF42" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG42" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AH42" t="n">
         <v>950</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ42" t="n">
         <v>900</v>
       </c>
       <c r="AK42" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AL42" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN42" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP42" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.28</v>
+        <v>3.65</v>
       </c>
       <c r="AS42" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA42" t="n">
         <v>2.38</v>
       </c>
-      <c r="AT42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BB42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG42" t="n">
         <v>2.38</v>
       </c>
-      <c r="BC42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BH42" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
@@ -11206,41 +11206,41 @@
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY42" t="n">
         <v>1.1</v>
       </c>
-      <c r="BR42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS42" t="n">
+      <c r="BZ42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA42" t="n">
         <v>1.1</v>
       </c>
-      <c r="BT42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BV42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BX42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY42" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BZ42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA42" t="n">
-        <v>1.09</v>
-      </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
         <v>3.2</v>
@@ -11280,7 +11280,7 @@
         <v>2.46</v>
       </c>
       <c r="I43" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J43" t="n">
         <v>3.5</v>
@@ -11289,7 +11289,7 @@
         <v>3.7</v>
       </c>
       <c r="L43" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M43" t="n">
         <v>1.06</v>
@@ -11301,70 +11301,70 @@
         <v>1.3</v>
       </c>
       <c r="P43" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R43" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T43" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U43" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V43" t="n">
         <v>1.64</v>
       </c>
       <c r="W43" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X43" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Y43" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z43" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
         <v>900</v>
       </c>
       <c r="AB43" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC43" t="n">
         <v>8</v>
       </c>
       <c r="AD43" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AE43" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF43" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AG43" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AH43" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI43" t="n">
         <v>85</v>
       </c>
       <c r="AJ43" t="n">
-        <v>900</v>
+        <v>280</v>
       </c>
       <c r="AK43" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL43" t="n">
         <v>60</v>
@@ -11373,7 +11373,7 @@
         <v>580</v>
       </c>
       <c r="AN43" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AO43" t="n">
         <v>55</v>
@@ -11382,73 +11382,73 @@
         <v>13</v>
       </c>
       <c r="AQ43" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR43" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="AS43" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT43" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU43" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW43" t="n">
         <v>21</v>
       </c>
       <c r="AX43" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ43" t="n">
         <v>13.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB43" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF43" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC43" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF43" t="n">
+      <c r="BG43" t="n">
         <v>7.8</v>
       </c>
-      <c r="BG43" t="n">
-        <v>7</v>
-      </c>
       <c r="BH43" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BJ43" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK43" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN43" t="n">
         <v>6.2</v>
@@ -11460,41 +11460,41 @@
         <v>26</v>
       </c>
       <c r="BQ43" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR43" t="n">
         <v>38</v>
       </c>
       <c r="BS43" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BT43" t="n">
         <v>5.6</v>
       </c>
       <c r="BU43" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV43" t="n">
         <v>22</v>
       </c>
       <c r="BW43" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX43" t="n">
         <v>36</v>
       </c>
       <c r="BY43" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BZ43" t="n">
         <v>28</v>
       </c>
       <c r="CA43" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -11525,10 +11525,10 @@
         </is>
       </c>
       <c r="F44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G44" t="n">
         <v>1.11</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1.12</v>
       </c>
       <c r="H44" t="n">
         <v>34</v>
@@ -11537,13 +11537,13 @@
         <v>36</v>
       </c>
       <c r="J44" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="K44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L44" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M44" t="n">
         <v>1.02</v>
@@ -11561,28 +11561,28 @@
         <v>1.38</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S44" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="T44" t="n">
         <v>2.68</v>
       </c>
       <c r="U44" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V44" t="n">
         <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="X44" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Y44" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="Z44" t="n">
         <v>660</v>
@@ -11600,7 +11600,7 @@
         <v>120</v>
       </c>
       <c r="AE44" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
         <v>7.8</v>
@@ -11609,16 +11609,16 @@
         <v>16</v>
       </c>
       <c r="AH44" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AI44" t="n">
         <v>430</v>
       </c>
       <c r="AJ44" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AK44" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL44" t="n">
         <v>65</v>
@@ -11633,16 +11633,16 @@
         <v>990</v>
       </c>
       <c r="AP44" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AQ44" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AR44" t="n">
         <v>170</v>
       </c>
       <c r="AS44" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AT44" t="n">
         <v>12</v>
@@ -11651,13 +11651,13 @@
         <v>29</v>
       </c>
       <c r="AV44" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AW44" t="n">
         <v>260</v>
       </c>
       <c r="AX44" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY44" t="n">
         <v>15</v>
@@ -11669,7 +11669,7 @@
         <v>200</v>
       </c>
       <c r="BB44" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC44" t="n">
         <v>14</v>
@@ -11678,13 +11678,13 @@
         <v>55</v>
       </c>
       <c r="BE44" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BF44" t="n">
         <v>2.5</v>
       </c>
       <c r="BG44" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="BH44" t="n">
         <v>5.8</v>
@@ -11699,10 +11699,10 @@
         <v>9</v>
       </c>
       <c r="BL44" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="BM44" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BN44" t="n">
         <v>3.8</v>
@@ -11729,7 +11729,7 @@
         <v>11</v>
       </c>
       <c r="BV44" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="BW44" t="n">
         <v>17.5</v>
@@ -11744,11 +11744,11 @@
         <v>5.8</v>
       </c>
       <c r="CA44" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11827,7 @@
         <v>2.74</v>
       </c>
       <c r="V45" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W45" t="n">
         <v>1.64</v>
@@ -11836,10 +11836,10 @@
         <v>29</v>
       </c>
       <c r="Y45" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z45" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA45" t="n">
         <v>48</v>
@@ -11857,7 +11857,7 @@
         <v>26</v>
       </c>
       <c r="AF45" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG45" t="n">
         <v>14.5</v>
@@ -11872,7 +11872,7 @@
         <v>36</v>
       </c>
       <c r="AK45" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL45" t="n">
         <v>28</v>
@@ -11896,7 +11896,7 @@
         <v>20</v>
       </c>
       <c r="AS45" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT45" t="n">
         <v>13</v>
@@ -11908,7 +11908,7 @@
         <v>10</v>
       </c>
       <c r="AW45" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AX45" t="n">
         <v>18</v>
@@ -11920,10 +11920,10 @@
         <v>11</v>
       </c>
       <c r="BA45" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BB45" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BC45" t="n">
         <v>19.5</v>
@@ -11932,7 +11932,7 @@
         <v>20</v>
       </c>
       <c r="BE45" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF45" t="n">
         <v>9.199999999999999</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -12057,13 +12057,13 @@
         <v>1.02</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O46" t="n">
         <v>1.15</v>
       </c>
       <c r="P46" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="Q46" t="n">
         <v>1.46</v>
@@ -12072,13 +12072,13 @@
         <v>1.77</v>
       </c>
       <c r="S46" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T46" t="n">
         <v>1.6</v>
       </c>
       <c r="U46" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V46" t="n">
         <v>1.15</v>
@@ -12093,43 +12093,43 @@
         <v>950</v>
       </c>
       <c r="Z46" t="n">
-        <v>170</v>
+        <v>420</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AC46" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="AD46" t="n">
         <v>950</v>
       </c>
       <c r="AE46" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="AF46" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG46" t="n">
         <v>20</v>
       </c>
       <c r="AH46" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AI46" t="n">
-        <v>170</v>
+        <v>300</v>
       </c>
       <c r="AJ46" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AK46" t="n">
         <v>970</v>
       </c>
       <c r="AL46" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AM46" t="n">
         <v>75</v>
@@ -12138,16 +12138,16 @@
         <v>15</v>
       </c>
       <c r="AO46" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="AP46" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AQ46" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS46" t="n">
         <v>4.2</v>
@@ -12174,7 +12174,7 @@
         <v>9.6</v>
       </c>
       <c r="BA46" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB46" t="n">
         <v>12</v>
@@ -12183,16 +12183,16 @@
         <v>10.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BE46" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF46" t="n">
         <v>4.3</v>
       </c>
       <c r="BG46" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH46" t="n">
         <v>20</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>1.48</v>
       </c>
       <c r="G47" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H47" t="n">
         <v>5.9</v>
@@ -12308,7 +12308,7 @@
         <v>1.23</v>
       </c>
       <c r="M47" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N47" t="n">
         <v>5.9</v>
@@ -12317,13 +12317,13 @@
         <v>1.16</v>
       </c>
       <c r="P47" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q47" t="n">
         <v>1.48</v>
       </c>
       <c r="R47" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S47" t="n">
         <v>2.18</v>
@@ -12338,55 +12338,55 @@
         <v>1.16</v>
       </c>
       <c r="W47" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X47" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="Y47" t="n">
         <v>950</v>
       </c>
       <c r="Z47" t="n">
-        <v>160</v>
+        <v>350</v>
       </c>
       <c r="AA47" t="n">
         <v>180</v>
       </c>
       <c r="AB47" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC47" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="AD47" t="n">
         <v>950</v>
       </c>
       <c r="AE47" t="n">
-        <v>190</v>
+        <v>400</v>
       </c>
       <c r="AF47" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AH47" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AI47" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="AJ47" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AK47" t="n">
         <v>970</v>
       </c>
       <c r="AL47" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AM47" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN47" t="n">
         <v>5.6</v>
@@ -12398,25 +12398,25 @@
         <v>14</v>
       </c>
       <c r="AQ47" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS47" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT47" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AU47" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AV47" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AW47" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX47" t="n">
         <v>9.199999999999999</v>
@@ -12425,10 +12425,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ47" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB47" t="n">
         <v>11.5</v>
@@ -12437,16 +12437,16 @@
         <v>11</v>
       </c>
       <c r="BD47" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BE47" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BF47" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BG47" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH47" t="n">
         <v>4.9</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
         <v>5.1</v>
       </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L48" t="n">
         <v>1.22</v>
@@ -12610,7 +12610,7 @@
         <v>36</v>
       </c>
       <c r="AC48" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD48" t="n">
         <v>11</v>
@@ -12640,7 +12640,7 @@
         <v>60</v>
       </c>
       <c r="AM48" t="n">
-        <v>580</v>
+        <v>260</v>
       </c>
       <c r="AN48" t="n">
         <v>55</v>
@@ -12649,7 +12649,7 @@
         <v>5.8</v>
       </c>
       <c r="AP48" t="n">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="AQ48" t="n">
         <v>10.5</v>
@@ -12673,10 +12673,10 @@
         <v>11</v>
       </c>
       <c r="AX48" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY48" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AZ48" t="n">
         <v>15</v>
@@ -12685,16 +12685,16 @@
         <v>18.5</v>
       </c>
       <c r="BB48" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD48" t="n">
         <v>7</v>
       </c>
-      <c r="BC48" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE48" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BF48" t="n">
         <v>34</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -12849,13 +12849,13 @@
         <v>1.92</v>
       </c>
       <c r="X49" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y49" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Z49" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AA49" t="n">
         <v>900</v>
@@ -12864,43 +12864,43 @@
         <v>7.4</v>
       </c>
       <c r="AC49" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD49" t="n">
         <v>950</v>
       </c>
       <c r="AE49" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AF49" t="n">
         <v>19</v>
       </c>
       <c r="AG49" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AI49" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AJ49" t="n">
         <v>900</v>
       </c>
       <c r="AK49" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AL49" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="AM49" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN49" t="n">
         <v>55</v>
       </c>
       <c r="AO49" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AP49" t="n">
         <v>8</v>
@@ -12909,52 +12909,52 @@
         <v>10.5</v>
       </c>
       <c r="AR49" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS49" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT49" t="n">
         <v>5.6</v>
       </c>
       <c r="AU49" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AV49" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX49" t="n">
         <v>8.4</v>
       </c>
       <c r="AY49" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ49" t="n">
         <v>17</v>
       </c>
       <c r="BA49" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE49" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG49" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>8.4</v>
       </c>
       <c r="BH49" t="n">
         <v>3.05</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -13052,19 +13052,19 @@
         <v>1.97</v>
       </c>
       <c r="G50" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H50" t="n">
         <v>4.3</v>
       </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J50" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K50" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L50" t="n">
         <v>1.49</v>
@@ -13082,10 +13082,10 @@
         <v>1.67</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R50" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S50" t="n">
         <v>4.3</v>
@@ -13100,7 +13100,7 @@
         <v>1.26</v>
       </c>
       <c r="W50" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X50" t="n">
         <v>12</v>
@@ -13154,7 +13154,7 @@
         <v>21</v>
       </c>
       <c r="AO50" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AP50" t="n">
         <v>8.6</v>
@@ -13163,7 +13163,7 @@
         <v>11.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AS50" t="n">
         <v>9.199999999999999</v>
@@ -13178,7 +13178,7 @@
         <v>16</v>
       </c>
       <c r="AW50" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AX50" t="n">
         <v>9.6</v>
@@ -13190,7 +13190,7 @@
         <v>16</v>
       </c>
       <c r="BA50" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BB50" t="n">
         <v>21</v>
@@ -13220,13 +13220,13 @@
         <v>11</v>
       </c>
       <c r="BK50" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN50" t="n">
         <v>4.6</v>
@@ -13235,19 +13235,19 @@
         <v>3.65</v>
       </c>
       <c r="BP50" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ50" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR50" t="n">
         <v>36</v>
       </c>
       <c r="BS50" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT50" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU50" t="n">
         <v>6</v>
@@ -13268,11 +13268,11 @@
         <v>36</v>
       </c>
       <c r="CA50" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -13312,10 +13312,10 @@
         <v>3.75</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J51" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="K51" t="n">
         <v>3.25</v>
@@ -13330,13 +13330,13 @@
         <v>2.68</v>
       </c>
       <c r="O51" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P51" t="n">
         <v>1.57</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R51" t="n">
         <v>1.2</v>
@@ -13348,7 +13348,7 @@
         <v>2.06</v>
       </c>
       <c r="U51" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V51" t="n">
         <v>1.33</v>
@@ -13357,7 +13357,7 @@
         <v>1.69</v>
       </c>
       <c r="X51" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="Y51" t="n">
         <v>13</v>
@@ -13378,7 +13378,7 @@
         <v>20</v>
       </c>
       <c r="AE51" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AF51" t="n">
         <v>16.5</v>
@@ -13402,7 +13402,7 @@
         <v>70</v>
       </c>
       <c r="AM51" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN51" t="n">
         <v>38</v>
@@ -13417,10 +13417,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR51" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS51" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>6</v>
       </c>
       <c r="AT51" t="n">
         <v>6.6</v>
@@ -13432,7 +13432,7 @@
         <v>14.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX51" t="n">
         <v>11.5</v>
@@ -13444,25 +13444,25 @@
         <v>19.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BB51" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC51" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE51" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BH51" t="n">
         <v>2.78</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -13557,22 +13557,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="G52" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H52" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="I52" t="n">
         <v>990</v>
       </c>
       <c r="J52" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K52" t="n">
-        <v>5.1</v>
+        <v>500</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13581,13 +13581,13 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O52" t="n">
         <v>1.2</v>
       </c>
       <c r="P52" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q52" t="n">
         <v>1.19</v>
@@ -13605,10 +13605,10 @@
         <v>1.11</v>
       </c>
       <c r="V52" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
         <v>3.85</v>
       </c>
       <c r="L53" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M53" t="n">
         <v>1.11</v>
@@ -13931,7 +13931,7 @@
         <v>5</v>
       </c>
       <c r="AT53" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU53" t="n">
         <v>6.4</v>
@@ -13955,10 +13955,10 @@
         <v>4.9</v>
       </c>
       <c r="BB53" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BC53" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BD53" t="n">
         <v>4.9</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
         <v>2.22</v>
       </c>
       <c r="G54" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="H54" t="n">
         <v>3.55</v>
@@ -14095,7 +14095,7 @@
         <v>1.45</v>
       </c>
       <c r="P54" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q54" t="n">
         <v>2.32</v>
@@ -14104,7 +14104,7 @@
         <v>1.22</v>
       </c>
       <c r="S54" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="T54" t="n">
         <v>1.96</v>
@@ -14173,22 +14173,22 @@
         <v>85</v>
       </c>
       <c r="AP54" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ54" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR54" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS54" t="n">
         <v>4.9</v>
       </c>
       <c r="AT54" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU54" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>5.8</v>
       </c>
       <c r="AV54" t="n">
         <v>13.5</v>
@@ -14197,22 +14197,22 @@
         <v>4.9</v>
       </c>
       <c r="AX54" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY54" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ54" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA54" t="n">
         <v>4.9</v>
       </c>
       <c r="BB54" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC54" t="n">
         <v>5</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>5.1</v>
       </c>
       <c r="BD54" t="n">
         <v>4.9</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
         <v>1.3</v>
       </c>
       <c r="S55" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T55" t="n">
         <v>1.78</v>
@@ -14379,7 +14379,7 @@
         <v>15.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA55" t="n">
         <v>85</v>
@@ -14391,7 +14391,7 @@
         <v>9.4</v>
       </c>
       <c r="AD55" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE55" t="n">
         <v>55</v>
@@ -14433,16 +14433,16 @@
         <v>9.6</v>
       </c>
       <c r="AR55" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AS55" t="n">
         <v>4.1</v>
       </c>
       <c r="AT55" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU55" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV55" t="n">
         <v>3.7</v>
@@ -14463,16 +14463,16 @@
         <v>4.1</v>
       </c>
       <c r="BB55" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="BC55" t="n">
-        <v>18</v>
+        <v>4.1</v>
       </c>
       <c r="BD55" t="n">
         <v>4.1</v>
       </c>
       <c r="BE55" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF55" t="n">
         <v>14.5</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14627,7 @@
         <v>1.84</v>
       </c>
       <c r="X56" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y56" t="n">
         <v>18</v>
@@ -14660,7 +14660,7 @@
         <v>22</v>
       </c>
       <c r="AI56" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ56" t="n">
         <v>27</v>
@@ -14678,61 +14678,61 @@
         <v>16.5</v>
       </c>
       <c r="AO56" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP56" t="n">
         <v>4</v>
       </c>
       <c r="AQ56" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF56" t="n">
         <v>4</v>
       </c>
-      <c r="AR56" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS56" t="n">
+      <c r="BG56" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG56" t="n">
-        <v>4.8</v>
       </c>
       <c r="BH56" t="n">
         <v>3.75</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -14830,16 +14830,16 @@
         <v>3.35</v>
       </c>
       <c r="G57" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H57" t="n">
         <v>2.46</v>
       </c>
       <c r="I57" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K57" t="n">
         <v>3.4</v>
@@ -14890,7 +14890,7 @@
         <v>970</v>
       </c>
       <c r="AA57" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AB57" t="n">
         <v>970</v>
@@ -14902,7 +14902,7 @@
         <v>970</v>
       </c>
       <c r="AE57" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF57" t="n">
         <v>25</v>
@@ -14917,7 +14917,7 @@
         <v>60</v>
       </c>
       <c r="AJ57" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK57" t="n">
         <v>55</v>
@@ -14932,28 +14932,28 @@
         <v>65</v>
       </c>
       <c r="AO57" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP57" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR57" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT57" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU57" t="n">
         <v>6</v>
       </c>
       <c r="AV57" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW57" t="n">
         <v>5.7</v>
@@ -14962,7 +14962,7 @@
         <v>5.3</v>
       </c>
       <c r="AY57" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AZ57" t="n">
         <v>5.1</v>
@@ -14983,7 +14983,7 @@
         <v>6.4</v>
       </c>
       <c r="BF57" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG57" t="n">
         <v>5.7</v>
@@ -14998,31 +14998,31 @@
         <v>11</v>
       </c>
       <c r="BK57" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL57" t="n">
         <v>1000</v>
       </c>
       <c r="BM57" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN57" t="n">
         <v>6.6</v>
       </c>
       <c r="BO57" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP57" t="n">
         <v>1000</v>
       </c>
       <c r="BQ57" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR57" t="n">
         <v>1000</v>
       </c>
       <c r="BS57" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT57" t="n">
         <v>5.5</v>
@@ -15040,17 +15040,17 @@
         <v>1000</v>
       </c>
       <c r="BY57" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ57" t="n">
         <v>1000</v>
       </c>
       <c r="CA57" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>
@@ -15081,19 +15081,19 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G58" t="n">
         <v>990</v>
       </c>
       <c r="H58" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I58" t="n">
         <v>990</v>
       </c>
       <c r="J58" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K58" t="n">
         <v>500</v>
@@ -15105,13 +15105,13 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="O58" t="n">
         <v>1.33</v>
       </c>
       <c r="P58" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q58" t="n">
         <v>1.33</v>
@@ -15120,7 +15120,7 @@
         <v>1.18</v>
       </c>
       <c r="S58" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="T58" t="n">
         <v>1.11</v>
@@ -15132,7 +15132,7 @@
         <v>1.01</v>
       </c>
       <c r="W58" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X58" t="n">
         <v>1000</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-17 19:00:56</t>
+          <t>2026-05-17 21:14:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB58"/>
+  <dimension ref="A1:CB59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,16 +863,16 @@
         <v>7.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.38</v>
@@ -881,7 +881,7 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
@@ -890,7 +890,7 @@
         <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
@@ -902,10 +902,10 @@
         <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="W2" t="n">
         <v>1.16</v>
@@ -923,13 +923,13 @@
         <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AC2" t="n">
         <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE2" t="n">
         <v>34</v>
@@ -938,13 +938,13 @@
         <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AH2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
         <v>700</v>
@@ -962,7 +962,7 @@
         <v>700</v>
       </c>
       <c r="AO2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP2" t="n">
         <v>15</v>
@@ -974,22 +974,22 @@
         <v>8.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
         <v>19</v>
@@ -998,46 +998,46 @@
         <v>10</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="BB2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD2" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BE2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG2" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
         <v>3.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BO2" t="n">
         <v>5.8</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT2" t="n">
         <v>4.2</v>
@@ -1070,17 +1070,17 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>19.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
         <v>10.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I3" t="n">
         <v>1.55</v>
@@ -1126,7 +1126,7 @@
         <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.44</v>
@@ -1144,7 +1144,7 @@
         <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
         <v>1.27</v>
@@ -1177,7 +1177,7 @@
         <v>13.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC3" t="n">
         <v>11</v>
@@ -1201,7 +1201,7 @@
         <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="AK3" t="n">
         <v>210</v>
@@ -1213,10 +1213,10 @@
         <v>300</v>
       </c>
       <c r="AN3" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AO3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
         <v>8.800000000000001</v>
@@ -1243,31 +1243,31 @@
         <v>14</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.6</v>
+        <v>130</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BG3" t="n">
         <v>8.800000000000001</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="BN3" t="n">
         <v>13</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="G4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="I4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>1.28</v>
@@ -1395,10 +1395,10 @@
         <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
         <v>1.45</v>
@@ -1410,13 +1410,13 @@
         <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V4" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
@@ -1425,7 +1425,7 @@
         <v>27</v>
       </c>
       <c r="Z4" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
@@ -1440,10 +1440,10 @@
         <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AG4" t="n">
         <v>950</v>
@@ -1473,40 +1473,40 @@
         <v>29</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.1</v>
+        <v>2.64</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="AR4" t="n">
         <v>3.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="AT4" t="n">
         <v>4.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AW4" t="n">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="AX4" t="n">
         <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="BB4" t="n">
         <v>4.2</v>
@@ -1518,13 +1518,13 @@
         <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="BF4" t="n">
         <v>4.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="n">
         <v>4.1</v>
@@ -1560,10 +1560,10 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="BT4" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="BU4" t="n">
         <v>2.96</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.92</v>
       </c>
       <c r="G5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
@@ -1631,13 +1631,13 @@
         <v>6.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K5" t="n">
         <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="M5" t="n">
         <v>1.17</v>
@@ -1670,7 +1670,7 @@
         <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X5" t="n">
         <v>6.8</v>
@@ -1679,7 +1679,7 @@
         <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AA5" t="n">
         <v>700</v>
@@ -1697,7 +1697,7 @@
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
@@ -1709,7 +1709,7 @@
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
         <v>80</v>
@@ -1721,7 +1721,7 @@
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
@@ -1733,22 +1733,22 @@
         <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX5" t="n">
         <v>8.6</v>
@@ -1757,28 +1757,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH5" t="n">
         <v>2.54</v>
@@ -1796,13 +1796,13 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN5" t="n">
         <v>4.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BP5" t="n">
         <v>17</v>
@@ -1838,11 +1838,11 @@
         <v>65</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -1891,19 +1891,19 @@
         <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
         <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
         <v>2.36</v>
@@ -1918,7 +1918,7 @@
         <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
         <v>1.23</v>
@@ -1978,7 +1978,7 @@
         <v>23</v>
       </c>
       <c r="AO6" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>9</v>
@@ -2023,7 +2023,7 @@
         <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
         <v>6.8</v>
@@ -2044,7 +2044,7 @@
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2068,7 +2068,7 @@
         <v>42</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
         <v>9</v>
@@ -2086,7 +2086,7 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>36</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
         <v>3.7</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J7" t="n">
         <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
@@ -2154,7 +2154,7 @@
         <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
         <v>1.78</v>
@@ -2166,22 +2166,22 @@
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
         <v>1.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
         <v>9</v>
@@ -2190,7 +2190,7 @@
         <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>21</v>
@@ -2208,19 +2208,19 @@
         <v>85</v>
       </c>
       <c r="AG7" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AI7" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
         <v>500</v>
@@ -2229,10 +2229,10 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
@@ -2253,13 +2253,13 @@
         <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW7" t="n">
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AY7" t="n">
         <v>12.5</v>
@@ -2268,43 +2268,43 @@
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="n">
         <v>3.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
         <v>7.4</v>
@@ -2316,7 +2316,7 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2331,16 +2331,16 @@
         <v>3.85</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I8" t="n">
         <v>1.39</v>
       </c>
       <c r="J8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K8" t="n">
         <v>6.4</v>
@@ -2411,7 +2411,7 @@
         <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
         <v>1.71</v>
@@ -2423,13 +2423,13 @@
         <v>2.68</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.1</v>
@@ -2483,7 +2483,7 @@
         <v>240</v>
       </c>
       <c r="AN8" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AO8" t="n">
         <v>6.2</v>
@@ -2507,7 +2507,7 @@
         <v>4.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW8" t="n">
         <v>5</v>
@@ -2516,7 +2516,7 @@
         <v>6.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
         <v>5.9</v>
@@ -2537,10 +2537,10 @@
         <v>6.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
         <v>3.35</v>
@@ -2665,7 +2665,7 @@
         <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q9" t="n">
         <v>2.3</v>
@@ -2680,13 +2680,13 @@
         <v>1.97</v>
       </c>
       <c r="U9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X9" t="n">
         <v>10.5</v>
@@ -2698,7 +2698,7 @@
         <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB9" t="n">
         <v>8.6</v>
@@ -2728,7 +2728,7 @@
         <v>36</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
@@ -2806,13 +2806,13 @@
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN9" t="n">
         <v>5.2</v>
@@ -2821,16 +2821,16 @@
         <v>3.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR9" t="n">
         <v>44</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT9" t="n">
         <v>6.6</v>
@@ -2842,23 +2842,23 @@
         <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>44</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
         <v>2.8</v>
@@ -2991,61 +2991,61 @@
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.6</v>
+        <v>3.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.6</v>
+        <v>3.35</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA10" t="n">
         <v>5.2</v>
       </c>
-      <c r="AX10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BB10" t="n">
-        <v>5.9</v>
+        <v>3.45</v>
       </c>
       <c r="BC10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.2</v>
       </c>
-      <c r="BD10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE10" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG10" t="n">
         <v>3.45</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>1.55</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.21</v>
@@ -3173,13 +3173,13 @@
         <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="Q11" t="n">
         <v>1.49</v>
       </c>
       <c r="R11" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S11" t="n">
         <v>2.22</v>
@@ -3188,7 +3188,7 @@
         <v>1.66</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
@@ -3203,7 +3203,7 @@
         <v>75</v>
       </c>
       <c r="Z11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA11" t="n">
         <v>190</v>
@@ -3239,13 +3239,13 @@
         <v>15</v>
       </c>
       <c r="AL11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AM11" t="n">
         <v>260</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AO11" t="n">
         <v>170</v>
@@ -3257,10 +3257,10 @@
         <v>15.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT11" t="n">
         <v>9.4</v>
@@ -3272,7 +3272,7 @@
         <v>18</v>
       </c>
       <c r="AW11" t="n">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="AX11" t="n">
         <v>8.6</v>
@@ -3284,7 +3284,7 @@
         <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB11" t="n">
         <v>10.5</v>
@@ -3302,7 +3302,7 @@
         <v>4.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="n">
         <v>5</v>
@@ -3314,13 +3314,13 @@
         <v>10</v>
       </c>
       <c r="BK11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN11" t="n">
         <v>4.7</v>
@@ -3329,7 +3329,7 @@
         <v>3.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.9</v>
@@ -3338,7 +3338,7 @@
         <v>19.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT11" t="n">
         <v>11</v>
@@ -3350,13 +3350,13 @@
         <v>48</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX11" t="n">
         <v>44</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>3.6</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H12" t="n">
         <v>2.06</v>
@@ -3421,16 +3421,16 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R12" t="n">
         <v>1.34</v>
@@ -3445,10 +3445,10 @@
         <v>2.16</v>
       </c>
       <c r="V12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X12" t="n">
         <v>14.5</v>
@@ -3466,10 +3466,10 @@
         <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE12" t="n">
         <v>42</v>
@@ -3493,7 +3493,7 @@
         <v>60</v>
       </c>
       <c r="AL12" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
@@ -3508,7 +3508,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR12" t="n">
         <v>10</v>
@@ -3523,7 +3523,7 @@
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
         <v>18</v>
@@ -3538,22 +3538,22 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB12" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB12" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC12" t="n">
-        <v>40</v>
+        <v>6.6</v>
       </c>
       <c r="BD12" t="n">
         <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
         <v>13.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -3651,73 +3651,73 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="G13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="S13" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="U13" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="X13" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y13" t="n">
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC13" t="n">
         <v>42</v>
@@ -3726,7 +3726,7 @@
         <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
         <v>40</v>
@@ -3735,70 +3735,70 @@
         <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
         <v>180</v>
       </c>
       <c r="AK13" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
         <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW13" t="n">
         <v>6.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="AZ13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC13" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5</v>
       </c>
       <c r="BD13" t="n">
         <v>5.8</v>
@@ -3807,49 +3807,49 @@
         <v>6.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BG13" t="n">
         <v>6.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO13" t="n">
         <v>3.25</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU13" t="n">
         <v>4.4</v>
@@ -3858,13 +3858,13 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
@@ -3929,28 +3929,28 @@
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="T14" t="n">
         <v>1.73</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -3959,7 +3959,7 @@
         <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
         <v>950</v>
@@ -3971,7 +3971,7 @@
         <v>230</v>
       </c>
       <c r="AB14" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
         <v>42</v>
@@ -3986,7 +3986,7 @@
         <v>19</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
@@ -3995,13 +3995,13 @@
         <v>200</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="AK14" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -4013,58 +4013,58 @@
         <v>100</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV14" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>6</v>
-      </c>
       <c r="AW14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="n">
         <v>4.9</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H15" t="n">
         <v>5.4</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
         <v>3.85</v>
@@ -4183,7 +4183,7 @@
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.37</v>
@@ -4204,13 +4204,13 @@
         <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
@@ -4237,7 +4237,7 @@
         <v>700</v>
       </c>
       <c r="AF15" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
         <v>36</v>
@@ -4276,7 +4276,7 @@
         <v>7.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT15" t="n">
         <v>4.1</v>
@@ -4288,7 +4288,7 @@
         <v>6.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX15" t="n">
         <v>4.5</v>
@@ -4300,7 +4300,7 @@
         <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB15" t="n">
         <v>7.6</v>
@@ -4318,7 +4318,7 @@
         <v>5.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH15" t="n">
         <v>3.75</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>2.44</v>
       </c>
       <c r="G16" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="H16" t="n">
         <v>2.98</v>
@@ -4458,13 +4458,13 @@
         <v>1.76</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V16" t="n">
         <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X16" t="n">
         <v>24</v>
@@ -4524,7 +4524,7 @@
         <v>9.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="AR16" t="n">
         <v>6.2</v>
@@ -4542,7 +4542,7 @@
         <v>5.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="AX16" t="n">
         <v>5.9</v>
@@ -4560,7 +4560,7 @@
         <v>4.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BD16" t="n">
         <v>4.8</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN16" t="n">
         <v>5.9</v>
@@ -4608,7 +4608,7 @@
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT16" t="n">
         <v>6.4</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.31</v>
@@ -4694,7 +4694,7 @@
         <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P17" t="n">
         <v>2.26</v>
@@ -4703,7 +4703,7 @@
         <v>1.67</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -4721,7 +4721,7 @@
         <v>2.4</v>
       </c>
       <c r="X17" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="Y17" t="n">
         <v>950</v>
@@ -4748,10 +4748,10 @@
         <v>12.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="AH17" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AI17" t="n">
         <v>700</v>
@@ -4763,28 +4763,28 @@
         <v>970</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
         <v>700</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT17" t="n">
         <v>9</v>
@@ -4793,13 +4793,13 @@
         <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW17" t="n">
         <v>6.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AY17" t="n">
         <v>7.8</v>
@@ -4811,22 +4811,22 @@
         <v>6.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC17" t="n">
         <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE17" t="n">
         <v>7</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH17" t="n">
         <v>4.2</v>
@@ -4838,7 +4838,7 @@
         <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4921,31 +4921,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" t="n">
         <v>1.35</v>
       </c>
       <c r="I18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
@@ -4966,13 +4966,13 @@
         <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V18" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
         <v>21</v>
@@ -4987,16 +4987,16 @@
         <v>11</v>
       </c>
       <c r="AB18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AC18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF18" t="n">
         <v>120</v>
@@ -5011,13 +5011,13 @@
         <v>42</v>
       </c>
       <c r="AJ18" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="AK18" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AL18" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AM18" t="n">
         <v>200</v>
@@ -5026,7 +5026,7 @@
         <v>270</v>
       </c>
       <c r="AO18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AP18" t="n">
         <v>16.5</v>
@@ -5041,58 +5041,58 @@
         <v>6</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW18" t="n">
         <v>13</v>
       </c>
       <c r="AX18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
         <v>19</v>
       </c>
       <c r="BA18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE18" t="n">
         <v>12.5</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BF18" t="n">
         <v>12.5</v>
       </c>
-      <c r="BC18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>17</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>15</v>
-      </c>
       <c r="BG18" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ18" t="n">
         <v>15.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5101,10 +5101,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BO18" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
@@ -5119,32 +5119,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BU18" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BV18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BW18" t="n">
         <v>4.2</v>
       </c>
       <c r="BX18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA18" t="n">
         <v>5.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>11</v>
@@ -5214,7 +5214,7 @@
         <v>2.26</v>
       </c>
       <c r="S19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="T19" t="n">
         <v>1.82</v>
@@ -5226,7 +5226,7 @@
         <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="X19" t="n">
         <v>75</v>
@@ -5241,7 +5241,7 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC19" t="n">
         <v>29</v>
@@ -5253,19 +5253,19 @@
         <v>260</v>
       </c>
       <c r="AF19" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AI19" t="n">
         <v>170</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AK19" t="n">
         <v>16.5</v>
@@ -5283,16 +5283,16 @@
         <v>220</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19" t="n">
         <v>13</v>
@@ -5301,10 +5301,10 @@
         <v>20</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -5316,10 +5316,10 @@
         <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="BC19" t="n">
         <v>11.5</v>
@@ -5328,7 +5328,7 @@
         <v>20</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF19" t="n">
         <v>2.1</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -5438,10 +5438,10 @@
         <v>1.97</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
         <v>3.95</v>
@@ -5450,7 +5450,7 @@
         <v>1.34</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
         <v>4.3</v>
@@ -5471,19 +5471,19 @@
         <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W20" t="n">
         <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="n">
         <v>11</v>
@@ -5504,37 +5504,37 @@
         <v>11</v>
       </c>
       <c r="AE20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF20" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AG20" t="n">
         <v>17.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
         <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AL20" t="n">
         <v>120</v>
       </c>
       <c r="AM20" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
         <v>500</v>
       </c>
       <c r="AO20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP20" t="n">
         <v>15</v>
@@ -5561,7 +5561,7 @@
         <v>16.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY20" t="n">
         <v>14.5</v>
@@ -5570,13 +5570,13 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD20" t="n">
         <v>42</v>
@@ -5600,59 +5600,59 @@
         <v>9.6</v>
       </c>
       <c r="BK20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO20" t="n">
         <v>4.5</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT20" t="n">
         <v>4.9</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV20" t="n">
         <v>14</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="BX20" t="n">
         <v>29</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ20" t="n">
         <v>24</v>
       </c>
       <c r="CA20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -5692,13 +5692,13 @@
         <v>2.3</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J21" t="n">
         <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
         <v>1.39</v>
@@ -5746,7 +5746,7 @@
         <v>16.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AB21" t="n">
         <v>14</v>
@@ -5827,7 +5827,7 @@
         <v>18</v>
       </c>
       <c r="BB21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC21" t="n">
         <v>16</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G22" t="n">
         <v>2.1</v>
       </c>
       <c r="H22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
         <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L22" t="n">
         <v>1.29</v>
@@ -5970,7 +5970,7 @@
         <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R22" t="n">
         <v>1.44</v>
@@ -5985,7 +5985,7 @@
         <v>2.24</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
         <v>1.9</v>
@@ -6066,7 +6066,7 @@
         <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX22" t="n">
         <v>10</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
         <v>3.65</v>
       </c>
       <c r="O23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -6463,37 +6463,37 @@
         <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U24" t="n">
         <v>2.56</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W24" t="n">
         <v>1.73</v>
@@ -6553,7 +6553,7 @@
         <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>14.5</v>
@@ -6565,7 +6565,7 @@
         <v>27</v>
       </c>
       <c r="AT24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU24" t="n">
         <v>8.199999999999999</v>
@@ -6586,7 +6586,7 @@
         <v>14</v>
       </c>
       <c r="BA24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
         <v>20</v>
@@ -6616,19 +6616,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN24" t="n">
         <v>5.7</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP24" t="n">
         <v>16.5</v>
@@ -6637,7 +6637,7 @@
         <v>6.2</v>
       </c>
       <c r="BR24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS24" t="n">
         <v>7.6</v>
@@ -6646,13 +6646,13 @@
         <v>6.8</v>
       </c>
       <c r="BU24" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV24" t="n">
         <v>23</v>
       </c>
       <c r="BW24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX24" t="n">
         <v>32</v>
@@ -6664,11 +6664,11 @@
         <v>19</v>
       </c>
       <c r="CA24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G25" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H25" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.28</v>
@@ -6729,16 +6729,16 @@
         <v>1.22</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R25" t="n">
         <v>1.52</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T25" t="n">
         <v>1.68</v>
@@ -6855,10 +6855,10 @@
         <v>28</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH25" t="n">
         <v>4.2</v>
@@ -6870,25 +6870,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN25" t="n">
         <v>4.8</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP25" t="n">
         <v>12</v>
       </c>
       <c r="BQ25" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR25" t="n">
         <v>24</v>
@@ -6900,7 +6900,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV25" t="n">
         <v>38</v>
@@ -6912,17 +6912,17 @@
         <v>42</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ25" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G26" t="n">
         <v>5.6</v>
@@ -6962,7 +6962,7 @@
         <v>1.73</v>
       </c>
       <c r="I26" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J26" t="n">
         <v>3.8</v>
@@ -7061,7 +7061,7 @@
         <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AQ26" t="n">
         <v>6.2</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
         <v>4.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -7464,10 +7464,10 @@
         <v>2.4</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H28" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I28" t="n">
         <v>3.7</v>
@@ -7476,7 +7476,7 @@
         <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
         <v>1.47</v>
@@ -7485,10 +7485,10 @@
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O28" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
         <v>1.66</v>
@@ -7497,16 +7497,16 @@
         <v>2.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U28" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V28" t="n">
         <v>1.37</v>
@@ -7536,7 +7536,7 @@
         <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AF28" t="n">
         <v>32</v>
@@ -7554,7 +7554,7 @@
         <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AL28" t="n">
         <v>500</v>
@@ -7620,7 +7620,7 @@
         <v>20</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH28" t="n">
         <v>3.1</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
         <v>6.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC29" t="n">
         <v>6.2</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         <v>3.3</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
         <v>3.8</v>
@@ -8005,7 +8005,7 @@
         <v>1.79</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -8020,7 +8020,7 @@
         <v>1.44</v>
       </c>
       <c r="W30" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X30" t="n">
         <v>18</v>
@@ -8062,10 +8062,10 @@
         <v>34</v>
       </c>
       <c r="AK30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM30" t="n">
         <v>500</v>
@@ -8098,7 +8098,7 @@
         <v>10.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -8110,7 +8110,7 @@
         <v>12.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB30" t="n">
         <v>14.5</v>
@@ -8122,7 +8122,7 @@
         <v>18</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF30" t="n">
         <v>14.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -8223,19 +8223,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
         <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J31" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="K31" t="n">
         <v>2.7</v>
@@ -8253,7 +8253,7 @@
         <v>1.84</v>
       </c>
       <c r="P31" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Q31" t="n">
         <v>3.6</v>
@@ -8271,7 +8271,7 @@
         <v>1.51</v>
       </c>
       <c r="V31" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W31" t="n">
         <v>1.33</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -8477,13 +8477,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G32" t="n">
         <v>2.46</v>
       </c>
       <c r="H32" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I32" t="n">
         <v>4.3</v>
@@ -8606,7 +8606,7 @@
         <v>13.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
@@ -8627,7 +8627,7 @@
         <v>16</v>
       </c>
       <c r="BD32" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BE32" t="n">
         <v>9.199999999999999</v>
@@ -8660,7 +8660,7 @@
         <v>5.1</v>
       </c>
       <c r="BO32" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BP32" t="n">
         <v>23</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -8734,16 +8734,16 @@
         <v>1.93</v>
       </c>
       <c r="G33" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="H33" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I33" t="n">
         <v>4.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K33" t="n">
         <v>3.95</v>
@@ -8758,13 +8758,13 @@
         <v>3.95</v>
       </c>
       <c r="O33" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R33" t="n">
         <v>1.39</v>
@@ -8773,25 +8773,25 @@
         <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U33" t="n">
         <v>2.14</v>
       </c>
       <c r="V33" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W33" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X33" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y33" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z33" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AA33" t="n">
         <v>100</v>
@@ -8800,10 +8800,10 @@
         <v>10.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE33" t="n">
         <v>60</v>
@@ -8812,7 +8812,7 @@
         <v>12</v>
       </c>
       <c r="AG33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH33" t="n">
         <v>21</v>
@@ -8821,10 +8821,10 @@
         <v>65</v>
       </c>
       <c r="AJ33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK33" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL33" t="n">
         <v>34</v>
@@ -8842,25 +8842,25 @@
         <v>14.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS33" t="n">
         <v>36</v>
       </c>
       <c r="AT33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU33" t="n">
         <v>7.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX33" t="n">
         <v>10.5</v>
@@ -8881,16 +8881,16 @@
         <v>16.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BE33" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BF33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH33" t="n">
         <v>3.6</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -8985,19 +8985,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="G34" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H34" t="n">
         <v>2.44</v>
       </c>
       <c r="I34" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="J34" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K34" t="n">
         <v>3.85</v>
@@ -9018,25 +9018,25 @@
         <v>1.96</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R34" t="n">
         <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U34" t="n">
         <v>2.14</v>
       </c>
       <c r="V34" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W34" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X34" t="n">
         <v>18</v>
@@ -9054,7 +9054,7 @@
         <v>14</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD34" t="n">
         <v>13.5</v>
@@ -9075,22 +9075,22 @@
         <v>150</v>
       </c>
       <c r="AJ34" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AK34" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL34" t="n">
         <v>150</v>
       </c>
       <c r="AM34" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN34" t="n">
         <v>29</v>
       </c>
       <c r="AO34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP34" t="n">
         <v>12.5</v>
@@ -9126,7 +9126,7 @@
         <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB34" t="n">
         <v>7.4</v>
@@ -9135,16 +9135,16 @@
         <v>14.5</v>
       </c>
       <c r="BD34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE34" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>6.4</v>
       </c>
       <c r="BF34" t="n">
         <v>6.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BH34" t="n">
         <v>3.6</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -9248,10 +9248,10 @@
         <v>6.4</v>
       </c>
       <c r="I35" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J35" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K35" t="n">
         <v>4.1</v>
@@ -9263,7 +9263,7 @@
         <v>1.08</v>
       </c>
       <c r="N35" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
         <v>1.41</v>
@@ -9290,7 +9290,7 @@
         <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X35" t="n">
         <v>19</v>
@@ -9308,7 +9308,7 @@
         <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD35" t="n">
         <v>500</v>
@@ -9326,7 +9326,7 @@
         <v>30</v>
       </c>
       <c r="AI35" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AJ35" t="n">
         <v>16.5</v>
@@ -9335,7 +9335,7 @@
         <v>500</v>
       </c>
       <c r="AL35" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM35" t="n">
         <v>220</v>
@@ -9350,13 +9350,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT35" t="n">
         <v>4.7</v>
@@ -9368,7 +9368,7 @@
         <v>9</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX35" t="n">
         <v>5.3</v>
@@ -9380,10 +9380,10 @@
         <v>8.6</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB35" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC35" t="n">
         <v>8</v>
@@ -9398,7 +9398,7 @@
         <v>6.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH35" t="n">
         <v>3.15</v>
@@ -9410,7 +9410,7 @@
         <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
@@ -9422,19 +9422,19 @@
         <v>4.2</v>
       </c>
       <c r="BO35" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BP35" t="n">
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.92</v>
+        <v>7.8</v>
       </c>
       <c r="BT35" t="n">
         <v>1000</v>
@@ -9446,23 +9446,23 @@
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>9.199999999999999</v>
+        <v>1.88</v>
       </c>
       <c r="BZ35" t="n">
         <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
         <v>13</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J36" t="n">
         <v>7</v>
@@ -9517,7 +9517,7 @@
         <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O36" t="n">
         <v>1.16</v>
@@ -9526,22 +9526,22 @@
         <v>2.74</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R36" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S36" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T36" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
         <v>1.83</v>
       </c>
       <c r="V36" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W36" t="n">
         <v>4.8</v>
@@ -9553,31 +9553,31 @@
         <v>55</v>
       </c>
       <c r="Z36" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA36" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="AB36" t="n">
         <v>12</v>
       </c>
       <c r="AC36" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AD36" t="n">
         <v>55</v>
       </c>
       <c r="AE36" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AF36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG36" t="n">
         <v>13.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI36" t="n">
         <v>470</v>
@@ -9589,13 +9589,13 @@
         <v>16</v>
       </c>
       <c r="AL36" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM36" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN36" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AO36" t="n">
         <v>270</v>
@@ -9604,25 +9604,25 @@
         <v>13</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR36" t="n">
         <v>8.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU36" t="n">
         <v>14</v>
       </c>
       <c r="AV36" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX36" t="n">
         <v>7.8</v>
@@ -9652,25 +9652,25 @@
         <v>3.35</v>
       </c>
       <c r="BG36" t="n">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="BH36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK36" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN36" t="n">
         <v>4.1</v>
@@ -9685,38 +9685,38 @@
         <v>5.3</v>
       </c>
       <c r="BR36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS36" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BU36" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV36" t="n">
         <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX36" t="n">
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ36" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA36" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
         <v>2.1</v>
       </c>
       <c r="G37" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H37" t="n">
         <v>3.6</v>
@@ -9759,10 +9759,10 @@
         <v>3.9</v>
       </c>
       <c r="J37" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K37" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L37" t="n">
         <v>1.44</v>
@@ -9783,7 +9783,7 @@
         <v>2.02</v>
       </c>
       <c r="R37" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
         <v>3.75</v>
@@ -9798,7 +9798,7 @@
         <v>1.35</v>
       </c>
       <c r="W37" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X37" t="n">
         <v>14</v>
@@ -9834,7 +9834,7 @@
         <v>22</v>
       </c>
       <c r="AI37" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AJ37" t="n">
         <v>29</v>
@@ -9876,13 +9876,13 @@
         <v>12</v>
       </c>
       <c r="AW37" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX37" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ37" t="n">
         <v>15.5</v>
@@ -9930,13 +9930,13 @@
         <v>5.1</v>
       </c>
       <c r="BO37" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP37" t="n">
         <v>18</v>
       </c>
       <c r="BQ37" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="BR37" t="n">
         <v>38</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -10001,22 +10001,22 @@
         </is>
       </c>
       <c r="F38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H38" t="n">
         <v>2.5</v>
       </c>
-      <c r="G38" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="H38" t="n">
-        <v>2.52</v>
-      </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K38" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L38" t="n">
         <v>1.26</v>
@@ -10034,7 +10034,7 @@
         <v>2.26</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R38" t="n">
         <v>1.54</v>
@@ -10043,16 +10043,16 @@
         <v>2.46</v>
       </c>
       <c r="T38" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U38" t="n">
         <v>2.48</v>
       </c>
       <c r="V38" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="W38" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="X38" t="n">
         <v>500</v>
@@ -10070,7 +10070,7 @@
         <v>970</v>
       </c>
       <c r="AC38" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD38" t="n">
         <v>970</v>
@@ -10109,19 +10109,19 @@
         <v>55</v>
       </c>
       <c r="AP38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ38" t="n">
         <v>8.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="AT38" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU38" t="n">
         <v>5.1</v>
@@ -10130,40 +10130,40 @@
         <v>7</v>
       </c>
       <c r="AW38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX38" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>6.2</v>
       </c>
       <c r="AY38" t="n">
         <v>7</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BC38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="BH38" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BI38" t="n">
         <v>3.4</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -10279,22 +10279,22 @@
         <v>1.03</v>
       </c>
       <c r="N39" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="O39" t="n">
         <v>1.18</v>
       </c>
       <c r="P39" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R39" t="n">
         <v>1.58</v>
       </c>
       <c r="S39" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="T39" t="n">
         <v>1.68</v>
@@ -10306,7 +10306,7 @@
         <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X39" t="n">
         <v>950</v>
@@ -10357,64 +10357,64 @@
         <v>700</v>
       </c>
       <c r="AN39" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="AO39" t="n">
         <v>700</v>
       </c>
       <c r="AP39" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>5.1</v>
       </c>
-      <c r="AQ39" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS39" t="n">
+      <c r="BA39" t="n">
         <v>6</v>
       </c>
-      <c r="AT39" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BB39" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF39" t="n">
         <v>3.3</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH39" t="n">
         <v>4.5</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -10518,16 +10518,16 @@
         <v>3.1</v>
       </c>
       <c r="I40" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K40" t="n">
         <v>4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M40" t="n">
         <v>1.05</v>
@@ -10617,46 +10617,46 @@
         <v>27</v>
       </c>
       <c r="AP40" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AS40" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AT40" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU40" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AV40" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW40" t="n">
         <v>7.6</v>
       </c>
       <c r="AX40" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY40" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BA40" t="n">
         <v>7.8</v>
       </c>
       <c r="BB40" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC40" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BD40" t="n">
         <v>7.6</v>
@@ -10665,16 +10665,16 @@
         <v>17.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BG40" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BH40" t="n">
         <v>4</v>
       </c>
       <c r="BI40" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ40" t="n">
         <v>9.199999999999999</v>
@@ -10732,14 +10732,14 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10754,246 +10754,246 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="G41" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="H41" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I41" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="J41" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="K41" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L41" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="M41" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="N41" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="O41" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="P41" t="n">
-        <v>1.96</v>
+        <v>1.39</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="R41" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="S41" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X41" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE41" t="n">
         <v>3.55</v>
       </c>
-      <c r="T41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U41" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W41" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X41" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>14</v>
-      </c>
       <c r="BF41" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BG41" t="n">
-        <v>13</v>
+        <v>2.24</v>
       </c>
       <c r="BH41" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.84</v>
+        <v>2.1</v>
       </c>
       <c r="BJ41" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>5.1</v>
+        <v>1.51</v>
       </c>
       <c r="BL41" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>9.4</v>
+        <v>1.14</v>
       </c>
       <c r="BN41" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BP41" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>6</v>
+        <v>1.14</v>
       </c>
       <c r="BR41" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="BT41" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>6</v>
+        <v>1.22</v>
       </c>
       <c r="BV41" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>8</v>
+        <v>1.13</v>
       </c>
       <c r="BX41" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>8.4</v>
+        <v>1.13</v>
       </c>
       <c r="BZ41" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>7.2</v>
+        <v>1.11</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11008,239 +11008,239 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="G42" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="H42" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="I42" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="J42" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="K42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S42" t="n">
         <v>3.55</v>
       </c>
-      <c r="L42" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2</v>
+      </c>
+      <c r="X42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>130</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ42" t="n">
         <v>6.2</v>
       </c>
-      <c r="T42" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BF42" t="n">
+      <c r="BR42" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU42" t="n">
         <v>6</v>
       </c>
-      <c r="BG42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BI42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BJ42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BN42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO42" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BR42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BT42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU42" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BV42" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX42" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ42" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11295,7 @@
         <v>1.06</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O43" t="n">
         <v>1.3</v>
@@ -11316,7 +11316,7 @@
         <v>1.72</v>
       </c>
       <c r="U43" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V43" t="n">
         <v>1.64</v>
@@ -11361,7 +11361,7 @@
         <v>85</v>
       </c>
       <c r="AJ43" t="n">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="AK43" t="n">
         <v>75</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="J44" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="K44" t="n">
         <v>15</v>
@@ -11546,7 +11546,7 @@
         <v>1.2</v>
       </c>
       <c r="M44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N44" t="n">
         <v>8.6</v>
@@ -11555,7 +11555,7 @@
         <v>1.12</v>
       </c>
       <c r="P44" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q44" t="n">
         <v>1.38</v>
@@ -11570,7 +11570,7 @@
         <v>2.68</v>
       </c>
       <c r="U44" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V44" t="n">
         <v>1.02</v>
@@ -11579,7 +11579,7 @@
         <v>10</v>
       </c>
       <c r="X44" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y44" t="n">
         <v>110</v>
@@ -11591,7 +11591,7 @@
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC44" t="n">
         <v>32</v>
@@ -11600,19 +11600,19 @@
         <v>120</v>
       </c>
       <c r="AE44" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AF44" t="n">
         <v>7.8</v>
       </c>
       <c r="AG44" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH44" t="n">
         <v>75</v>
       </c>
       <c r="AI44" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="AJ44" t="n">
         <v>7.6</v>
@@ -11633,7 +11633,7 @@
         <v>990</v>
       </c>
       <c r="AP44" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AQ44" t="n">
         <v>85</v>
@@ -11651,16 +11651,16 @@
         <v>29</v>
       </c>
       <c r="AV44" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AW44" t="n">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="AX44" t="n">
         <v>7.4</v>
       </c>
       <c r="AY44" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ44" t="n">
         <v>60</v>
@@ -11681,7 +11681,7 @@
         <v>170</v>
       </c>
       <c r="BF44" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BG44" t="n">
         <v>300</v>
@@ -11702,7 +11702,7 @@
         <v>220</v>
       </c>
       <c r="BM44" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BN44" t="n">
         <v>3.8</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
         <v>2.56</v>
       </c>
       <c r="H45" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I45" t="n">
         <v>2.94</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -12165,7 +12165,7 @@
         <v>4.2</v>
       </c>
       <c r="AX46" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AY46" t="n">
         <v>8</v>
@@ -12183,10 +12183,10 @@
         <v>10.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BE46" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF46" t="n">
         <v>4.3</v>
@@ -12210,7 +12210,7 @@
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>4.7</v>
+        <v>2.04</v>
       </c>
       <c r="BN46" t="n">
         <v>4.8</v>
@@ -12240,7 +12240,7 @@
         <v>1000</v>
       </c>
       <c r="BW46" t="n">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="BX46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>1.48</v>
       </c>
       <c r="G47" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H47" t="n">
         <v>5.9</v>
@@ -12338,7 +12338,7 @@
         <v>1.16</v>
       </c>
       <c r="W47" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X47" t="n">
         <v>75</v>
@@ -12380,7 +12380,7 @@
         <v>36</v>
       </c>
       <c r="AK47" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL47" t="n">
         <v>500</v>
@@ -12401,7 +12401,7 @@
         <v>14.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS47" t="n">
         <v>9.199999999999999</v>
@@ -12413,7 +12413,7 @@
         <v>10.5</v>
       </c>
       <c r="AV47" t="n">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="AW47" t="n">
         <v>8.6</v>
@@ -12437,10 +12437,10 @@
         <v>11</v>
       </c>
       <c r="BD47" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BE47" t="n">
-        <v>28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF47" t="n">
         <v>4.7</v>
@@ -12491,7 +12491,7 @@
         <v>5.2</v>
       </c>
       <c r="BV47" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW47" t="n">
         <v>7.8</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
         <v>5.1</v>
       </c>
       <c r="K48" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L48" t="n">
         <v>1.22</v>
@@ -12595,7 +12595,7 @@
         <v>1.19</v>
       </c>
       <c r="X48" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y48" t="n">
         <v>14</v>
@@ -12619,7 +12619,7 @@
         <v>15</v>
       </c>
       <c r="AF48" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AG48" t="n">
         <v>25</v>
@@ -12676,7 +12676,7 @@
         <v>7</v>
       </c>
       <c r="AY48" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ48" t="n">
         <v>15</v>
@@ -12712,7 +12712,7 @@
         <v>11</v>
       </c>
       <c r="BK48" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
@@ -12754,7 +12754,7 @@
         <v>22</v>
       </c>
       <c r="BY48" t="n">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="BZ48" t="n">
         <v>0</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="G49" t="n">
         <v>2.08</v>
       </c>
       <c r="H49" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I49" t="n">
         <v>5.2</v>
@@ -12810,7 +12810,7 @@
         <v>3.2</v>
       </c>
       <c r="K49" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L49" t="n">
         <v>1.49</v>
@@ -12819,7 +12819,7 @@
         <v>1.1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O49" t="n">
         <v>1.43</v>
@@ -12840,7 +12840,7 @@
         <v>2.02</v>
       </c>
       <c r="U49" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V49" t="n">
         <v>1.23</v>
@@ -12852,7 +12852,7 @@
         <v>18</v>
       </c>
       <c r="Y49" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Z49" t="n">
         <v>500</v>
@@ -12864,10 +12864,10 @@
         <v>7.4</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD49" t="n">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="AE49" t="n">
         <v>700</v>
@@ -12885,7 +12885,7 @@
         <v>700</v>
       </c>
       <c r="AJ49" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK49" t="n">
         <v>110</v>
@@ -12909,52 +12909,52 @@
         <v>10.5</v>
       </c>
       <c r="AR49" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="AS49" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT49" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU49" t="n">
         <v>4.9</v>
       </c>
       <c r="AV49" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AW49" t="n">
         <v>8.4</v>
       </c>
       <c r="AX49" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="AY49" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ49" t="n">
         <v>17</v>
       </c>
       <c r="BA49" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB49" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC49" t="n">
         <v>18.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE49" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BF49" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG49" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH49" t="n">
         <v>3.05</v>
@@ -12972,7 +12972,7 @@
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="BN49" t="n">
         <v>4.6</v>
@@ -12990,7 +12990,7 @@
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT49" t="n">
         <v>8.4</v>
@@ -13002,13 +13002,13 @@
         <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ49" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -13055,10 +13055,10 @@
         <v>2.04</v>
       </c>
       <c r="H50" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I50" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J50" t="n">
         <v>3.4</v>
@@ -13079,10 +13079,10 @@
         <v>1.43</v>
       </c>
       <c r="P50" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R50" t="n">
         <v>1.25</v>
@@ -13154,7 +13154,7 @@
         <v>21</v>
       </c>
       <c r="AO50" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AP50" t="n">
         <v>8.6</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -13309,10 +13309,10 @@
         <v>2.44</v>
       </c>
       <c r="H51" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I51" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>2.98</v>
@@ -13321,7 +13321,7 @@
         <v>3.25</v>
       </c>
       <c r="L51" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="M51" t="n">
         <v>1.12</v>
@@ -13333,7 +13333,7 @@
         <v>1.52</v>
       </c>
       <c r="P51" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q51" t="n">
         <v>2.52</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="AI51" t="n">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="AJ51" t="n">
         <v>40</v>
@@ -13420,7 +13420,7 @@
         <v>11.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT51" t="n">
         <v>6.6</v>
@@ -13432,7 +13432,7 @@
         <v>14.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX51" t="n">
         <v>11.5</v>
@@ -13462,7 +13462,7 @@
         <v>5.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH51" t="n">
         <v>2.78</v>
@@ -13471,16 +13471,16 @@
         <v>2.28</v>
       </c>
       <c r="BJ51" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK51" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN51" t="n">
         <v>4.9</v>
@@ -13492,13 +13492,13 @@
         <v>24</v>
       </c>
       <c r="BQ51" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR51" t="n">
         <v>50</v>
       </c>
       <c r="BS51" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT51" t="n">
         <v>7</v>
@@ -13510,13 +13510,13 @@
         <v>46</v>
       </c>
       <c r="BW51" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX51" t="n">
         <v>70</v>
       </c>
       <c r="BY51" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ51" t="n">
         <v>0</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
         <v>3.05</v>
       </c>
       <c r="K53" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L53" t="n">
         <v>1.51</v>
@@ -13850,7 +13850,7 @@
         <v>1.21</v>
       </c>
       <c r="S53" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T53" t="n">
         <v>2.04</v>
@@ -13880,7 +13880,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC53" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD53" t="n">
         <v>23</v>
@@ -13925,10 +13925,10 @@
         <v>9.6</v>
       </c>
       <c r="AR53" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS53" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT53" t="n">
         <v>6</v>
@@ -13940,7 +13940,7 @@
         <v>16</v>
       </c>
       <c r="AW53" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX53" t="n">
         <v>9.6</v>
@@ -13952,25 +13952,25 @@
         <v>19.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB53" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BC53" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE53" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF53" t="n">
         <v>20</v>
       </c>
       <c r="BG53" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH53" t="n">
         <v>2.94</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
         <v>2.22</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H54" t="n">
         <v>3.55</v>
@@ -14098,7 +14098,7 @@
         <v>1.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R54" t="n">
         <v>1.22</v>
@@ -14110,7 +14110,7 @@
         <v>1.96</v>
       </c>
       <c r="U54" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V54" t="n">
         <v>1.31</v>
@@ -14119,46 +14119,46 @@
         <v>1.66</v>
       </c>
       <c r="X54" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA54" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB54" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC54" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE54" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF54" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG54" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI54" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ54" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK54" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL54" t="n">
         <v>65</v>
@@ -14170,7 +14170,7 @@
         <v>34</v>
       </c>
       <c r="AO54" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP54" t="n">
         <v>8.4</v>
@@ -14182,7 +14182,7 @@
         <v>19.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AT54" t="n">
         <v>6.8</v>
@@ -14194,7 +14194,7 @@
         <v>13.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX54" t="n">
         <v>11.5</v>
@@ -14206,25 +14206,25 @@
         <v>17.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BB54" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC54" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE54" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BF54" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BG54" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH54" t="n">
         <v>2.98</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
         <v>2.14</v>
       </c>
       <c r="G55" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H55" t="n">
         <v>3.35</v>
@@ -14334,7 +14334,7 @@
         <v>2.94</v>
       </c>
       <c r="K55" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L55" t="n">
         <v>1.36</v>
@@ -14358,7 +14358,7 @@
         <v>1.3</v>
       </c>
       <c r="S55" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T55" t="n">
         <v>1.78</v>
@@ -14367,7 +14367,7 @@
         <v>2</v>
       </c>
       <c r="V55" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W55" t="n">
         <v>1.68</v>
@@ -14433,19 +14433,19 @@
         <v>9.6</v>
       </c>
       <c r="AR55" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS55" t="n">
         <v>4.1</v>
       </c>
       <c r="AT55" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU55" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV55" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AW55" t="n">
         <v>4.1</v>
@@ -14457,22 +14457,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ55" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BA55" t="n">
         <v>4.1</v>
       </c>
       <c r="BB55" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BD55" t="n">
         <v>4.1</v>
       </c>
       <c r="BE55" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF55" t="n">
         <v>14.5</v>
@@ -14481,7 +14481,7 @@
         <v>4.1</v>
       </c>
       <c r="BH55" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BI55" t="n">
         <v>2.62</v>
@@ -14490,16 +14490,16 @@
         <v>1000</v>
       </c>
       <c r="BK55" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>5.9</v>
+        <v>1.62</v>
       </c>
       <c r="BN55" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BO55" t="n">
         <v>3.9</v>
@@ -14508,13 +14508,13 @@
         <v>1000</v>
       </c>
       <c r="BQ55" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BR55" t="n">
         <v>1000</v>
       </c>
       <c r="BS55" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BT55" t="n">
         <v>7.2</v>
@@ -14526,23 +14526,23 @@
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ55" t="n">
         <v>1000</v>
       </c>
       <c r="CA55" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -14573,220 +14573,220 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="G56" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H56" t="n">
         <v>3.6</v>
       </c>
       <c r="I56" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J56" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K56" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L56" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M56" t="n">
         <v>1.06</v>
       </c>
       <c r="N56" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O56" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P56" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="Q56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W56" t="n">
         <v>1.83</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S56" t="n">
-        <v>3</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.84</v>
       </c>
       <c r="X56" t="n">
         <v>16.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z56" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA56" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM56" t="n">
         <v>110</v>
       </c>
-      <c r="AB56" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD56" t="n">
+      <c r="AN56" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB56" t="n">
         <v>20</v>
       </c>
-      <c r="AE56" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK56" t="n">
+      <c r="BC56" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD56" t="n">
         <v>25</v>
       </c>
-      <c r="AL56" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE56" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BF56" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BG56" t="n">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="BH56" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK56" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN56" t="n">
         <v>5.1</v>
       </c>
       <c r="BO56" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="BP56" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ56" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR56" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT56" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU56" t="n">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="BV56" t="n">
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BZ56" t="n">
         <v>0</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
         <v>3.35</v>
       </c>
       <c r="G57" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H57" t="n">
         <v>2.46</v>
@@ -14872,13 +14872,13 @@
         <v>1.93</v>
       </c>
       <c r="U57" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V57" t="n">
         <v>1.6</v>
       </c>
       <c r="W57" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X57" t="n">
         <v>970</v>
@@ -14935,25 +14935,25 @@
         <v>36</v>
       </c>
       <c r="AP57" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ57" t="n">
         <v>7.2</v>
       </c>
       <c r="AR57" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS57" t="n">
         <v>5.9</v>
       </c>
       <c r="AT57" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU57" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="AV57" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW57" t="n">
         <v>5.7</v>
@@ -14962,7 +14962,7 @@
         <v>5.3</v>
       </c>
       <c r="AY57" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ57" t="n">
         <v>5.1</v>
@@ -15010,7 +15010,7 @@
         <v>6.6</v>
       </c>
       <c r="BO57" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP57" t="n">
         <v>1000</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-17 21:14:06</t>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
@@ -15067,36 +15067,36 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>23:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Real Espana</t>
+          <t>CD Motagua</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Marathon</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G58" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H58" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I58" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J58" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="K58" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -15105,34 +15105,34 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O58" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="P58" t="n">
         <v>1.24</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="R58" t="n">
         <v>1.18</v>
       </c>
       <c r="S58" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T58" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U58" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V58" t="n">
         <v>1.01</v>
       </c>
       <c r="W58" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X58" t="n">
         <v>1000</v>
@@ -15246,65 +15246,319 @@
         <v>1000</v>
       </c>
       <c r="BI58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB58" t="inlineStr">
+        <is>
+          <t>2026-05-17 23:28:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>23:15:00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Real Espana</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>CD Marathon</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G59" t="n">
+        <v>990</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I59" t="n">
+        <v>990</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K59" t="n">
+        <v>500</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI59" t="n">
         <v>1.04</v>
       </c>
-      <c r="BJ58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK58" t="n">
+      <c r="BJ59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK59" t="n">
         <v>1.04</v>
       </c>
-      <c r="BL58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM58" t="n">
+      <c r="BL59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM59" t="n">
         <v>1.04</v>
       </c>
-      <c r="BN58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO58" t="n">
+      <c r="BN59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO59" t="n">
         <v>1.04</v>
       </c>
-      <c r="BP58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ58" t="n">
+      <c r="BP59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ59" t="n">
         <v>1.04</v>
       </c>
-      <c r="BR58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS58" t="n">
+      <c r="BR59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS59" t="n">
         <v>1.04</v>
       </c>
-      <c r="BT58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU58" t="n">
+      <c r="BT59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU59" t="n">
         <v>1.04</v>
       </c>
-      <c r="BV58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW58" t="n">
+      <c r="BV59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW59" t="n">
         <v>1.04</v>
       </c>
-      <c r="BX58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY58" t="n">
+      <c r="BX59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY59" t="n">
         <v>1.04</v>
       </c>
-      <c r="BZ58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA58" t="n">
+      <c r="BZ59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA59" t="n">
         <v>1.04</v>
       </c>
-      <c r="CB58" t="inlineStr">
-        <is>
-          <t>2026-05-17 21:14:06</t>
+      <c r="CB59" t="inlineStr">
+        <is>
+          <t>2026-05-17 23:28:34</t>
         </is>
       </c>
     </row>
